--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="224">
   <si>
     <t>200006191</t>
   </si>
@@ -289,27 +289,6 @@
     <t>M90頭鏟花</t>
   </si>
   <si>
-    <t>200006329</t>
-  </si>
-  <si>
-    <t>1400091196</t>
-  </si>
-  <si>
-    <t>1400094675</t>
-  </si>
-  <si>
-    <t>1400091295</t>
-  </si>
-  <si>
-    <t>1400094678</t>
-  </si>
-  <si>
-    <t>1400091197</t>
-  </si>
-  <si>
-    <t>1400094679</t>
-  </si>
-  <si>
     <t>200006349</t>
   </si>
   <si>
@@ -434,21 +413,6 @@
   </si>
   <si>
     <t>1400095562</t>
-  </si>
-  <si>
-    <t>200006413</t>
-  </si>
-  <si>
-    <t>1400093327</t>
-  </si>
-  <si>
-    <t>0060</t>
-  </si>
-  <si>
-    <t>1400097007</t>
-  </si>
-  <si>
-    <t>機頭精度檢驗</t>
   </si>
   <si>
     <t>200006425</t>
@@ -823,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -848,58 +812,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="N1" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="R1" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2325,28 +2289,28 @@
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I27" s="2">
-        <v>46083</v>
+        <v>46014</v>
       </c>
       <c r="J27" t="s">
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M27" s="3">
         <v>1</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="P27" t="s">
         <v>7</v>
@@ -2355,7 +2319,7 @@
         <v>7</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2372,7 +2336,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>96</v>
@@ -2381,28 +2345,28 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I28" s="2">
-        <v>46099</v>
+        <v>46015</v>
       </c>
       <c r="J28" t="s">
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M28" s="3">
         <v>1</v>
       </c>
       <c r="N28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="P28" t="s">
         <v>7</v>
@@ -2411,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="R28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2428,7 +2392,7 @@
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
         <v>98</v>
@@ -2437,16 +2401,16 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2">
-        <v>46099</v>
+        <v>46037</v>
       </c>
       <c r="J29" t="s">
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
         <v>7</v>
@@ -2458,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="2">
-        <v>45979</v>
+        <v>46030</v>
       </c>
       <c r="P29" t="s">
         <v>7</v>
@@ -2472,37 +2436,37 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
         <v>99</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
         <v>100</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" t="s">
-        <v>101</v>
-      </c>
       <c r="G30" t="s">
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I30" s="2">
-        <v>46014</v>
+        <v>46027</v>
       </c>
       <c r="J30" t="s">
         <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L30" t="s">
         <v>9</v>
@@ -2528,37 +2492,37 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" t="s">
         <v>102</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" t="s">
-        <v>103</v>
-      </c>
       <c r="G31" t="s">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I31" s="2">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="J31" t="s">
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L31" t="s">
         <v>9</v>
@@ -2584,49 +2548,49 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" t="s">
         <v>104</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" t="s">
-        <v>105</v>
-      </c>
       <c r="G32" t="s">
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I32" s="2">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="J32" t="s">
         <v>7</v>
       </c>
       <c r="K32" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="L32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M32" s="3">
         <v>1</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2">
-        <v>46030</v>
+        <v>45987</v>
       </c>
       <c r="P32" t="s">
         <v>7</v>
@@ -2635,27 +2599,27 @@
         <v>7</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
         <v>106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" t="s">
-        <v>107</v>
       </c>
       <c r="G33" t="s">
         <v>2</v>
@@ -2664,13 +2628,13 @@
         <v>6</v>
       </c>
       <c r="I33" s="2">
-        <v>46027</v>
+        <v>46014</v>
       </c>
       <c r="J33" t="s">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="L33" t="s">
         <v>9</v>
@@ -2696,22 +2660,22 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" t="s">
         <v>108</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" t="s">
-        <v>109</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
@@ -2720,13 +2684,13 @@
         <v>19</v>
       </c>
       <c r="I34" s="2">
-        <v>46027</v>
+        <v>46020</v>
       </c>
       <c r="J34" t="s">
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L34" t="s">
         <v>9</v>
@@ -2752,7 +2716,7 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B35" t="s">
         <v>110</v>
@@ -2764,7 +2728,7 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F35" t="s">
         <v>111</v>
@@ -2776,25 +2740,25 @@
         <v>6</v>
       </c>
       <c r="I35" s="2">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="J35" t="s">
         <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M35" s="3">
         <v>1</v>
       </c>
       <c r="N35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="P35" t="s">
         <v>7</v>
@@ -2803,27 +2767,27 @@
         <v>7</v>
       </c>
       <c r="R35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
       </c>
       <c r="F36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
@@ -2832,25 +2796,25 @@
         <v>6</v>
       </c>
       <c r="I36" s="2">
-        <v>46014</v>
+        <v>46065</v>
       </c>
       <c r="J36" t="s">
         <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="L36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M36" s="3">
         <v>1</v>
       </c>
       <c r="N36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="P36" t="s">
         <v>7</v>
@@ -2859,27 +2823,27 @@
         <v>7</v>
       </c>
       <c r="R36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
@@ -2888,25 +2852,25 @@
         <v>19</v>
       </c>
       <c r="I37" s="2">
-        <v>46020</v>
+        <v>46097</v>
       </c>
       <c r="J37" t="s">
         <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="L37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M37" s="3">
         <v>1</v>
       </c>
       <c r="N37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="P37" t="s">
         <v>7</v>
@@ -2915,15 +2879,15 @@
         <v>7</v>
       </c>
       <c r="R37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -2935,7 +2899,7 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
@@ -2944,42 +2908,42 @@
         <v>6</v>
       </c>
       <c r="I38" s="2">
-        <v>46065</v>
+        <v>46014</v>
       </c>
       <c r="J38" t="s">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="L38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M38" s="3">
         <v>1</v>
       </c>
       <c r="N38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2">
-        <v>45995</v>
+        <v>46035</v>
       </c>
       <c r="P38" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
@@ -2988,37 +2952,37 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I39" s="2">
-        <v>46065</v>
+        <v>46029</v>
       </c>
       <c r="J39" t="s">
         <v>7</v>
       </c>
       <c r="K39" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="P39" t="s">
         <v>7</v>
@@ -3032,10 +2996,10 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -3044,46 +3008,46 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="F40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I40" s="2">
-        <v>46097</v>
+        <v>46029</v>
       </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="L40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M40" s="3">
         <v>1</v>
       </c>
       <c r="N40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2">
-        <v>45995</v>
+        <v>46035</v>
       </c>
       <c r="P40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -3112,7 +3076,7 @@
         <v>6</v>
       </c>
       <c r="I41" s="2">
-        <v>46014</v>
+        <v>46007</v>
       </c>
       <c r="J41" t="s">
         <v>7</v>
@@ -3168,7 +3132,7 @@
         <v>19</v>
       </c>
       <c r="I42" s="2">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="J42" t="s">
         <v>7</v>
@@ -3186,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="2">
-        <v>46002</v>
+        <v>46055</v>
       </c>
       <c r="P42" t="s">
         <v>7</v>
@@ -3224,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="I43" s="2">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="J43" t="s">
         <v>7</v>
@@ -3277,37 +3241,37 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I44" s="2">
-        <v>46007</v>
+        <v>46092</v>
       </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="L44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M44" s="3">
         <v>1</v>
       </c>
       <c r="N44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2">
-        <v>46035</v>
+        <v>46028</v>
       </c>
       <c r="P44" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -3324,7 +3288,7 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F45" t="s">
         <v>138</v>
@@ -3333,16 +3297,16 @@
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I45" s="2">
-        <v>46024</v>
+        <v>46093</v>
       </c>
       <c r="J45" t="s">
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s">
         <v>7</v>
@@ -3354,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="2">
-        <v>46002</v>
+        <v>46029</v>
       </c>
       <c r="P45" t="s">
         <v>7</v>
@@ -3380,7 +3344,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
         <v>140</v>
@@ -3392,54 +3356,54 @@
         <v>6</v>
       </c>
       <c r="I46" s="2">
-        <v>46024</v>
+        <v>46105</v>
       </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M46" s="3">
         <v>1</v>
       </c>
       <c r="N46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="2">
-        <v>46035</v>
+        <v>46029</v>
       </c>
       <c r="P46" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" t="s">
         <v>141</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F47" t="s">
         <v>142</v>
-      </c>
-      <c r="C47" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" t="s">
-        <v>143</v>
-      </c>
-      <c r="F47" t="s">
-        <v>144</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
@@ -3448,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="I47" s="2">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="L47" t="s">
         <v>7</v>
@@ -3466,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="2">
-        <v>46049</v>
+        <v>46028</v>
       </c>
       <c r="P47" t="s">
         <v>7</v>
@@ -3480,10 +3444,10 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
@@ -3492,25 +3456,25 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F48" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I48" s="2">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J48" t="s">
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="L48" t="s">
         <v>7</v>
@@ -3522,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="P48" t="s">
         <v>7</v>
@@ -3536,22 +3500,22 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" t="s">
         <v>146</v>
-      </c>
-      <c r="B49" t="s">
-        <v>149</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" t="s">
-        <v>45</v>
-      </c>
-      <c r="F49" t="s">
-        <v>150</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
@@ -3560,13 +3524,13 @@
         <v>6</v>
       </c>
       <c r="I49" s="2">
-        <v>46093</v>
+        <v>46092</v>
       </c>
       <c r="J49" t="s">
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L49" t="s">
         <v>7</v>
@@ -3592,37 +3556,37 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
       </c>
       <c r="F50" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I50" s="2">
-        <v>46105</v>
+        <v>46097</v>
       </c>
       <c r="J50" t="s">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L50" t="s">
         <v>7</v>
@@ -3634,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="P50" t="s">
         <v>7</v>
@@ -3648,10 +3612,10 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
@@ -3660,10 +3624,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
@@ -3672,13 +3636,13 @@
         <v>19</v>
       </c>
       <c r="I51" s="2">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="J51" t="s">
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L51" t="s">
         <v>7</v>
@@ -3690,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="P51" t="s">
         <v>7</v>
@@ -3704,10 +3668,10 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
@@ -3716,10 +3680,10 @@
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F52" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
@@ -3728,13 +3692,13 @@
         <v>6</v>
       </c>
       <c r="I52" s="2">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="J52" t="s">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L52" t="s">
         <v>7</v>
@@ -3746,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="P52" t="s">
         <v>7</v>
@@ -3760,22 +3724,22 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
@@ -3784,13 +3748,13 @@
         <v>6</v>
       </c>
       <c r="I53" s="2">
-        <v>46092</v>
+        <v>46126</v>
       </c>
       <c r="J53" t="s">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L53" t="s">
         <v>7</v>
@@ -3802,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="P53" t="s">
         <v>7</v>
@@ -3816,22 +3780,22 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C54" t="s">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F54" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G54" t="s">
         <v>2</v>
@@ -3840,13 +3804,13 @@
         <v>19</v>
       </c>
       <c r="I54" s="2">
-        <v>46097</v>
+        <v>46126</v>
       </c>
       <c r="J54" t="s">
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L54" t="s">
         <v>7</v>
@@ -3858,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="P54" t="s">
         <v>7</v>
@@ -3872,10 +3836,10 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
         <v>2</v>
@@ -3884,25 +3848,25 @@
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G55" t="s">
         <v>2</v>
       </c>
       <c r="H55" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I55" s="2">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="J55" t="s">
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="L55" t="s">
         <v>7</v>
@@ -3914,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="P55" t="s">
         <v>7</v>
@@ -3928,22 +3892,22 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" t="s">
+        <v>30</v>
+      </c>
+      <c r="F56" t="s">
         <v>161</v>
-      </c>
-      <c r="B56" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>3</v>
-      </c>
-      <c r="E56" t="s">
-        <v>45</v>
-      </c>
-      <c r="F56" t="s">
-        <v>165</v>
       </c>
       <c r="G56" t="s">
         <v>2</v>
@@ -3952,13 +3916,13 @@
         <v>6</v>
       </c>
       <c r="I56" s="2">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="J56" t="s">
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L56" t="s">
         <v>7</v>
@@ -3984,37 +3948,37 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B57" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
         <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E57" t="s">
         <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G57" t="s">
         <v>2</v>
       </c>
       <c r="H57" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I57" s="2">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="J57" t="s">
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L57" t="s">
         <v>7</v>
@@ -4026,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="P57" t="s">
         <v>7</v>
@@ -4040,10 +4004,10 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
@@ -4052,10 +4016,10 @@
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G58" t="s">
         <v>2</v>
@@ -4064,13 +4028,13 @@
         <v>19</v>
       </c>
       <c r="I58" s="2">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="J58" t="s">
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L58" t="s">
         <v>7</v>
@@ -4082,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="P58" t="s">
         <v>7</v>
@@ -4096,10 +4060,10 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
@@ -4108,10 +4072,10 @@
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G59" t="s">
         <v>2</v>
@@ -4120,13 +4084,13 @@
         <v>6</v>
       </c>
       <c r="I59" s="2">
-        <v>46129</v>
+        <v>46121</v>
       </c>
       <c r="J59" t="s">
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L59" t="s">
         <v>7</v>
@@ -4152,22 +4116,22 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C60" t="s">
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G60" t="s">
         <v>2</v>
@@ -4176,13 +4140,13 @@
         <v>6</v>
       </c>
       <c r="I60" s="2">
-        <v>46113</v>
+        <v>46133</v>
       </c>
       <c r="J60" t="s">
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L60" t="s">
         <v>7</v>
@@ -4208,22 +4172,22 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B61" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F61" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G61" t="s">
         <v>2</v>
@@ -4232,13 +4196,13 @@
         <v>19</v>
       </c>
       <c r="I61" s="2">
-        <v>46120</v>
+        <v>46133</v>
       </c>
       <c r="J61" t="s">
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L61" t="s">
         <v>7</v>
@@ -4250,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="P61" t="s">
         <v>7</v>
@@ -4264,10 +4228,10 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B62" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
         <v>2</v>
@@ -4276,25 +4240,25 @@
         <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F62" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G62" t="s">
         <v>2</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I62" s="2">
-        <v>46120</v>
+        <v>46136</v>
       </c>
       <c r="J62" t="s">
         <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="L62" t="s">
         <v>7</v>
@@ -4320,22 +4284,22 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" t="s">
+        <v>164</v>
+      </c>
+      <c r="B63" t="s">
+        <v>175</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" t="s">
         <v>176</v>
-      </c>
-      <c r="B63" t="s">
-        <v>179</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>45</v>
-      </c>
-      <c r="F63" t="s">
-        <v>180</v>
       </c>
       <c r="G63" t="s">
         <v>2</v>
@@ -4344,13 +4308,13 @@
         <v>6</v>
       </c>
       <c r="I63" s="2">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="J63" t="s">
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L63" t="s">
         <v>7</v>
@@ -4376,37 +4340,37 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E64" t="s">
         <v>53</v>
       </c>
       <c r="F64" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G64" t="s">
         <v>2</v>
       </c>
       <c r="H64" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I64" s="2">
-        <v>46133</v>
+        <v>46125</v>
       </c>
       <c r="J64" t="s">
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L64" t="s">
         <v>7</v>
@@ -4432,10 +4396,10 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C65" t="s">
         <v>2</v>
@@ -4444,10 +4408,10 @@
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="F65" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G65" t="s">
         <v>2</v>
@@ -4456,13 +4420,13 @@
         <v>19</v>
       </c>
       <c r="I65" s="2">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="J65" t="s">
         <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L65" t="s">
         <v>7</v>
@@ -4474,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="2">
-        <v>46028</v>
+        <v>46046</v>
       </c>
       <c r="P65" t="s">
         <v>7</v>
@@ -4488,10 +4452,10 @@
     </row>
     <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B66" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
@@ -4500,10 +4464,10 @@
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F66" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G66" t="s">
         <v>2</v>
@@ -4512,13 +4476,13 @@
         <v>6</v>
       </c>
       <c r="I66" s="2">
-        <v>46136</v>
+        <v>46128</v>
       </c>
       <c r="J66" t="s">
         <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L66" t="s">
         <v>7</v>
@@ -4530,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="2">
-        <v>46028</v>
+        <v>46046</v>
       </c>
       <c r="P66" t="s">
         <v>7</v>
@@ -4544,22 +4508,22 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B67" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F67" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G67" t="s">
         <v>2</v>
@@ -4568,13 +4532,13 @@
         <v>6</v>
       </c>
       <c r="I67" s="2">
-        <v>46120</v>
+        <v>46140</v>
       </c>
       <c r="J67" t="s">
         <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L67" t="s">
         <v>7</v>
@@ -4586,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="2">
-        <v>46028</v>
+        <v>46046</v>
       </c>
       <c r="P67" t="s">
         <v>7</v>
@@ -4600,22 +4564,22 @@
     </row>
     <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B68" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F68" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G68" t="s">
         <v>2</v>
@@ -4624,13 +4588,13 @@
         <v>19</v>
       </c>
       <c r="I68" s="2">
-        <v>46125</v>
+        <v>46140</v>
       </c>
       <c r="J68" t="s">
         <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L68" t="s">
         <v>7</v>
@@ -4642,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="2">
-        <v>46028</v>
+        <v>46046</v>
       </c>
       <c r="P68" t="s">
         <v>7</v>
@@ -4656,10 +4620,10 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C69" t="s">
         <v>2</v>
@@ -4668,25 +4632,25 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F69" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G69" t="s">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I69" s="2">
-        <v>46127</v>
+        <v>46146</v>
       </c>
       <c r="J69" t="s">
         <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="L69" t="s">
         <v>7</v>
@@ -4712,22 +4676,22 @@
     </row>
     <row r="70" spans="1:18">
       <c r="A70" t="s">
+        <v>179</v>
+      </c>
+      <c r="B70" t="s">
+        <v>190</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" t="s">
         <v>191</v>
-      </c>
-      <c r="B70" t="s">
-        <v>194</v>
-      </c>
-      <c r="C70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" t="s">
-        <v>45</v>
-      </c>
-      <c r="F70" t="s">
-        <v>195</v>
       </c>
       <c r="G70" t="s">
         <v>2</v>
@@ -4736,13 +4700,13 @@
         <v>6</v>
       </c>
       <c r="I70" s="2">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="J70" t="s">
         <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L70" t="s">
         <v>7</v>
@@ -4768,37 +4732,37 @@
     </row>
     <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B71" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C71" t="s">
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E71" t="s">
         <v>53</v>
       </c>
       <c r="F71" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G71" t="s">
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I71" s="2">
-        <v>46140</v>
+        <v>46132</v>
       </c>
       <c r="J71" t="s">
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L71" t="s">
         <v>7</v>
@@ -4824,10 +4788,10 @@
     </row>
     <row r="72" spans="1:18">
       <c r="A72" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B72" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C72" t="s">
         <v>2</v>
@@ -4836,25 +4800,25 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F72" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G72" t="s">
         <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I72" s="2">
-        <v>46140</v>
+        <v>46045</v>
       </c>
       <c r="J72" t="s">
         <v>7</v>
       </c>
       <c r="K72" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L72" t="s">
         <v>7</v>
@@ -4866,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="2">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="P72" t="s">
         <v>7</v>
@@ -4880,22 +4844,22 @@
     </row>
     <row r="73" spans="1:18">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C73" t="s">
-        <v>2</v>
+        <v>197</v>
       </c>
       <c r="D73" t="s">
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F73" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G73" t="s">
         <v>2</v>
@@ -4904,13 +4868,13 @@
         <v>6</v>
       </c>
       <c r="I73" s="2">
-        <v>46146</v>
+        <v>46057</v>
       </c>
       <c r="J73" t="s">
         <v>7</v>
       </c>
       <c r="K73" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="L73" t="s">
         <v>7</v>
@@ -4922,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="2">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="P73" t="s">
         <v>7</v>
@@ -4936,37 +4900,37 @@
     </row>
     <row r="74" spans="1:18">
       <c r="A74" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C74" t="s">
         <v>2</v>
       </c>
       <c r="D74" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E74" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F74" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G74" t="s">
         <v>2</v>
       </c>
       <c r="H74" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I74" s="2">
-        <v>46127</v>
+        <v>46057</v>
       </c>
       <c r="J74" t="s">
         <v>7</v>
       </c>
       <c r="K74" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="L74" t="s">
         <v>7</v>
@@ -4978,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="2">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="P74" t="s">
         <v>7</v>
@@ -4992,37 +4956,37 @@
     </row>
     <row r="75" spans="1:18">
       <c r="A75" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G75" t="s">
         <v>2</v>
       </c>
       <c r="H75" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I75" s="2">
-        <v>46132</v>
+        <v>46062</v>
       </c>
       <c r="J75" t="s">
         <v>7</v>
       </c>
       <c r="K75" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L75" t="s">
         <v>7</v>
@@ -5034,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="2">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="P75" t="s">
         <v>7</v>
@@ -5048,22 +5012,22 @@
     </row>
     <row r="76" spans="1:18">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B76" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C76" t="s">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="D76" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E76" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F76" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G76" t="s">
         <v>2</v>
@@ -5072,13 +5036,13 @@
         <v>6</v>
       </c>
       <c r="I76" s="2">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="J76" t="s">
         <v>7</v>
       </c>
       <c r="K76" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L76" t="s">
         <v>7</v>
@@ -5104,37 +5068,37 @@
     </row>
     <row r="77" spans="1:18">
       <c r="A77" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D77" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E77" t="s">
         <v>53</v>
       </c>
       <c r="F77" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G77" t="s">
         <v>2</v>
       </c>
       <c r="H77" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I77" s="2">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="J77" t="s">
         <v>7</v>
       </c>
       <c r="K77" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L77" t="s">
         <v>7</v>
@@ -5155,230 +5119,6 @@
         <v>7</v>
       </c>
       <c r="R77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18">
-      <c r="A78" t="s">
-        <v>206</v>
-      </c>
-      <c r="B78" t="s">
-        <v>211</v>
-      </c>
-      <c r="C78" t="s">
-        <v>2</v>
-      </c>
-      <c r="D78" t="s">
-        <v>3</v>
-      </c>
-      <c r="E78" t="s">
-        <v>57</v>
-      </c>
-      <c r="F78" t="s">
-        <v>212</v>
-      </c>
-      <c r="G78" t="s">
-        <v>2</v>
-      </c>
-      <c r="H78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I78" s="2">
-        <v>46057</v>
-      </c>
-      <c r="J78" t="s">
-        <v>7</v>
-      </c>
-      <c r="K78" t="s">
-        <v>59</v>
-      </c>
-      <c r="L78" t="s">
-        <v>7</v>
-      </c>
-      <c r="M78" s="3">
-        <v>1</v>
-      </c>
-      <c r="N78" s="3">
-        <v>0</v>
-      </c>
-      <c r="O78" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P78" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>7</v>
-      </c>
-      <c r="R78" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18">
-      <c r="A79" t="s">
-        <v>206</v>
-      </c>
-      <c r="B79" t="s">
-        <v>207</v>
-      </c>
-      <c r="C79" t="s">
-        <v>213</v>
-      </c>
-      <c r="D79" t="s">
-        <v>3</v>
-      </c>
-      <c r="E79" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" t="s">
-        <v>214</v>
-      </c>
-      <c r="G79" t="s">
-        <v>2</v>
-      </c>
-      <c r="H79" t="s">
-        <v>6</v>
-      </c>
-      <c r="I79" s="2">
-        <v>46062</v>
-      </c>
-      <c r="J79" t="s">
-        <v>7</v>
-      </c>
-      <c r="K79" t="s">
-        <v>62</v>
-      </c>
-      <c r="L79" t="s">
-        <v>7</v>
-      </c>
-      <c r="M79" s="3">
-        <v>1</v>
-      </c>
-      <c r="N79" s="3">
-        <v>0</v>
-      </c>
-      <c r="O79" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P79" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>7</v>
-      </c>
-      <c r="R79" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18">
-      <c r="A80" t="s">
-        <v>206</v>
-      </c>
-      <c r="B80" t="s">
-        <v>207</v>
-      </c>
-      <c r="C80" t="s">
-        <v>215</v>
-      </c>
-      <c r="D80" t="s">
-        <v>64</v>
-      </c>
-      <c r="E80" t="s">
-        <v>30</v>
-      </c>
-      <c r="F80" t="s">
-        <v>216</v>
-      </c>
-      <c r="G80" t="s">
-        <v>2</v>
-      </c>
-      <c r="H80" t="s">
-        <v>6</v>
-      </c>
-      <c r="I80" s="2">
-        <v>46044</v>
-      </c>
-      <c r="J80" t="s">
-        <v>7</v>
-      </c>
-      <c r="K80" t="s">
-        <v>66</v>
-      </c>
-      <c r="L80" t="s">
-        <v>7</v>
-      </c>
-      <c r="M80" s="3">
-        <v>1</v>
-      </c>
-      <c r="N80" s="3">
-        <v>0</v>
-      </c>
-      <c r="O80" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P80" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>7</v>
-      </c>
-      <c r="R80" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18">
-      <c r="A81" t="s">
-        <v>206</v>
-      </c>
-      <c r="B81" t="s">
-        <v>211</v>
-      </c>
-      <c r="C81" t="s">
-        <v>209</v>
-      </c>
-      <c r="D81" t="s">
-        <v>64</v>
-      </c>
-      <c r="E81" t="s">
-        <v>53</v>
-      </c>
-      <c r="F81" t="s">
-        <v>217</v>
-      </c>
-      <c r="G81" t="s">
-        <v>2</v>
-      </c>
-      <c r="H81" t="s">
-        <v>19</v>
-      </c>
-      <c r="I81" s="2">
-        <v>46050</v>
-      </c>
-      <c r="J81" t="s">
-        <v>7</v>
-      </c>
-      <c r="K81" t="s">
-        <v>69</v>
-      </c>
-      <c r="L81" t="s">
-        <v>7</v>
-      </c>
-      <c r="M81" s="3">
-        <v>1</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P81" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>7</v>
-      </c>
-      <c r="R81" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="224">
-  <si>
-    <t>200006191</t>
-  </si>
-  <si>
-    <t>1400089839</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="174">
+  <si>
+    <t>200006254</t>
+  </si>
+  <si>
+    <t>1400090379</t>
   </si>
   <si>
     <t>10</t>
@@ -28,31 +28,175 @@
     <t>0010</t>
   </si>
   <si>
-    <t>1400093291</t>
+    <t>1400093676</t>
+  </si>
+  <si>
+    <t>2E0001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>C軸結合面鏟花</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>1400090339</t>
+  </si>
+  <si>
+    <t>0030</t>
+  </si>
+  <si>
+    <t>1400093677</t>
   </si>
   <si>
     <t>2C0018</t>
   </si>
   <si>
-    <t/>
+    <t>AUC軸頭噴漆</t>
+  </si>
+  <si>
+    <t>1400090344</t>
+  </si>
+  <si>
+    <t>0090</t>
+  </si>
+  <si>
+    <t>1400093850</t>
+  </si>
+  <si>
+    <t>AU介面座噴漆</t>
+  </si>
+  <si>
+    <t>1400090388</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>1400093851</t>
+  </si>
+  <si>
+    <t>Ｃ軸鏟花</t>
+  </si>
+  <si>
+    <t>1400090345</t>
+  </si>
+  <si>
+    <t>0160</t>
+  </si>
+  <si>
+    <t>1400093852</t>
+  </si>
+  <si>
+    <t>萬向頭附配件噴漆</t>
+  </si>
+  <si>
+    <t>1400090346</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>1400093853</t>
+  </si>
+  <si>
+    <t>AUA軸頭噴漆</t>
+  </si>
+  <si>
+    <t>1400090389</t>
+  </si>
+  <si>
+    <t>1400093854</t>
+  </si>
+  <si>
+    <t>A軸鏟花</t>
+  </si>
+  <si>
+    <t>200006326</t>
+  </si>
+  <si>
+    <t>1400091195</t>
+  </si>
+  <si>
+    <t>1400094673</t>
+  </si>
+  <si>
+    <t>M90頭噴漆</t>
+  </si>
+  <si>
+    <t>1400091294</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>1400094674</t>
+  </si>
+  <si>
+    <t>M90頭鏟花</t>
+  </si>
+  <si>
+    <t>200006370</t>
+  </si>
+  <si>
+    <t>1400091823</t>
+  </si>
+  <si>
+    <t>1400095323</t>
+  </si>
+  <si>
+    <t>PBM機頭噴漆</t>
+  </si>
+  <si>
+    <t>1400091824</t>
+  </si>
+  <si>
+    <t>1400095324</t>
+  </si>
+  <si>
+    <t>PBM進給座噴漆</t>
+  </si>
+  <si>
+    <t>1400091844</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>1400095325</t>
+  </si>
+  <si>
+    <t>齒輪箱進給座鏟花</t>
+  </si>
+  <si>
+    <t>200006388</t>
+  </si>
+  <si>
+    <t>1400092027</t>
+  </si>
+  <si>
+    <t>1400095483</t>
   </si>
   <si>
     <t>A90頭噴漆</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>1400091619</t>
+    <t>1400093569</t>
   </si>
   <si>
     <t>0110</t>
   </si>
   <si>
-    <t>1400093293</t>
+    <t>1400095485</t>
   </si>
   <si>
     <t>1G0054</t>
@@ -61,339 +205,27 @@
     <t>軸承箱墊片研磨</t>
   </si>
   <si>
-    <t>1400089843</t>
+    <t>1400092068</t>
   </si>
   <si>
     <t>0150</t>
   </si>
   <si>
-    <t>1400093294</t>
-  </si>
-  <si>
-    <t>2E0001</t>
+    <t>1400095486</t>
   </si>
   <si>
     <t>A90頭鏟花</t>
   </si>
   <si>
-    <t>1400089840</t>
-  </si>
-  <si>
-    <t>0160</t>
-  </si>
-  <si>
-    <t>1400093295</t>
+    <t>1400092028</t>
+  </si>
+  <si>
+    <t>1400095487</t>
   </si>
   <si>
     <t>接頭座噴漆</t>
   </si>
   <si>
-    <t>200006232</t>
-  </si>
-  <si>
-    <t>1400090217</t>
-  </si>
-  <si>
-    <t>1400093662</t>
-  </si>
-  <si>
-    <t>SUA軸頭噴漆</t>
-  </si>
-  <si>
-    <t>1400090218</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>1400093663</t>
-  </si>
-  <si>
-    <t>SUC軸頭噴漆</t>
-  </si>
-  <si>
-    <t>1400090247</t>
-  </si>
-  <si>
-    <t>1400093664</t>
-  </si>
-  <si>
-    <t>SU頭鏟花</t>
-  </si>
-  <si>
-    <t>1400090219</t>
-  </si>
-  <si>
-    <t>0180</t>
-  </si>
-  <si>
-    <t>1400093665</t>
-  </si>
-  <si>
-    <t>出貨固定座噴漆</t>
-  </si>
-  <si>
-    <t>200006241</t>
-  </si>
-  <si>
-    <t>1400090251</t>
-  </si>
-  <si>
-    <t>1400093683</t>
-  </si>
-  <si>
-    <t>C軸結合面鏟花</t>
-  </si>
-  <si>
-    <t>1400090222</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>1400093684</t>
-  </si>
-  <si>
-    <t>AUC軸頭噴漆</t>
-  </si>
-  <si>
-    <t>1400092246</t>
-  </si>
-  <si>
-    <t>0080</t>
-  </si>
-  <si>
-    <t>1400093686</t>
-  </si>
-  <si>
-    <t>角度頭墊片研磨</t>
-  </si>
-  <si>
-    <t>1400090223</t>
-  </si>
-  <si>
-    <t>0090</t>
-  </si>
-  <si>
-    <t>1400093687</t>
-  </si>
-  <si>
-    <t>AU介面座噴漆</t>
-  </si>
-  <si>
-    <t>1400090252</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>1400093688</t>
-  </si>
-  <si>
-    <t>Ｃ軸鏟花</t>
-  </si>
-  <si>
-    <t>1400090224</t>
-  </si>
-  <si>
-    <t>1400093689</t>
-  </si>
-  <si>
-    <t>萬向頭附配件噴漆</t>
-  </si>
-  <si>
-    <t>1400090226</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1400093700</t>
-  </si>
-  <si>
-    <t>AUA軸頭噴漆</t>
-  </si>
-  <si>
-    <t>1400090253</t>
-  </si>
-  <si>
-    <t>1400093701</t>
-  </si>
-  <si>
-    <t>A軸鏟花</t>
-  </si>
-  <si>
-    <t>200006254</t>
-  </si>
-  <si>
-    <t>1400090379</t>
-  </si>
-  <si>
-    <t>1400093676</t>
-  </si>
-  <si>
-    <t>1400090339</t>
-  </si>
-  <si>
-    <t>1400093677</t>
-  </si>
-  <si>
-    <t>1400090344</t>
-  </si>
-  <si>
-    <t>1400093850</t>
-  </si>
-  <si>
-    <t>1400090388</t>
-  </si>
-  <si>
-    <t>1400093851</t>
-  </si>
-  <si>
-    <t>1400090345</t>
-  </si>
-  <si>
-    <t>1400093852</t>
-  </si>
-  <si>
-    <t>1400090346</t>
-  </si>
-  <si>
-    <t>1400093853</t>
-  </si>
-  <si>
-    <t>1400090389</t>
-  </si>
-  <si>
-    <t>1400093854</t>
-  </si>
-  <si>
-    <t>200006326</t>
-  </si>
-  <si>
-    <t>1400091195</t>
-  </si>
-  <si>
-    <t>1400094673</t>
-  </si>
-  <si>
-    <t>M90頭噴漆</t>
-  </si>
-  <si>
-    <t>1400091294</t>
-  </si>
-  <si>
-    <t>1400094674</t>
-  </si>
-  <si>
-    <t>M90頭鏟花</t>
-  </si>
-  <si>
-    <t>200006349</t>
-  </si>
-  <si>
-    <t>1400091572</t>
-  </si>
-  <si>
-    <t>1400095028</t>
-  </si>
-  <si>
-    <t>1400091535</t>
-  </si>
-  <si>
-    <t>1400095029</t>
-  </si>
-  <si>
-    <t>1400092803</t>
-  </si>
-  <si>
-    <t>1400095051</t>
-  </si>
-  <si>
-    <t>1400091536</t>
-  </si>
-  <si>
-    <t>1400095052</t>
-  </si>
-  <si>
-    <t>1400091574</t>
-  </si>
-  <si>
-    <t>1400095053</t>
-  </si>
-  <si>
-    <t>1400091537</t>
-  </si>
-  <si>
-    <t>1400095054</t>
-  </si>
-  <si>
-    <t>1400091538</t>
-  </si>
-  <si>
-    <t>1400095055</t>
-  </si>
-  <si>
-    <t>1400091575</t>
-  </si>
-  <si>
-    <t>1400095056</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>1400091823</t>
-  </si>
-  <si>
-    <t>1400095323</t>
-  </si>
-  <si>
-    <t>PBM機頭噴漆</t>
-  </si>
-  <si>
-    <t>1400091824</t>
-  </si>
-  <si>
-    <t>1400095324</t>
-  </si>
-  <si>
-    <t>PBM進給座噴漆</t>
-  </si>
-  <si>
-    <t>1400091844</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>1400095325</t>
-  </si>
-  <si>
-    <t>齒輪箱進給座鏟花</t>
-  </si>
-  <si>
-    <t>200006388</t>
-  </si>
-  <si>
-    <t>1400092027</t>
-  </si>
-  <si>
-    <t>1400095483</t>
-  </si>
-  <si>
-    <t>1400092068</t>
-  </si>
-  <si>
-    <t>1400095486</t>
-  </si>
-  <si>
-    <t>1400092028</t>
-  </si>
-  <si>
-    <t>1400095487</t>
-  </si>
-  <si>
     <t>200006389</t>
   </si>
   <si>
@@ -403,6 +235,12 @@
     <t>1400095488</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1400095560</t>
+  </si>
+  <si>
     <t>1400092069</t>
   </si>
   <si>
@@ -415,184 +253,196 @@
     <t>1400095562</t>
   </si>
   <si>
-    <t>200006425</t>
-  </si>
-  <si>
-    <t>1400092690</t>
-  </si>
-  <si>
-    <t>1400096202</t>
-  </si>
-  <si>
-    <t>1400092760</t>
-  </si>
-  <si>
-    <t>1400096203</t>
-  </si>
-  <si>
-    <t>1400092761</t>
-  </si>
-  <si>
-    <t>1400096206</t>
-  </si>
-  <si>
-    <t>1400092691</t>
-  </si>
-  <si>
-    <t>1400096207</t>
-  </si>
-  <si>
-    <t>1400092762</t>
-  </si>
-  <si>
-    <t>1400096208</t>
-  </si>
-  <si>
-    <t>1400092763</t>
-  </si>
-  <si>
-    <t>1400096209</t>
-  </si>
-  <si>
-    <t>1400092692</t>
-  </si>
-  <si>
-    <t>1400096210</t>
-  </si>
-  <si>
-    <t>200006426</t>
-  </si>
-  <si>
-    <t>1400092785</t>
-  </si>
-  <si>
-    <t>1400096211</t>
-  </si>
-  <si>
-    <t>1400092650</t>
-  </si>
-  <si>
-    <t>1400096212</t>
-  </si>
-  <si>
-    <t>1400092651</t>
-  </si>
-  <si>
-    <t>1400096215</t>
-  </si>
-  <si>
-    <t>1400092786</t>
-  </si>
-  <si>
-    <t>1400096216</t>
-  </si>
-  <si>
-    <t>1400092652</t>
-  </si>
-  <si>
-    <t>1400096217</t>
-  </si>
-  <si>
-    <t>1400092653</t>
-  </si>
-  <si>
-    <t>1400096218</t>
-  </si>
-  <si>
-    <t>1400092787</t>
-  </si>
-  <si>
-    <t>1400096219</t>
-  </si>
-  <si>
-    <t>200006427</t>
-  </si>
-  <si>
-    <t>1400092693</t>
-  </si>
-  <si>
-    <t>1400096220</t>
-  </si>
-  <si>
-    <t>1400092654</t>
-  </si>
-  <si>
-    <t>1400096221</t>
-  </si>
-  <si>
-    <t>1400092655</t>
-  </si>
-  <si>
-    <t>1400096224</t>
-  </si>
-  <si>
-    <t>1400092694</t>
-  </si>
-  <si>
-    <t>1400096225</t>
-  </si>
-  <si>
-    <t>1400092656</t>
-  </si>
-  <si>
-    <t>1400096226</t>
-  </si>
-  <si>
-    <t>1400092657</t>
-  </si>
-  <si>
-    <t>1400096227</t>
-  </si>
-  <si>
-    <t>1400092695</t>
-  </si>
-  <si>
-    <t>1400096228</t>
-  </si>
-  <si>
-    <t>200006451</t>
-  </si>
-  <si>
-    <t>1400093254</t>
-  </si>
-  <si>
-    <t>1400096769</t>
-  </si>
-  <si>
-    <t>1400093151</t>
-  </si>
-  <si>
-    <t>1400096790</t>
-  </si>
-  <si>
-    <t>1400093152</t>
-  </si>
-  <si>
-    <t>1400096793</t>
-  </si>
-  <si>
-    <t>1400093255</t>
-  </si>
-  <si>
-    <t>1400096794</t>
-  </si>
-  <si>
-    <t>1400093153</t>
-  </si>
-  <si>
-    <t>1400096795</t>
-  </si>
-  <si>
-    <t>1400093154</t>
-  </si>
-  <si>
-    <t>1400096796</t>
-  </si>
-  <si>
-    <t>1400093256</t>
-  </si>
-  <si>
-    <t>1400096797</t>
+    <t>200006466</t>
+  </si>
+  <si>
+    <t>1400093579</t>
+  </si>
+  <si>
+    <t>1400097135</t>
+  </si>
+  <si>
+    <t>1400093580</t>
+  </si>
+  <si>
+    <t>1400097136</t>
+  </si>
+  <si>
+    <t>1400093581</t>
+  </si>
+  <si>
+    <t>1400097139</t>
+  </si>
+  <si>
+    <t>1400093582</t>
+  </si>
+  <si>
+    <t>1400097140</t>
+  </si>
+  <si>
+    <t>1400093583</t>
+  </si>
+  <si>
+    <t>1400097141</t>
+  </si>
+  <si>
+    <t>1400093584</t>
+  </si>
+  <si>
+    <t>1400097142</t>
+  </si>
+  <si>
+    <t>1400093585</t>
+  </si>
+  <si>
+    <t>1400097143</t>
+  </si>
+  <si>
+    <t>200006467</t>
+  </si>
+  <si>
+    <t>1400093586</t>
+  </si>
+  <si>
+    <t>1400097144</t>
+  </si>
+  <si>
+    <t>AE頭噴漆</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>1400093587</t>
+  </si>
+  <si>
+    <t>1400097411</t>
+  </si>
+  <si>
+    <t>1400093588</t>
+  </si>
+  <si>
+    <t>1400097412</t>
+  </si>
+  <si>
+    <t>1400093589</t>
+  </si>
+  <si>
+    <t>1400097415</t>
+  </si>
+  <si>
+    <t>1400093590</t>
+  </si>
+  <si>
+    <t>1400097416</t>
+  </si>
+  <si>
+    <t>1400093591</t>
+  </si>
+  <si>
+    <t>1400097417</t>
+  </si>
+  <si>
+    <t>1400093592</t>
+  </si>
+  <si>
+    <t>1400097418</t>
+  </si>
+  <si>
+    <t>1400093593</t>
+  </si>
+  <si>
+    <t>1400097419</t>
+  </si>
+  <si>
+    <t>200006489</t>
+  </si>
+  <si>
+    <t>1400093594</t>
+  </si>
+  <si>
+    <t>1400097430</t>
+  </si>
+  <si>
+    <t>1400093595</t>
+  </si>
+  <si>
+    <t>1400097431</t>
+  </si>
+  <si>
+    <t>1400093596</t>
+  </si>
+  <si>
+    <t>1400097434</t>
+  </si>
+  <si>
+    <t>1400093597</t>
+  </si>
+  <si>
+    <t>1400097435</t>
+  </si>
+  <si>
+    <t>1400093598</t>
+  </si>
+  <si>
+    <t>1400097436</t>
+  </si>
+  <si>
+    <t>1400093599</t>
+  </si>
+  <si>
+    <t>1400097437</t>
+  </si>
+  <si>
+    <t>1400093600</t>
+  </si>
+  <si>
+    <t>1400097438</t>
+  </si>
+  <si>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>1400093601</t>
+  </si>
+  <si>
+    <t>1400097439</t>
+  </si>
+  <si>
+    <t>1400093602</t>
+  </si>
+  <si>
+    <t>1400097440</t>
+  </si>
+  <si>
+    <t>1400093603</t>
+  </si>
+  <si>
+    <t>1400097443</t>
+  </si>
+  <si>
+    <t>1400093604</t>
+  </si>
+  <si>
+    <t>1400097444</t>
+  </si>
+  <si>
+    <t>1400093605</t>
+  </si>
+  <si>
+    <t>1400097445</t>
+  </si>
+  <si>
+    <t>1400093606</t>
+  </si>
+  <si>
+    <t>1400097446</t>
+  </si>
+  <si>
+    <t>1400093607</t>
+  </si>
+  <si>
+    <t>1400097447</t>
   </si>
   <si>
     <t>630000329</t>
@@ -604,7 +454,7 @@
     <t>1400096493</t>
   </si>
   <si>
-    <t>20</t>
+    <t>L</t>
   </si>
   <si>
     <t>1400096496</t>
@@ -787,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -812,58 +662,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -892,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="I2" s="2">
-        <v>45993</v>
+        <v>45981</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
@@ -948,7 +798,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="2">
-        <v>46007</v>
+        <v>45982</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
@@ -966,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="2">
-        <v>46035</v>
+        <v>46009</v>
       </c>
       <c r="P3" t="s">
         <v>10</v>
@@ -1001,16 +851,16 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2">
+        <v>45994</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
         <v>19</v>
-      </c>
-      <c r="I4" s="2">
-        <v>46009</v>
-      </c>
-      <c r="J4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
       </c>
       <c r="L4" t="s">
         <v>9</v>
@@ -1022,13 +872,13 @@
         <v>1</v>
       </c>
       <c r="O4" s="2">
-        <v>45911</v>
+        <v>46009</v>
       </c>
       <c r="P4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R4" s="3">
         <v>1</v>
@@ -1039,19 +889,19 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>2</v>
@@ -1060,13 +910,13 @@
         <v>6</v>
       </c>
       <c r="I5" s="2">
-        <v>46009</v>
+        <v>45994</v>
       </c>
       <c r="J5" t="s">
         <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
@@ -1092,37 +942,37 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2">
+        <v>45999</v>
+      </c>
+      <c r="J6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="2">
-        <v>46009</v>
-      </c>
-      <c r="J6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
       </c>
       <c r="L6" t="s">
         <v>9</v>
@@ -1148,16 +998,16 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -1169,10 +1019,10 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2">
-        <v>46010</v>
+        <v>45981</v>
       </c>
       <c r="J7" t="s">
         <v>7</v>
@@ -1204,7 +1054,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1213,10 +1063,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -1225,10 +1075,10 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I8" s="2">
-        <v>46021</v>
+        <v>45986</v>
       </c>
       <c r="J8" t="s">
         <v>7</v>
@@ -1246,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="2">
-        <v>46035</v>
+        <v>46009</v>
       </c>
       <c r="P8" t="s">
         <v>10</v>
@@ -1260,10 +1110,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
@@ -1272,7 +1122,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
         <v>38</v>
@@ -1281,10 +1131,10 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I9" s="2">
-        <v>46021</v>
+        <v>46094</v>
       </c>
       <c r="J9" t="s">
         <v>7</v>
@@ -1293,42 +1143,42 @@
         <v>39</v>
       </c>
       <c r="L9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M9" s="3">
         <v>1</v>
       </c>
       <c r="N9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2">
-        <v>46009</v>
+        <v>45979</v>
       </c>
       <c r="P9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
       </c>
       <c r="F10" t="s">
         <v>42</v>
@@ -1337,10 +1187,10 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I10" s="2">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="J10" t="s">
         <v>7</v>
@@ -1349,33 +1199,33 @@
         <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M10" s="3">
         <v>1</v>
       </c>
       <c r="N10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2">
-        <v>46035</v>
+        <v>45979</v>
       </c>
       <c r="P10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
@@ -1384,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F11" t="s">
         <v>46</v>
@@ -1393,10 +1243,10 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2">
-        <v>46045</v>
+        <v>46065</v>
       </c>
       <c r="J11" t="s">
         <v>7</v>
@@ -1405,16 +1255,16 @@
         <v>47</v>
       </c>
       <c r="L11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" s="3">
         <v>1</v>
       </c>
       <c r="N11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2">
-        <v>45943</v>
+        <v>45995</v>
       </c>
       <c r="P11" t="s">
         <v>7</v>
@@ -1423,12 +1273,12 @@
         <v>7</v>
       </c>
       <c r="R11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
         <v>48</v>
@@ -1440,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
         <v>49</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>2</v>
@@ -1452,13 +1302,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="2">
-        <v>46027</v>
+        <v>46065</v>
       </c>
       <c r="J12" t="s">
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" t="s">
         <v>9</v>
@@ -1470,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="2">
-        <v>46008</v>
+        <v>45995</v>
       </c>
       <c r="P12" t="s">
         <v>7</v>
@@ -1484,22 +1334,22 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
         <v>52</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>53</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
       </c>
       <c r="G13" t="s">
         <v>2</v>
@@ -1508,13 +1358,13 @@
         <v>6</v>
       </c>
       <c r="I13" s="2">
-        <v>46057</v>
+        <v>46097</v>
       </c>
       <c r="J13" t="s">
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L13" t="s">
         <v>7</v>
@@ -1526,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="2">
-        <v>45943</v>
+        <v>45995</v>
       </c>
       <c r="P13" t="s">
         <v>7</v>
@@ -1540,7 +1390,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>56</v>
@@ -1552,25 +1402,25 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
         <v>57</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="2">
+        <v>46014</v>
+      </c>
+      <c r="J14" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" t="s">
         <v>58</v>
-      </c>
-      <c r="G14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="2">
-        <v>46057</v>
-      </c>
-      <c r="J14" t="s">
-        <v>7</v>
-      </c>
-      <c r="K14" t="s">
-        <v>59</v>
       </c>
       <c r="L14" t="s">
         <v>9</v>
@@ -1596,19 +1446,19 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
         <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
       </c>
       <c r="F15" t="s">
         <v>61</v>
@@ -1617,28 +1467,28 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="I15" s="2">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="J15" t="s">
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M15" s="3">
         <v>1</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2">
-        <v>45943</v>
+        <v>46064</v>
       </c>
       <c r="P15" t="s">
         <v>7</v>
@@ -1652,22 +1502,22 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
         <v>2</v>
@@ -1676,25 +1526,25 @@
         <v>6</v>
       </c>
       <c r="I16" s="2">
-        <v>46044</v>
+        <v>46029</v>
       </c>
       <c r="J16" t="s">
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M16" s="3">
         <v>1</v>
       </c>
       <c r="N16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2">
-        <v>45943</v>
+        <v>46002</v>
       </c>
       <c r="P16" t="s">
         <v>7</v>
@@ -1703,42 +1553,42 @@
         <v>7</v>
       </c>
       <c r="R16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="J17" t="s">
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" t="s">
         <v>9</v>
@@ -1764,10 +1614,10 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
         <v>2</v>
@@ -1779,22 +1629,22 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2">
-        <v>45981</v>
+        <v>46007</v>
       </c>
       <c r="J18" t="s">
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="L18" t="s">
         <v>9</v>
@@ -1806,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="2">
-        <v>46009</v>
+        <v>46035</v>
       </c>
       <c r="P18" t="s">
         <v>10</v>
@@ -1820,37 +1670,37 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2">
-        <v>45982</v>
+        <v>46059</v>
       </c>
       <c r="J19" t="s">
         <v>7</v>
       </c>
       <c r="K19" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="L19" t="s">
         <v>9</v>
@@ -1862,24 +1712,24 @@
         <v>1</v>
       </c>
       <c r="O19" s="2">
-        <v>46009</v>
+        <v>46064</v>
       </c>
       <c r="P19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
         <v>2</v>
@@ -1888,10 +1738,10 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
         <v>2</v>
@@ -1900,13 +1750,13 @@
         <v>6</v>
       </c>
       <c r="I20" s="2">
-        <v>45994</v>
+        <v>46024</v>
       </c>
       <c r="J20" t="s">
         <v>7</v>
       </c>
       <c r="K20" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="L20" t="s">
         <v>9</v>
@@ -1918,13 +1768,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="2">
-        <v>46009</v>
+        <v>46055</v>
       </c>
       <c r="P20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R20" s="3">
         <v>1</v>
@@ -1932,37 +1782,37 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="2">
+        <v>46024</v>
+      </c>
+      <c r="J21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K21" t="s">
         <v>70</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="2">
-        <v>45994</v>
-      </c>
-      <c r="J21" t="s">
-        <v>7</v>
-      </c>
-      <c r="K21" t="s">
-        <v>59</v>
       </c>
       <c r="L21" t="s">
         <v>9</v>
@@ -1974,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="2">
-        <v>46009</v>
+        <v>46035</v>
       </c>
       <c r="P21" t="s">
         <v>10</v>
@@ -1988,10 +1838,10 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
@@ -2000,10 +1850,10 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s">
         <v>2</v>
@@ -2012,154 +1862,154 @@
         <v>6</v>
       </c>
       <c r="I22" s="2">
-        <v>45999</v>
+        <v>46065</v>
       </c>
       <c r="J22" t="s">
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="L22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M22" s="3">
         <v>1</v>
       </c>
       <c r="N22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2">
-        <v>46009</v>
+        <v>46065</v>
       </c>
       <c r="P22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2">
-        <v>45981</v>
+        <v>46066</v>
       </c>
       <c r="J23" t="s">
         <v>7</v>
       </c>
       <c r="K23" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M23" s="3">
         <v>1</v>
       </c>
       <c r="N23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>46009</v>
+        <v>46065</v>
       </c>
       <c r="P23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
       </c>
       <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="2">
+        <v>46083</v>
+      </c>
+      <c r="J24" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="2">
-        <v>45986</v>
-      </c>
-      <c r="J24" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" t="s">
-        <v>69</v>
-      </c>
       <c r="L24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M24" s="3">
         <v>1</v>
       </c>
       <c r="N24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>46009</v>
+        <v>46065</v>
       </c>
       <c r="P24" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
         <v>2</v>
@@ -2168,10 +2018,10 @@
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
@@ -2180,13 +2030,13 @@
         <v>6</v>
       </c>
       <c r="I25" s="2">
-        <v>46094</v>
+        <v>46083</v>
       </c>
       <c r="J25" t="s">
         <v>7</v>
       </c>
       <c r="K25" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="L25" t="s">
         <v>7</v>
@@ -2198,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="2">
-        <v>45979</v>
+        <v>46065</v>
       </c>
       <c r="P25" t="s">
         <v>7</v>
@@ -2212,7 +2062,7 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -2224,7 +2074,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
         <v>90</v>
@@ -2233,16 +2083,16 @@
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="J26" t="s">
         <v>7</v>
       </c>
       <c r="K26" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="L26" t="s">
         <v>7</v>
@@ -2254,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="2">
-        <v>45979</v>
+        <v>46065</v>
       </c>
       <c r="P26" t="s">
         <v>7</v>
@@ -2268,49 +2118,49 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
         <v>92</v>
       </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" t="s">
-        <v>94</v>
-      </c>
       <c r="G27" t="s">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2">
-        <v>46014</v>
+        <v>46065</v>
       </c>
       <c r="J27" t="s">
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M27" s="3">
         <v>1</v>
       </c>
       <c r="N27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P27" t="s">
         <v>7</v>
@@ -2319,27 +2169,27 @@
         <v>7</v>
       </c>
       <c r="R27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
@@ -2348,25 +2198,25 @@
         <v>6</v>
       </c>
       <c r="I28" s="2">
-        <v>46015</v>
+        <v>46077</v>
       </c>
       <c r="J28" t="s">
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="L28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M28" s="3">
         <v>1</v>
       </c>
       <c r="N28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P28" t="s">
         <v>7</v>
@@ -2375,27 +2225,27 @@
         <v>7</v>
       </c>
       <c r="R28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
         <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F29" t="s">
-        <v>98</v>
       </c>
       <c r="G29" t="s">
         <v>2</v>
@@ -2404,13 +2254,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="2">
-        <v>46037</v>
+        <v>46077</v>
       </c>
       <c r="J29" t="s">
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="L29" t="s">
         <v>7</v>
@@ -2422,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="2">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="P29" t="s">
         <v>7</v>
@@ -2436,10 +2286,10 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
         <v>2</v>
@@ -2448,10 +2298,10 @@
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G30" t="s">
         <v>2</v>
@@ -2460,25 +2310,25 @@
         <v>6</v>
       </c>
       <c r="I30" s="2">
-        <v>46027</v>
+        <v>46094</v>
       </c>
       <c r="J30" t="s">
         <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="L30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M30" s="3">
         <v>1</v>
       </c>
       <c r="N30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P30" t="s">
         <v>7</v>
@@ -2487,15 +2337,15 @@
         <v>7</v>
       </c>
       <c r="R30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
         <v>2</v>
@@ -2504,37 +2354,37 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G31" t="s">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I31" s="2">
-        <v>46027</v>
+        <v>46097</v>
       </c>
       <c r="J31" t="s">
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M31" s="3">
         <v>1</v>
       </c>
       <c r="N31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P31" t="s">
         <v>7</v>
@@ -2543,15 +2393,15 @@
         <v>7</v>
       </c>
       <c r="R31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
         <v>2</v>
@@ -2560,37 +2410,37 @@
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G32" t="s">
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I32" s="2">
-        <v>46030</v>
+        <v>46105</v>
       </c>
       <c r="J32" t="s">
         <v>7</v>
       </c>
       <c r="K32" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="L32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M32" s="3">
         <v>1</v>
       </c>
       <c r="N32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P32" t="s">
         <v>7</v>
@@ -2599,27 +2449,27 @@
         <v>7</v>
       </c>
       <c r="R32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G33" t="s">
         <v>2</v>
@@ -2628,25 +2478,25 @@
         <v>6</v>
       </c>
       <c r="I33" s="2">
-        <v>46014</v>
+        <v>46105</v>
       </c>
       <c r="J33" t="s">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="L33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M33" s="3">
         <v>1</v>
       </c>
       <c r="N33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P33" t="s">
         <v>7</v>
@@ -2655,54 +2505,54 @@
         <v>7</v>
       </c>
       <c r="R33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I34" s="2">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="J34" t="s">
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="L34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M34" s="3">
         <v>1</v>
       </c>
       <c r="N34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>45987</v>
+        <v>46065</v>
       </c>
       <c r="P34" t="s">
         <v>7</v>
@@ -2711,12 +2561,12 @@
         <v>7</v>
       </c>
       <c r="R34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
         <v>110</v>
@@ -2725,10 +2575,10 @@
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>111</v>
@@ -2737,28 +2587,28 @@
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2">
+        <v>46097</v>
+      </c>
+      <c r="J35" t="s">
+        <v>7</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="3">
+        <v>1</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2">
         <v>46065</v>
-      </c>
-      <c r="J35" t="s">
-        <v>7</v>
-      </c>
-      <c r="K35" t="s">
-        <v>112</v>
-      </c>
-      <c r="L35" t="s">
-        <v>7</v>
-      </c>
-      <c r="M35" s="3">
-        <v>1</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>45995</v>
       </c>
       <c r="P35" t="s">
         <v>7</v>
@@ -2772,22 +2622,22 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
         <v>113</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" t="s">
-        <v>114</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
@@ -2796,25 +2646,25 @@
         <v>6</v>
       </c>
       <c r="I36" s="2">
+        <v>46100</v>
+      </c>
+      <c r="J36" t="s">
+        <v>7</v>
+      </c>
+      <c r="K36" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" t="s">
+        <v>7</v>
+      </c>
+      <c r="M36" s="3">
+        <v>1</v>
+      </c>
+      <c r="N36" s="3">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2">
         <v>46065</v>
-      </c>
-      <c r="J36" t="s">
-        <v>7</v>
-      </c>
-      <c r="K36" t="s">
-        <v>115</v>
-      </c>
-      <c r="L36" t="s">
-        <v>7</v>
-      </c>
-      <c r="M36" s="3">
-        <v>1</v>
-      </c>
-      <c r="N36" s="3">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2">
-        <v>45995</v>
       </c>
       <c r="P36" t="s">
         <v>7</v>
@@ -2828,37 +2678,37 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" t="s">
         <v>116</v>
       </c>
-      <c r="C37" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" t="s">
-        <v>117</v>
-      </c>
-      <c r="F37" t="s">
-        <v>118</v>
-      </c>
       <c r="G37" t="s">
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2">
-        <v>46097</v>
+        <v>46114</v>
       </c>
       <c r="J37" t="s">
         <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="L37" t="s">
         <v>7</v>
@@ -2870,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="2">
-        <v>45995</v>
+        <v>46065</v>
       </c>
       <c r="P37" t="s">
         <v>7</v>
@@ -2884,10 +2734,10 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -2896,54 +2746,54 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I38" s="2">
-        <v>46014</v>
+        <v>46119</v>
       </c>
       <c r="J38" t="s">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M38" s="3">
         <v>1</v>
       </c>
       <c r="N38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2">
-        <v>46035</v>
+        <v>46065</v>
       </c>
       <c r="P38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
@@ -2955,34 +2805,34 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
       </c>
       <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="2">
+        <v>46127</v>
+      </c>
+      <c r="J39" t="s">
+        <v>7</v>
+      </c>
+      <c r="K39" t="s">
         <v>19</v>
       </c>
-      <c r="I39" s="2">
-        <v>46029</v>
-      </c>
-      <c r="J39" t="s">
-        <v>7</v>
-      </c>
-      <c r="K39" t="s">
-        <v>20</v>
-      </c>
       <c r="L39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2">
-        <v>46002</v>
+        <v>46065</v>
       </c>
       <c r="P39" t="s">
         <v>7</v>
@@ -2996,10 +2846,10 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -3008,10 +2858,10 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
@@ -3020,42 +2870,42 @@
         <v>6</v>
       </c>
       <c r="I40" s="2">
-        <v>46029</v>
+        <v>46127</v>
       </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M40" s="3">
         <v>1</v>
       </c>
       <c r="N40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2">
-        <v>46035</v>
+        <v>46065</v>
       </c>
       <c r="P40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
@@ -3064,81 +2914,81 @@
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G41" t="s">
         <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I41" s="2">
-        <v>46007</v>
+        <v>46132</v>
       </c>
       <c r="J41" t="s">
         <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="L41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M41" s="3">
         <v>1</v>
       </c>
       <c r="N41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2">
-        <v>46035</v>
+        <v>46065</v>
       </c>
       <c r="P41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G42" t="s">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2">
-        <v>46024</v>
+        <v>46119</v>
       </c>
       <c r="J42" t="s">
         <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="L42" t="s">
         <v>7</v>
@@ -3150,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="2">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="P42" t="s">
         <v>7</v>
@@ -3164,22 +3014,22 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>127</v>
       </c>
-      <c r="B43" t="s">
-        <v>132</v>
-      </c>
       <c r="C43" t="s">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G43" t="s">
         <v>2</v>
@@ -3188,42 +3038,42 @@
         <v>6</v>
       </c>
       <c r="I43" s="2">
-        <v>46024</v>
+        <v>46122</v>
       </c>
       <c r="J43" t="s">
         <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M43" s="3">
         <v>1</v>
       </c>
       <c r="N43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2">
-        <v>46035</v>
+        <v>46065</v>
       </c>
       <c r="P43" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
@@ -3235,22 +3085,22 @@
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G44" t="s">
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I44" s="2">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="L44" t="s">
         <v>7</v>
@@ -3262,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="2">
-        <v>46028</v>
+        <v>46065</v>
       </c>
       <c r="P44" t="s">
         <v>7</v>
@@ -3276,10 +3126,10 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -3288,25 +3138,25 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G45" t="s">
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I45" s="2">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="J45" t="s">
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="L45" t="s">
         <v>7</v>
@@ -3318,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="2">
-        <v>46029</v>
+        <v>46065</v>
       </c>
       <c r="P45" t="s">
         <v>7</v>
@@ -3332,11 +3182,11 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" t="s">
         <v>134</v>
       </c>
-      <c r="B46" t="s">
-        <v>139</v>
-      </c>
       <c r="C46" t="s">
         <v>2</v>
       </c>
@@ -3344,25 +3194,25 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G46" t="s">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I46" s="2">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="L46" t="s">
         <v>7</v>
@@ -3374,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="2">
-        <v>46029</v>
+        <v>46065</v>
       </c>
       <c r="P46" t="s">
         <v>7</v>
@@ -3388,10 +3238,10 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
@@ -3400,25 +3250,25 @@
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="F47" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I47" s="2">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="L47" t="s">
         <v>7</v>
@@ -3430,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="2">
-        <v>46028</v>
+        <v>46065</v>
       </c>
       <c r="P47" t="s">
         <v>7</v>
@@ -3444,10 +3294,10 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
@@ -3456,25 +3306,25 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I48" s="2">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="J48" t="s">
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="L48" t="s">
         <v>7</v>
@@ -3486,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="2">
-        <v>46029</v>
+        <v>46065</v>
       </c>
       <c r="P48" t="s">
         <v>7</v>
@@ -3500,37 +3350,37 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
       </c>
       <c r="F49" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I49" s="2">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J49" t="s">
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L49" t="s">
         <v>7</v>
@@ -3542,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="2">
-        <v>46029</v>
+        <v>46065</v>
       </c>
       <c r="P49" t="s">
         <v>7</v>
@@ -3556,37 +3406,37 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I50" s="2">
-        <v>46097</v>
+        <v>46128</v>
       </c>
       <c r="J50" t="s">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L50" t="s">
         <v>7</v>
@@ -3598,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="2">
-        <v>46028</v>
+        <v>46065</v>
       </c>
       <c r="P50" t="s">
         <v>7</v>
@@ -3612,10 +3462,10 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
@@ -3624,25 +3474,25 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I51" s="2">
-        <v>46113</v>
+        <v>46045</v>
       </c>
       <c r="J51" t="s">
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="L51" t="s">
         <v>7</v>
@@ -3654,10 +3504,10 @@
         <v>0</v>
       </c>
       <c r="O51" s="2">
-        <v>46029</v>
+        <v>46056</v>
       </c>
       <c r="P51" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="Q51" t="s">
         <v>7</v>
@@ -3668,37 +3518,37 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D52" t="s">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
       </c>
       <c r="H52" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I52" s="2">
-        <v>46114</v>
+        <v>46057</v>
       </c>
       <c r="J52" t="s">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="L52" t="s">
         <v>7</v>
@@ -3710,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="O52" s="2">
-        <v>46028</v>
+        <v>46056</v>
       </c>
       <c r="P52" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="Q52" t="s">
         <v>7</v>
@@ -3724,11 +3574,11 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" t="s">
         <v>149</v>
       </c>
-      <c r="B53" t="s">
-        <v>154</v>
-      </c>
       <c r="C53" t="s">
         <v>2</v>
       </c>
@@ -3736,10 +3586,10 @@
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="F53" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
@@ -3748,13 +3598,13 @@
         <v>6</v>
       </c>
       <c r="I53" s="2">
-        <v>46126</v>
+        <v>46057</v>
       </c>
       <c r="J53" t="s">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="L53" t="s">
         <v>7</v>
@@ -3766,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="P53" t="s">
         <v>7</v>
@@ -3780,37 +3630,37 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G54" t="s">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I54" s="2">
-        <v>46126</v>
+        <v>46062</v>
       </c>
       <c r="J54" t="s">
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="L54" t="s">
         <v>7</v>
@@ -3822,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="O54" s="2">
-        <v>46029</v>
+        <v>46056</v>
       </c>
       <c r="P54" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="Q54" t="s">
         <v>7</v>
@@ -3836,37 +3686,37 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F55" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G55" t="s">
         <v>2</v>
       </c>
       <c r="H55" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I55" s="2">
-        <v>46129</v>
+        <v>46044</v>
       </c>
       <c r="J55" t="s">
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="L55" t="s">
         <v>7</v>
@@ -3878,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="O55" s="2">
-        <v>46028</v>
+        <v>46056</v>
       </c>
       <c r="P55" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="Q55" t="s">
         <v>7</v>
@@ -3892,22 +3742,22 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" t="s">
         <v>149</v>
       </c>
-      <c r="B56" t="s">
-        <v>160</v>
-      </c>
       <c r="C56" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G56" t="s">
         <v>2</v>
@@ -3916,13 +3766,13 @@
         <v>6</v>
       </c>
       <c r="I56" s="2">
-        <v>46113</v>
+        <v>46050</v>
       </c>
       <c r="J56" t="s">
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="L56" t="s">
         <v>7</v>
@@ -3934,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="2">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="P56" t="s">
         <v>7</v>
@@ -3943,1182 +3793,6 @@
         <v>7</v>
       </c>
       <c r="R56" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18">
-      <c r="A57" t="s">
-        <v>149</v>
-      </c>
-      <c r="B57" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" t="s">
-        <v>2</v>
-      </c>
-      <c r="D57" t="s">
-        <v>64</v>
-      </c>
-      <c r="E57" t="s">
-        <v>53</v>
-      </c>
-      <c r="F57" t="s">
-        <v>163</v>
-      </c>
-      <c r="G57" t="s">
-        <v>2</v>
-      </c>
-      <c r="H57" t="s">
-        <v>19</v>
-      </c>
-      <c r="I57" s="2">
-        <v>46120</v>
-      </c>
-      <c r="J57" t="s">
-        <v>7</v>
-      </c>
-      <c r="K57" t="s">
-        <v>69</v>
-      </c>
-      <c r="L57" t="s">
-        <v>7</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="2">
-        <v>46029</v>
-      </c>
-      <c r="P57" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>7</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18">
-      <c r="A58" t="s">
-        <v>164</v>
-      </c>
-      <c r="B58" t="s">
-        <v>165</v>
-      </c>
-      <c r="C58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" t="s">
-        <v>166</v>
-      </c>
-      <c r="G58" t="s">
-        <v>2</v>
-      </c>
-      <c r="H58" t="s">
-        <v>19</v>
-      </c>
-      <c r="I58" s="2">
-        <v>46120</v>
-      </c>
-      <c r="J58" t="s">
-        <v>7</v>
-      </c>
-      <c r="K58" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" t="s">
-        <v>7</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P58" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>7</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18">
-      <c r="A59" t="s">
-        <v>164</v>
-      </c>
-      <c r="B59" t="s">
-        <v>167</v>
-      </c>
-      <c r="C59" t="s">
-        <v>2</v>
-      </c>
-      <c r="D59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" t="s">
-        <v>168</v>
-      </c>
-      <c r="G59" t="s">
-        <v>2</v>
-      </c>
-      <c r="H59" t="s">
-        <v>6</v>
-      </c>
-      <c r="I59" s="2">
-        <v>46121</v>
-      </c>
-      <c r="J59" t="s">
-        <v>7</v>
-      </c>
-      <c r="K59" t="s">
-        <v>47</v>
-      </c>
-      <c r="L59" t="s">
-        <v>7</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1</v>
-      </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P59" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>7</v>
-      </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18">
-      <c r="A60" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" t="s">
-        <v>169</v>
-      </c>
-      <c r="C60" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" t="s">
-        <v>170</v>
-      </c>
-      <c r="G60" t="s">
-        <v>2</v>
-      </c>
-      <c r="H60" t="s">
-        <v>6</v>
-      </c>
-      <c r="I60" s="2">
-        <v>46133</v>
-      </c>
-      <c r="J60" t="s">
-        <v>7</v>
-      </c>
-      <c r="K60" t="s">
-        <v>55</v>
-      </c>
-      <c r="L60" t="s">
-        <v>7</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1</v>
-      </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P60" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>7</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18">
-      <c r="A61" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" t="s">
-        <v>171</v>
-      </c>
-      <c r="C61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D61" t="s">
-        <v>3</v>
-      </c>
-      <c r="E61" t="s">
-        <v>57</v>
-      </c>
-      <c r="F61" t="s">
-        <v>172</v>
-      </c>
-      <c r="G61" t="s">
-        <v>2</v>
-      </c>
-      <c r="H61" t="s">
-        <v>19</v>
-      </c>
-      <c r="I61" s="2">
-        <v>46133</v>
-      </c>
-      <c r="J61" t="s">
-        <v>7</v>
-      </c>
-      <c r="K61" t="s">
-        <v>59</v>
-      </c>
-      <c r="L61" t="s">
-        <v>7</v>
-      </c>
-      <c r="M61" s="3">
-        <v>1</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P61" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>7</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18">
-      <c r="A62" t="s">
-        <v>164</v>
-      </c>
-      <c r="B62" t="s">
-        <v>173</v>
-      </c>
-      <c r="C62" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" t="s">
-        <v>22</v>
-      </c>
-      <c r="F62" t="s">
-        <v>174</v>
-      </c>
-      <c r="G62" t="s">
-        <v>2</v>
-      </c>
-      <c r="H62" t="s">
-        <v>6</v>
-      </c>
-      <c r="I62" s="2">
-        <v>46136</v>
-      </c>
-      <c r="J62" t="s">
-        <v>7</v>
-      </c>
-      <c r="K62" t="s">
-        <v>62</v>
-      </c>
-      <c r="L62" t="s">
-        <v>7</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P62" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>7</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18">
-      <c r="A63" t="s">
-        <v>164</v>
-      </c>
-      <c r="B63" t="s">
-        <v>175</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
-        <v>64</v>
-      </c>
-      <c r="E63" t="s">
-        <v>30</v>
-      </c>
-      <c r="F63" t="s">
-        <v>176</v>
-      </c>
-      <c r="G63" t="s">
-        <v>2</v>
-      </c>
-      <c r="H63" t="s">
-        <v>6</v>
-      </c>
-      <c r="I63" s="2">
-        <v>46120</v>
-      </c>
-      <c r="J63" t="s">
-        <v>7</v>
-      </c>
-      <c r="K63" t="s">
-        <v>66</v>
-      </c>
-      <c r="L63" t="s">
-        <v>7</v>
-      </c>
-      <c r="M63" s="3">
-        <v>1</v>
-      </c>
-      <c r="N63" s="3">
-        <v>0</v>
-      </c>
-      <c r="O63" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P63" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>7</v>
-      </c>
-      <c r="R63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18">
-      <c r="A64" t="s">
-        <v>164</v>
-      </c>
-      <c r="B64" t="s">
-        <v>177</v>
-      </c>
-      <c r="C64" t="s">
-        <v>2</v>
-      </c>
-      <c r="D64" t="s">
-        <v>64</v>
-      </c>
-      <c r="E64" t="s">
-        <v>53</v>
-      </c>
-      <c r="F64" t="s">
-        <v>178</v>
-      </c>
-      <c r="G64" t="s">
-        <v>2</v>
-      </c>
-      <c r="H64" t="s">
-        <v>19</v>
-      </c>
-      <c r="I64" s="2">
-        <v>46125</v>
-      </c>
-      <c r="J64" t="s">
-        <v>7</v>
-      </c>
-      <c r="K64" t="s">
-        <v>69</v>
-      </c>
-      <c r="L64" t="s">
-        <v>7</v>
-      </c>
-      <c r="M64" s="3">
-        <v>1</v>
-      </c>
-      <c r="N64" s="3">
-        <v>0</v>
-      </c>
-      <c r="O64" s="2">
-        <v>46028</v>
-      </c>
-      <c r="P64" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>7</v>
-      </c>
-      <c r="R64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18">
-      <c r="A65" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" t="s">
-        <v>180</v>
-      </c>
-      <c r="C65" t="s">
-        <v>2</v>
-      </c>
-      <c r="D65" t="s">
-        <v>3</v>
-      </c>
-      <c r="E65" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" t="s">
-        <v>181</v>
-      </c>
-      <c r="G65" t="s">
-        <v>2</v>
-      </c>
-      <c r="H65" t="s">
-        <v>19</v>
-      </c>
-      <c r="I65" s="2">
-        <v>46127</v>
-      </c>
-      <c r="J65" t="s">
-        <v>7</v>
-      </c>
-      <c r="K65" t="s">
-        <v>43</v>
-      </c>
-      <c r="L65" t="s">
-        <v>7</v>
-      </c>
-      <c r="M65" s="3">
-        <v>1</v>
-      </c>
-      <c r="N65" s="3">
-        <v>0</v>
-      </c>
-      <c r="O65" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P65" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>7</v>
-      </c>
-      <c r="R65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18">
-      <c r="A66" t="s">
-        <v>179</v>
-      </c>
-      <c r="B66" t="s">
-        <v>182</v>
-      </c>
-      <c r="C66" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" t="s">
-        <v>3</v>
-      </c>
-      <c r="E66" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" t="s">
-        <v>183</v>
-      </c>
-      <c r="G66" t="s">
-        <v>2</v>
-      </c>
-      <c r="H66" t="s">
-        <v>6</v>
-      </c>
-      <c r="I66" s="2">
-        <v>46128</v>
-      </c>
-      <c r="J66" t="s">
-        <v>7</v>
-      </c>
-      <c r="K66" t="s">
-        <v>47</v>
-      </c>
-      <c r="L66" t="s">
-        <v>7</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1</v>
-      </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
-      <c r="O66" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P66" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>7</v>
-      </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18">
-      <c r="A67" t="s">
-        <v>179</v>
-      </c>
-      <c r="B67" t="s">
-        <v>184</v>
-      </c>
-      <c r="C67" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" t="s">
-        <v>3</v>
-      </c>
-      <c r="E67" t="s">
-        <v>53</v>
-      </c>
-      <c r="F67" t="s">
-        <v>185</v>
-      </c>
-      <c r="G67" t="s">
-        <v>2</v>
-      </c>
-      <c r="H67" t="s">
-        <v>6</v>
-      </c>
-      <c r="I67" s="2">
-        <v>46140</v>
-      </c>
-      <c r="J67" t="s">
-        <v>7</v>
-      </c>
-      <c r="K67" t="s">
-        <v>55</v>
-      </c>
-      <c r="L67" t="s">
-        <v>7</v>
-      </c>
-      <c r="M67" s="3">
-        <v>1</v>
-      </c>
-      <c r="N67" s="3">
-        <v>0</v>
-      </c>
-      <c r="O67" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P67" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>7</v>
-      </c>
-      <c r="R67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18">
-      <c r="A68" t="s">
-        <v>179</v>
-      </c>
-      <c r="B68" t="s">
-        <v>186</v>
-      </c>
-      <c r="C68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
-        <v>3</v>
-      </c>
-      <c r="E68" t="s">
-        <v>57</v>
-      </c>
-      <c r="F68" t="s">
-        <v>187</v>
-      </c>
-      <c r="G68" t="s">
-        <v>2</v>
-      </c>
-      <c r="H68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" s="2">
-        <v>46140</v>
-      </c>
-      <c r="J68" t="s">
-        <v>7</v>
-      </c>
-      <c r="K68" t="s">
-        <v>59</v>
-      </c>
-      <c r="L68" t="s">
-        <v>7</v>
-      </c>
-      <c r="M68" s="3">
-        <v>1</v>
-      </c>
-      <c r="N68" s="3">
-        <v>0</v>
-      </c>
-      <c r="O68" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P68" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>7</v>
-      </c>
-      <c r="R68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18">
-      <c r="A69" t="s">
-        <v>179</v>
-      </c>
-      <c r="B69" t="s">
-        <v>188</v>
-      </c>
-      <c r="C69" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
-        <v>3</v>
-      </c>
-      <c r="E69" t="s">
-        <v>22</v>
-      </c>
-      <c r="F69" t="s">
-        <v>189</v>
-      </c>
-      <c r="G69" t="s">
-        <v>2</v>
-      </c>
-      <c r="H69" t="s">
-        <v>6</v>
-      </c>
-      <c r="I69" s="2">
-        <v>46146</v>
-      </c>
-      <c r="J69" t="s">
-        <v>7</v>
-      </c>
-      <c r="K69" t="s">
-        <v>62</v>
-      </c>
-      <c r="L69" t="s">
-        <v>7</v>
-      </c>
-      <c r="M69" s="3">
-        <v>1</v>
-      </c>
-      <c r="N69" s="3">
-        <v>0</v>
-      </c>
-      <c r="O69" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P69" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>7</v>
-      </c>
-      <c r="R69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18">
-      <c r="A70" t="s">
-        <v>179</v>
-      </c>
-      <c r="B70" t="s">
-        <v>190</v>
-      </c>
-      <c r="C70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
-        <v>64</v>
-      </c>
-      <c r="E70" t="s">
-        <v>30</v>
-      </c>
-      <c r="F70" t="s">
-        <v>191</v>
-      </c>
-      <c r="G70" t="s">
-        <v>2</v>
-      </c>
-      <c r="H70" t="s">
-        <v>6</v>
-      </c>
-      <c r="I70" s="2">
-        <v>46127</v>
-      </c>
-      <c r="J70" t="s">
-        <v>7</v>
-      </c>
-      <c r="K70" t="s">
-        <v>66</v>
-      </c>
-      <c r="L70" t="s">
-        <v>7</v>
-      </c>
-      <c r="M70" s="3">
-        <v>1</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-      <c r="O70" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P70" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>7</v>
-      </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18">
-      <c r="A71" t="s">
-        <v>179</v>
-      </c>
-      <c r="B71" t="s">
-        <v>192</v>
-      </c>
-      <c r="C71" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" t="s">
-        <v>64</v>
-      </c>
-      <c r="E71" t="s">
-        <v>53</v>
-      </c>
-      <c r="F71" t="s">
-        <v>193</v>
-      </c>
-      <c r="G71" t="s">
-        <v>2</v>
-      </c>
-      <c r="H71" t="s">
-        <v>19</v>
-      </c>
-      <c r="I71" s="2">
-        <v>46132</v>
-      </c>
-      <c r="J71" t="s">
-        <v>7</v>
-      </c>
-      <c r="K71" t="s">
-        <v>69</v>
-      </c>
-      <c r="L71" t="s">
-        <v>7</v>
-      </c>
-      <c r="M71" s="3">
-        <v>1</v>
-      </c>
-      <c r="N71" s="3">
-        <v>0</v>
-      </c>
-      <c r="O71" s="2">
-        <v>46046</v>
-      </c>
-      <c r="P71" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>7</v>
-      </c>
-      <c r="R71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18">
-      <c r="A72" t="s">
-        <v>194</v>
-      </c>
-      <c r="B72" t="s">
-        <v>195</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" t="s">
-        <v>45</v>
-      </c>
-      <c r="F72" t="s">
-        <v>196</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2</v>
-      </c>
-      <c r="H72" t="s">
-        <v>6</v>
-      </c>
-      <c r="I72" s="2">
-        <v>46045</v>
-      </c>
-      <c r="J72" t="s">
-        <v>7</v>
-      </c>
-      <c r="K72" t="s">
-        <v>47</v>
-      </c>
-      <c r="L72" t="s">
-        <v>7</v>
-      </c>
-      <c r="M72" s="3">
-        <v>1</v>
-      </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P72" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>7</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
-      <c r="A73" t="s">
-        <v>194</v>
-      </c>
-      <c r="B73" t="s">
-        <v>195</v>
-      </c>
-      <c r="C73" t="s">
-        <v>197</v>
-      </c>
-      <c r="D73" t="s">
-        <v>3</v>
-      </c>
-      <c r="E73" t="s">
-        <v>53</v>
-      </c>
-      <c r="F73" t="s">
-        <v>198</v>
-      </c>
-      <c r="G73" t="s">
-        <v>2</v>
-      </c>
-      <c r="H73" t="s">
-        <v>6</v>
-      </c>
-      <c r="I73" s="2">
-        <v>46057</v>
-      </c>
-      <c r="J73" t="s">
-        <v>7</v>
-      </c>
-      <c r="K73" t="s">
-        <v>55</v>
-      </c>
-      <c r="L73" t="s">
-        <v>7</v>
-      </c>
-      <c r="M73" s="3">
-        <v>1</v>
-      </c>
-      <c r="N73" s="3">
-        <v>0</v>
-      </c>
-      <c r="O73" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P73" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>7</v>
-      </c>
-      <c r="R73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
-      <c r="A74" t="s">
-        <v>194</v>
-      </c>
-      <c r="B74" t="s">
-        <v>199</v>
-      </c>
-      <c r="C74" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" t="s">
-        <v>3</v>
-      </c>
-      <c r="E74" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" t="s">
-        <v>200</v>
-      </c>
-      <c r="G74" t="s">
-        <v>2</v>
-      </c>
-      <c r="H74" t="s">
-        <v>19</v>
-      </c>
-      <c r="I74" s="2">
-        <v>46057</v>
-      </c>
-      <c r="J74" t="s">
-        <v>7</v>
-      </c>
-      <c r="K74" t="s">
-        <v>59</v>
-      </c>
-      <c r="L74" t="s">
-        <v>7</v>
-      </c>
-      <c r="M74" s="3">
-        <v>1</v>
-      </c>
-      <c r="N74" s="3">
-        <v>0</v>
-      </c>
-      <c r="O74" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P74" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>7</v>
-      </c>
-      <c r="R74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18">
-      <c r="A75" t="s">
-        <v>194</v>
-      </c>
-      <c r="B75" t="s">
-        <v>195</v>
-      </c>
-      <c r="C75" t="s">
-        <v>201</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E75" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75" t="s">
-        <v>202</v>
-      </c>
-      <c r="G75" t="s">
-        <v>2</v>
-      </c>
-      <c r="H75" t="s">
-        <v>6</v>
-      </c>
-      <c r="I75" s="2">
-        <v>46062</v>
-      </c>
-      <c r="J75" t="s">
-        <v>7</v>
-      </c>
-      <c r="K75" t="s">
-        <v>62</v>
-      </c>
-      <c r="L75" t="s">
-        <v>7</v>
-      </c>
-      <c r="M75" s="3">
-        <v>1</v>
-      </c>
-      <c r="N75" s="3">
-        <v>0</v>
-      </c>
-      <c r="O75" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P75" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>7</v>
-      </c>
-      <c r="R75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18">
-      <c r="A76" t="s">
-        <v>194</v>
-      </c>
-      <c r="B76" t="s">
-        <v>195</v>
-      </c>
-      <c r="C76" t="s">
-        <v>203</v>
-      </c>
-      <c r="D76" t="s">
-        <v>64</v>
-      </c>
-      <c r="E76" t="s">
-        <v>30</v>
-      </c>
-      <c r="F76" t="s">
-        <v>204</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2</v>
-      </c>
-      <c r="H76" t="s">
-        <v>6</v>
-      </c>
-      <c r="I76" s="2">
-        <v>46044</v>
-      </c>
-      <c r="J76" t="s">
-        <v>7</v>
-      </c>
-      <c r="K76" t="s">
-        <v>66</v>
-      </c>
-      <c r="L76" t="s">
-        <v>7</v>
-      </c>
-      <c r="M76" s="3">
-        <v>1</v>
-      </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P76" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>7</v>
-      </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" t="s">
-        <v>194</v>
-      </c>
-      <c r="B77" t="s">
-        <v>199</v>
-      </c>
-      <c r="C77" t="s">
-        <v>197</v>
-      </c>
-      <c r="D77" t="s">
-        <v>64</v>
-      </c>
-      <c r="E77" t="s">
-        <v>53</v>
-      </c>
-      <c r="F77" t="s">
-        <v>205</v>
-      </c>
-      <c r="G77" t="s">
-        <v>2</v>
-      </c>
-      <c r="H77" t="s">
-        <v>19</v>
-      </c>
-      <c r="I77" s="2">
-        <v>46050</v>
-      </c>
-      <c r="J77" t="s">
-        <v>7</v>
-      </c>
-      <c r="K77" t="s">
-        <v>69</v>
-      </c>
-      <c r="L77" t="s">
-        <v>7</v>
-      </c>
-      <c r="M77" s="3">
-        <v>1</v>
-      </c>
-      <c r="N77" s="3">
-        <v>0</v>
-      </c>
-      <c r="O77" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P77" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>7</v>
-      </c>
-      <c r="R77" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="255">
   <si>
     <t>200006254</t>
   </si>
@@ -310,6 +310,66 @@
     <t>AE頭噴漆</t>
   </si>
   <si>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>1400094671</t>
+  </si>
+  <si>
+    <t>1400097272</t>
+  </si>
+  <si>
+    <t>1400094151</t>
+  </si>
+  <si>
+    <t>1400097273</t>
+  </si>
+  <si>
+    <t>1400094152</t>
+  </si>
+  <si>
+    <t>1400097276</t>
+  </si>
+  <si>
+    <t>1400094672</t>
+  </si>
+  <si>
+    <t>1400097277</t>
+  </si>
+  <si>
+    <t>1400094153</t>
+  </si>
+  <si>
+    <t>1400097278</t>
+  </si>
+  <si>
+    <t>1400094154</t>
+  </si>
+  <si>
+    <t>1400097279</t>
+  </si>
+  <si>
+    <t>1400097290</t>
+  </si>
+  <si>
+    <t>200006483</t>
+  </si>
+  <si>
+    <t>1400094155</t>
+  </si>
+  <si>
+    <t>1400097291</t>
+  </si>
+  <si>
+    <t>1400097294</t>
+  </si>
+  <si>
+    <t>1400094156</t>
+  </si>
+  <si>
+    <t>1400097295</t>
+  </si>
+  <si>
     <t>200006488</t>
   </si>
   <si>
@@ -445,6 +505,174 @@
     <t>1400097447</t>
   </si>
   <si>
+    <t>200006493</t>
+  </si>
+  <si>
+    <t>1400094676</t>
+  </si>
+  <si>
+    <t>0070</t>
+  </si>
+  <si>
+    <t>1400097491</t>
+  </si>
+  <si>
+    <t>機頭精度檢驗</t>
+  </si>
+  <si>
+    <t>200006494</t>
+  </si>
+  <si>
+    <t>1400094677</t>
+  </si>
+  <si>
+    <t>1400097492</t>
+  </si>
+  <si>
+    <t>200006533</t>
+  </si>
+  <si>
+    <t>1400094679</t>
+  </si>
+  <si>
+    <t>1400097984</t>
+  </si>
+  <si>
+    <t>200006534</t>
+  </si>
+  <si>
+    <t>1400094678</t>
+  </si>
+  <si>
+    <t>1400097983</t>
+  </si>
+  <si>
+    <t>200006537</t>
+  </si>
+  <si>
+    <t>1400094681</t>
+  </si>
+  <si>
+    <t>1400097986</t>
+  </si>
+  <si>
+    <t>200006538</t>
+  </si>
+  <si>
+    <t>1400094680</t>
+  </si>
+  <si>
+    <t>1400097985</t>
+  </si>
+  <si>
+    <t>200006541</t>
+  </si>
+  <si>
+    <t>1400094683</t>
+  </si>
+  <si>
+    <t>1400097988</t>
+  </si>
+  <si>
+    <t>200006542</t>
+  </si>
+  <si>
+    <t>1400094682</t>
+  </si>
+  <si>
+    <t>1400097987</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>1400094686</t>
+  </si>
+  <si>
+    <t>1400098481</t>
+  </si>
+  <si>
+    <t>1400094161</t>
+  </si>
+  <si>
+    <t>1400098482</t>
+  </si>
+  <si>
+    <t>1400094162</t>
+  </si>
+  <si>
+    <t>1400098485</t>
+  </si>
+  <si>
+    <t>1400094687</t>
+  </si>
+  <si>
+    <t>1400098486</t>
+  </si>
+  <si>
+    <t>1400094163</t>
+  </si>
+  <si>
+    <t>1400098487</t>
+  </si>
+  <si>
+    <t>1400094164</t>
+  </si>
+  <si>
+    <t>1400098488</t>
+  </si>
+  <si>
+    <t>1400094688</t>
+  </si>
+  <si>
+    <t>1400098489</t>
+  </si>
+  <si>
+    <t>200006568</t>
+  </si>
+  <si>
+    <t>1400094691</t>
+  </si>
+  <si>
+    <t>1400098620</t>
+  </si>
+  <si>
+    <t>1400094166</t>
+  </si>
+  <si>
+    <t>1400098621</t>
+  </si>
+  <si>
+    <t>1400094167</t>
+  </si>
+  <si>
+    <t>1400098624</t>
+  </si>
+  <si>
+    <t>1400094692</t>
+  </si>
+  <si>
+    <t>1400098625</t>
+  </si>
+  <si>
+    <t>1400094168</t>
+  </si>
+  <si>
+    <t>1400098626</t>
+  </si>
+  <si>
+    <t>1400094169</t>
+  </si>
+  <si>
+    <t>1400098627</t>
+  </si>
+  <si>
+    <t>1400094693</t>
+  </si>
+  <si>
+    <t>1400098628</t>
+  </si>
+  <si>
     <t>630000329</t>
   </si>
   <si>
@@ -479,6 +707,21 @@
   </si>
   <si>
     <t>1400096510</t>
+  </si>
+  <si>
+    <t>630000337</t>
+  </si>
+  <si>
+    <t>1400093711</t>
+  </si>
+  <si>
+    <t>1400097255</t>
+  </si>
+  <si>
+    <t>1400094670</t>
+  </si>
+  <si>
+    <t>1400097256</t>
   </si>
   <si>
     <t>訂單</t>
@@ -637,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -662,58 +905,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>163</v>
+        <v>244</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>169</v>
+        <v>250</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>172</v>
+        <v>253</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>173</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1497,7 +1740,7 @@
         <v>7</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1721,7 +1964,7 @@
         <v>7</v>
       </c>
       <c r="R19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2310,7 +2553,7 @@
         <v>6</v>
       </c>
       <c r="I30" s="2">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="J30" t="s">
         <v>7</v>
@@ -2328,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P30" t="s">
         <v>7</v>
@@ -2366,7 +2609,7 @@
         <v>14</v>
       </c>
       <c r="I31" s="2">
-        <v>46097</v>
+        <v>46121</v>
       </c>
       <c r="J31" t="s">
         <v>7</v>
@@ -2384,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P31" t="s">
         <v>7</v>
@@ -2422,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="I32" s="2">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="J32" t="s">
         <v>7</v>
@@ -2440,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P32" t="s">
         <v>7</v>
@@ -2478,7 +2721,7 @@
         <v>6</v>
       </c>
       <c r="I33" s="2">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="J33" t="s">
         <v>7</v>
@@ -2496,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P33" t="s">
         <v>7</v>
@@ -2534,7 +2777,7 @@
         <v>14</v>
       </c>
       <c r="I34" s="2">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="J34" t="s">
         <v>7</v>
@@ -2552,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P34" t="s">
         <v>7</v>
@@ -2590,7 +2833,7 @@
         <v>14</v>
       </c>
       <c r="I35" s="2">
-        <v>46097</v>
+        <v>46120</v>
       </c>
       <c r="J35" t="s">
         <v>7</v>
@@ -2608,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P35" t="s">
         <v>7</v>
@@ -2625,7 +2868,7 @@
         <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
@@ -2637,7 +2880,7 @@
         <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
@@ -2646,7 +2889,7 @@
         <v>6</v>
       </c>
       <c r="I36" s="2">
-        <v>46100</v>
+        <v>46125</v>
       </c>
       <c r="J36" t="s">
         <v>7</v>
@@ -2664,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P36" t="s">
         <v>7</v>
@@ -2678,10 +2921,10 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" t="s">
         <v>114</v>
-      </c>
-      <c r="B37" t="s">
-        <v>115</v>
       </c>
       <c r="C37" t="s">
         <v>2</v>
@@ -2693,13 +2936,13 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I37" s="2">
         <v>46114</v>
@@ -2708,7 +2951,7 @@
         <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="L37" t="s">
         <v>7</v>
@@ -2720,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P37" t="s">
         <v>7</v>
@@ -2734,10 +2977,10 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -2746,25 +2989,25 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I38" s="2">
-        <v>46119</v>
+        <v>46134</v>
       </c>
       <c r="J38" t="s">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="L38" t="s">
         <v>7</v>
@@ -2776,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P38" t="s">
         <v>7</v>
@@ -2790,10 +3033,10 @@
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
@@ -2802,10 +3045,10 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
@@ -2814,13 +3057,13 @@
         <v>14</v>
       </c>
       <c r="I39" s="2">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="J39" t="s">
         <v>7</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="L39" t="s">
         <v>7</v>
@@ -2832,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P39" t="s">
         <v>7</v>
@@ -2846,22 +3089,22 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" t="s">
         <v>121</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" t="s">
-        <v>122</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
@@ -2870,13 +3113,13 @@
         <v>6</v>
       </c>
       <c r="I40" s="2">
-        <v>46127</v>
+        <v>46094</v>
       </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L40" t="s">
         <v>7</v>
@@ -2902,22 +3145,22 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
         <v>123</v>
-      </c>
-      <c r="C41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" t="s">
-        <v>124</v>
       </c>
       <c r="G41" t="s">
         <v>2</v>
@@ -2926,13 +3169,13 @@
         <v>14</v>
       </c>
       <c r="I41" s="2">
-        <v>46132</v>
+        <v>46097</v>
       </c>
       <c r="J41" t="s">
         <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L41" t="s">
         <v>7</v>
@@ -2958,22 +3201,22 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" t="s">
         <v>125</v>
-      </c>
-      <c r="C42" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" t="s">
-        <v>30</v>
-      </c>
-      <c r="F42" t="s">
-        <v>126</v>
       </c>
       <c r="G42" t="s">
         <v>2</v>
@@ -2982,13 +3225,13 @@
         <v>14</v>
       </c>
       <c r="I42" s="2">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="J42" t="s">
         <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L42" t="s">
         <v>7</v>
@@ -3014,22 +3257,22 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" t="s">
-        <v>128</v>
       </c>
       <c r="G43" t="s">
         <v>2</v>
@@ -3038,13 +3281,13 @@
         <v>6</v>
       </c>
       <c r="I43" s="2">
-        <v>46122</v>
+        <v>46105</v>
       </c>
       <c r="J43" t="s">
         <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L43" t="s">
         <v>7</v>
@@ -3070,37 +3313,37 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" t="s">
         <v>129</v>
       </c>
-      <c r="B44" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" t="s">
-        <v>131</v>
-      </c>
       <c r="G44" t="s">
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I44" s="2">
-        <v>46122</v>
+        <v>46108</v>
       </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="L44" t="s">
         <v>7</v>
@@ -3126,22 +3369,22 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G45" t="s">
         <v>2</v>
@@ -3150,13 +3393,13 @@
         <v>14</v>
       </c>
       <c r="I45" s="2">
-        <v>46125</v>
+        <v>46097</v>
       </c>
       <c r="J45" t="s">
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L45" t="s">
         <v>7</v>
@@ -3182,37 +3425,37 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G46" t="s">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I46" s="2">
-        <v>46133</v>
+        <v>46100</v>
       </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L46" t="s">
         <v>7</v>
@@ -3238,22 +3481,22 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B47" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" t="s">
         <v>136</v>
-      </c>
-      <c r="C47" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" t="s">
-        <v>137</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
@@ -3262,13 +3505,13 @@
         <v>6</v>
       </c>
       <c r="I47" s="2">
-        <v>46133</v>
+        <v>46114</v>
       </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L47" t="s">
         <v>7</v>
@@ -3294,22 +3537,22 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B48" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
         <v>138</v>
-      </c>
-      <c r="C48" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" t="s">
-        <v>139</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
@@ -3318,13 +3561,13 @@
         <v>14</v>
       </c>
       <c r="I48" s="2">
-        <v>46136</v>
+        <v>46119</v>
       </c>
       <c r="J48" t="s">
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L48" t="s">
         <v>7</v>
@@ -3350,22 +3593,22 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B49" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" t="s">
         <v>140</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" t="s">
-        <v>141</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
@@ -3374,13 +3617,13 @@
         <v>14</v>
       </c>
       <c r="I49" s="2">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="J49" t="s">
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L49" t="s">
         <v>7</v>
@@ -3406,22 +3649,22 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" t="s">
         <v>142</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" t="s">
-        <v>143</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
@@ -3430,13 +3673,13 @@
         <v>6</v>
       </c>
       <c r="I50" s="2">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="J50" t="s">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L50" t="s">
         <v>7</v>
@@ -3462,22 +3705,22 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
         <v>144</v>
-      </c>
-      <c r="B51" t="s">
-        <v>145</v>
-      </c>
-      <c r="C51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" t="s">
-        <v>146</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
@@ -3486,13 +3729,13 @@
         <v>14</v>
       </c>
       <c r="I51" s="2">
-        <v>46045</v>
+        <v>46132</v>
       </c>
       <c r="J51" t="s">
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L51" t="s">
         <v>7</v>
@@ -3504,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="O51" s="2">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="P51" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="s">
         <v>7</v>
@@ -3518,22 +3761,22 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
         <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
@@ -3542,13 +3785,13 @@
         <v>14</v>
       </c>
       <c r="I52" s="2">
-        <v>46057</v>
+        <v>46119</v>
       </c>
       <c r="J52" t="s">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L52" t="s">
         <v>7</v>
@@ -3560,10 +3803,10 @@
         <v>0</v>
       </c>
       <c r="O52" s="2">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="P52" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="s">
         <v>7</v>
@@ -3574,22 +3817,22 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F53" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
@@ -3598,13 +3841,13 @@
         <v>6</v>
       </c>
       <c r="I53" s="2">
-        <v>46057</v>
+        <v>46122</v>
       </c>
       <c r="J53" t="s">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L53" t="s">
         <v>7</v>
@@ -3616,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2">
-        <v>46038</v>
+        <v>46065</v>
       </c>
       <c r="P53" t="s">
         <v>7</v>
@@ -3630,37 +3873,37 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" t="s">
         <v>151</v>
       </c>
-      <c r="D54" t="s">
-        <v>3</v>
-      </c>
-      <c r="E54" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" t="s">
-        <v>152</v>
-      </c>
       <c r="G54" t="s">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I54" s="2">
-        <v>46062</v>
+        <v>46122</v>
       </c>
       <c r="J54" t="s">
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L54" t="s">
         <v>7</v>
@@ -3672,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="O54" s="2">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="P54" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="Q54" t="s">
         <v>7</v>
@@ -3686,22 +3929,22 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
         <v>153</v>
-      </c>
-      <c r="D55" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" t="s">
-        <v>154</v>
       </c>
       <c r="G55" t="s">
         <v>2</v>
@@ -3710,13 +3953,13 @@
         <v>14</v>
       </c>
       <c r="I55" s="2">
-        <v>46044</v>
+        <v>46125</v>
       </c>
       <c r="J55" t="s">
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L55" t="s">
         <v>7</v>
@@ -3728,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="O55" s="2">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="P55" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="Q55" t="s">
         <v>7</v>
@@ -3742,16 +3985,16 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
@@ -3763,36 +4006,1940 @@
         <v>2</v>
       </c>
       <c r="H56" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2">
+        <v>46133</v>
+      </c>
+      <c r="J56" t="s">
+        <v>7</v>
+      </c>
+      <c r="K56" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" t="s">
+        <v>7</v>
+      </c>
+      <c r="M56" s="3">
+        <v>1</v>
+      </c>
+      <c r="N56" s="3">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2">
+        <v>46065</v>
+      </c>
+      <c r="P56" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>7</v>
+      </c>
+      <c r="R56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" t="s">
+        <v>2</v>
+      </c>
+      <c r="H57" t="s">
         <v>6</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I57" s="2">
+        <v>46133</v>
+      </c>
+      <c r="J57" t="s">
+        <v>7</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>7</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2">
+        <v>46065</v>
+      </c>
+      <c r="P57" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>7</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>159</v>
+      </c>
+      <c r="G58" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="2">
+        <v>46136</v>
+      </c>
+      <c r="J58" t="s">
+        <v>7</v>
+      </c>
+      <c r="K58" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" t="s">
+        <v>7</v>
+      </c>
+      <c r="M58" s="3">
+        <v>1</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2">
+        <v>46065</v>
+      </c>
+      <c r="P58" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>7</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" t="s">
+        <v>30</v>
+      </c>
+      <c r="F59" t="s">
+        <v>161</v>
+      </c>
+      <c r="G59" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="2">
+        <v>46125</v>
+      </c>
+      <c r="J59" t="s">
+        <v>7</v>
+      </c>
+      <c r="K59" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" t="s">
+        <v>7</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2">
+        <v>46065</v>
+      </c>
+      <c r="P59" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>7</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" t="s">
+        <v>163</v>
+      </c>
+      <c r="G60" t="s">
+        <v>2</v>
+      </c>
+      <c r="H60" t="s">
+        <v>6</v>
+      </c>
+      <c r="I60" s="2">
+        <v>46128</v>
+      </c>
+      <c r="J60" t="s">
+        <v>7</v>
+      </c>
+      <c r="K60" t="s">
+        <v>35</v>
+      </c>
+      <c r="L60" t="s">
+        <v>7</v>
+      </c>
+      <c r="M60" s="3">
+        <v>1</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="2">
+        <v>46065</v>
+      </c>
+      <c r="P60" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>7</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" t="s">
+        <v>164</v>
+      </c>
+      <c r="B61" t="s">
+        <v>165</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>166</v>
+      </c>
+      <c r="F61" t="s">
+        <v>167</v>
+      </c>
+      <c r="G61" t="s">
+        <v>2</v>
+      </c>
+      <c r="H61" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="2">
+        <v>46100</v>
+      </c>
+      <c r="J61" t="s">
+        <v>7</v>
+      </c>
+      <c r="K61" t="s">
+        <v>168</v>
+      </c>
+      <c r="L61" t="s">
+        <v>7</v>
+      </c>
+      <c r="M61" s="3">
+        <v>1</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P61" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>7</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" t="s">
+        <v>169</v>
+      </c>
+      <c r="B62" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" t="s">
+        <v>171</v>
+      </c>
+      <c r="G62" t="s">
+        <v>2</v>
+      </c>
+      <c r="H62" t="s">
+        <v>6</v>
+      </c>
+      <c r="I62" s="2">
+        <v>46101</v>
+      </c>
+      <c r="J62" t="s">
+        <v>7</v>
+      </c>
+      <c r="K62" t="s">
+        <v>168</v>
+      </c>
+      <c r="L62" t="s">
+        <v>7</v>
+      </c>
+      <c r="M62" s="3">
+        <v>1</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P62" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>7</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" t="s">
+        <v>172</v>
+      </c>
+      <c r="B63" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" t="s">
+        <v>174</v>
+      </c>
+      <c r="G63" t="s">
+        <v>2</v>
+      </c>
+      <c r="H63" t="s">
+        <v>6</v>
+      </c>
+      <c r="I63" s="2">
+        <v>46163</v>
+      </c>
+      <c r="J63" t="s">
+        <v>7</v>
+      </c>
+      <c r="K63" t="s">
+        <v>168</v>
+      </c>
+      <c r="L63" t="s">
+        <v>7</v>
+      </c>
+      <c r="M63" s="3">
+        <v>1</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P63" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>7</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" t="s">
+        <v>175</v>
+      </c>
+      <c r="B64" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" t="s">
+        <v>177</v>
+      </c>
+      <c r="G64" t="s">
+        <v>2</v>
+      </c>
+      <c r="H64" t="s">
+        <v>6</v>
+      </c>
+      <c r="I64" s="2">
+        <v>46163</v>
+      </c>
+      <c r="J64" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" t="s">
+        <v>168</v>
+      </c>
+      <c r="L64" t="s">
+        <v>7</v>
+      </c>
+      <c r="M64" s="3">
+        <v>1</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P64" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>7</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" t="s">
+        <v>180</v>
+      </c>
+      <c r="G65" t="s">
+        <v>2</v>
+      </c>
+      <c r="H65" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="2">
+        <v>46213</v>
+      </c>
+      <c r="J65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K65" t="s">
+        <v>168</v>
+      </c>
+      <c r="L65" t="s">
+        <v>7</v>
+      </c>
+      <c r="M65" s="3">
+        <v>1</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P65" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>7</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" t="s">
+        <v>183</v>
+      </c>
+      <c r="G66" t="s">
+        <v>2</v>
+      </c>
+      <c r="H66" t="s">
+        <v>6</v>
+      </c>
+      <c r="I66" s="2">
+        <v>46213</v>
+      </c>
+      <c r="J66" t="s">
+        <v>7</v>
+      </c>
+      <c r="K66" t="s">
+        <v>168</v>
+      </c>
+      <c r="L66" t="s">
+        <v>7</v>
+      </c>
+      <c r="M66" s="3">
+        <v>1</v>
+      </c>
+      <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P66" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>7</v>
+      </c>
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" t="s">
+        <v>6</v>
+      </c>
+      <c r="I67" s="2">
+        <v>46252</v>
+      </c>
+      <c r="J67" t="s">
+        <v>7</v>
+      </c>
+      <c r="K67" t="s">
+        <v>168</v>
+      </c>
+      <c r="L67" t="s">
+        <v>7</v>
+      </c>
+      <c r="M67" s="3">
+        <v>1</v>
+      </c>
+      <c r="N67" s="3">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P67" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>7</v>
+      </c>
+      <c r="R67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" t="s">
+        <v>188</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" t="s">
+        <v>189</v>
+      </c>
+      <c r="G68" t="s">
+        <v>2</v>
+      </c>
+      <c r="H68" t="s">
+        <v>6</v>
+      </c>
+      <c r="I68" s="2">
+        <v>46252</v>
+      </c>
+      <c r="J68" t="s">
+        <v>7</v>
+      </c>
+      <c r="K68" t="s">
+        <v>168</v>
+      </c>
+      <c r="L68" t="s">
+        <v>7</v>
+      </c>
+      <c r="M68" s="3">
+        <v>1</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P68" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>7</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" t="s">
+        <v>190</v>
+      </c>
+      <c r="B69" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" t="s">
+        <v>192</v>
+      </c>
+      <c r="G69" t="s">
+        <v>2</v>
+      </c>
+      <c r="H69" t="s">
+        <v>6</v>
+      </c>
+      <c r="I69" s="2">
+        <v>46083</v>
+      </c>
+      <c r="J69" t="s">
+        <v>7</v>
+      </c>
+      <c r="K69" t="s">
+        <v>8</v>
+      </c>
+      <c r="L69" t="s">
+        <v>7</v>
+      </c>
+      <c r="M69" s="3">
+        <v>1</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P69" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>7</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" t="s">
+        <v>190</v>
+      </c>
+      <c r="B70" t="s">
+        <v>193</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>194</v>
+      </c>
+      <c r="G70" t="s">
+        <v>2</v>
+      </c>
+      <c r="H70" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="2">
+        <v>46084</v>
+      </c>
+      <c r="J70" t="s">
+        <v>7</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
+        <v>7</v>
+      </c>
+      <c r="M70" s="3">
+        <v>1</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P70" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>7</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" t="s">
+        <v>196</v>
+      </c>
+      <c r="G71" t="s">
+        <v>2</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="2">
+        <v>46097</v>
+      </c>
+      <c r="J71" t="s">
+        <v>7</v>
+      </c>
+      <c r="K71" t="s">
+        <v>19</v>
+      </c>
+      <c r="L71" t="s">
+        <v>7</v>
+      </c>
+      <c r="M71" s="3">
+        <v>1</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P71" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>7</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" t="s">
+        <v>190</v>
+      </c>
+      <c r="B72" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" t="s">
+        <v>198</v>
+      </c>
+      <c r="G72" t="s">
+        <v>2</v>
+      </c>
+      <c r="H72" t="s">
+        <v>6</v>
+      </c>
+      <c r="I72" s="2">
+        <v>46097</v>
+      </c>
+      <c r="J72" t="s">
+        <v>7</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>7</v>
+      </c>
+      <c r="M72" s="3">
+        <v>1</v>
+      </c>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P72" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>7</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>200</v>
+      </c>
+      <c r="G73" t="s">
+        <v>2</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="2">
+        <v>46100</v>
+      </c>
+      <c r="J73" t="s">
+        <v>7</v>
+      </c>
+      <c r="K73" t="s">
+        <v>27</v>
+      </c>
+      <c r="L73" t="s">
+        <v>7</v>
+      </c>
+      <c r="M73" s="3">
+        <v>1</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P73" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>7</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" t="s">
+        <v>190</v>
+      </c>
+      <c r="B74" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" t="s">
+        <v>30</v>
+      </c>
+      <c r="F74" t="s">
+        <v>202</v>
+      </c>
+      <c r="G74" t="s">
+        <v>2</v>
+      </c>
+      <c r="H74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="2">
+        <v>46083</v>
+      </c>
+      <c r="J74" t="s">
+        <v>7</v>
+      </c>
+      <c r="K74" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74" t="s">
+        <v>7</v>
+      </c>
+      <c r="M74" s="3">
+        <v>1</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P74" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>7</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" t="s">
+        <v>203</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" t="s">
+        <v>204</v>
+      </c>
+      <c r="G75" t="s">
+        <v>2</v>
+      </c>
+      <c r="H75" t="s">
+        <v>6</v>
+      </c>
+      <c r="I75" s="2">
+        <v>46086</v>
+      </c>
+      <c r="J75" t="s">
+        <v>7</v>
+      </c>
+      <c r="K75" t="s">
+        <v>35</v>
+      </c>
+      <c r="L75" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" s="3">
+        <v>1</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P75" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>7</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" t="s">
+        <v>205</v>
+      </c>
+      <c r="B76" t="s">
+        <v>206</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" t="s">
+        <v>207</v>
+      </c>
+      <c r="G76" t="s">
+        <v>2</v>
+      </c>
+      <c r="H76" t="s">
+        <v>6</v>
+      </c>
+      <c r="I76" s="2">
+        <v>46085</v>
+      </c>
+      <c r="J76" t="s">
+        <v>7</v>
+      </c>
+      <c r="K76" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" s="3">
+        <v>1</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P76" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>7</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" t="s">
+        <v>205</v>
+      </c>
+      <c r="B77" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>209</v>
+      </c>
+      <c r="G77" t="s">
+        <v>2</v>
+      </c>
+      <c r="H77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="2">
+        <v>46086</v>
+      </c>
+      <c r="J77" t="s">
+        <v>7</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>7</v>
+      </c>
+      <c r="M77" s="3">
+        <v>1</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P77" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>7</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="A78" t="s">
+        <v>205</v>
+      </c>
+      <c r="B78" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
+        <v>3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" t="s">
+        <v>211</v>
+      </c>
+      <c r="G78" t="s">
+        <v>2</v>
+      </c>
+      <c r="H78" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="2">
+        <v>46098</v>
+      </c>
+      <c r="J78" t="s">
+        <v>7</v>
+      </c>
+      <c r="K78" t="s">
+        <v>19</v>
+      </c>
+      <c r="L78" t="s">
+        <v>7</v>
+      </c>
+      <c r="M78" s="3">
+        <v>1</v>
+      </c>
+      <c r="N78" s="3">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P78" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>7</v>
+      </c>
+      <c r="R78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
+      <c r="A79" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" t="s">
+        <v>213</v>
+      </c>
+      <c r="G79" t="s">
+        <v>2</v>
+      </c>
+      <c r="H79" t="s">
+        <v>6</v>
+      </c>
+      <c r="I79" s="2">
+        <v>46098</v>
+      </c>
+      <c r="J79" t="s">
+        <v>7</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>7</v>
+      </c>
+      <c r="M79" s="3">
+        <v>1</v>
+      </c>
+      <c r="N79" s="3">
+        <v>0</v>
+      </c>
+      <c r="O79" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P79" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>7</v>
+      </c>
+      <c r="R79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
+      <c r="A80" t="s">
+        <v>205</v>
+      </c>
+      <c r="B80" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" t="s">
+        <v>215</v>
+      </c>
+      <c r="G80" t="s">
+        <v>2</v>
+      </c>
+      <c r="H80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="2">
+        <v>46101</v>
+      </c>
+      <c r="J80" t="s">
+        <v>7</v>
+      </c>
+      <c r="K80" t="s">
+        <v>27</v>
+      </c>
+      <c r="L80" t="s">
+        <v>7</v>
+      </c>
+      <c r="M80" s="3">
+        <v>1</v>
+      </c>
+      <c r="N80" s="3">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P80" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>7</v>
+      </c>
+      <c r="R80" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
+      <c r="A81" t="s">
+        <v>205</v>
+      </c>
+      <c r="B81" t="s">
+        <v>216</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" t="s">
+        <v>217</v>
+      </c>
+      <c r="G81" t="s">
+        <v>2</v>
+      </c>
+      <c r="H81" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="2">
+        <v>46085</v>
+      </c>
+      <c r="J81" t="s">
+        <v>7</v>
+      </c>
+      <c r="K81" t="s">
+        <v>32</v>
+      </c>
+      <c r="L81" t="s">
+        <v>7</v>
+      </c>
+      <c r="M81" s="3">
+        <v>1</v>
+      </c>
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P81" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>7</v>
+      </c>
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
+      <c r="A82" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" t="s">
+        <v>218</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" t="s">
+        <v>219</v>
+      </c>
+      <c r="G82" t="s">
+        <v>2</v>
+      </c>
+      <c r="H82" t="s">
+        <v>6</v>
+      </c>
+      <c r="I82" s="2">
+        <v>46090</v>
+      </c>
+      <c r="J82" t="s">
+        <v>7</v>
+      </c>
+      <c r="K82" t="s">
+        <v>35</v>
+      </c>
+      <c r="L82" t="s">
+        <v>7</v>
+      </c>
+      <c r="M82" s="3">
+        <v>1</v>
+      </c>
+      <c r="N82" s="3">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P82" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>7</v>
+      </c>
+      <c r="R82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
+      <c r="A83" t="s">
+        <v>220</v>
+      </c>
+      <c r="B83" t="s">
+        <v>221</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>222</v>
+      </c>
+      <c r="G83" t="s">
+        <v>2</v>
+      </c>
+      <c r="H83" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="2">
+        <v>46045</v>
+      </c>
+      <c r="J83" t="s">
+        <v>7</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
+        <v>7</v>
+      </c>
+      <c r="M83" s="3">
+        <v>1</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="2">
+        <v>46056</v>
+      </c>
+      <c r="P83" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>7</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
+      <c r="A84" t="s">
+        <v>220</v>
+      </c>
+      <c r="B84" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" t="s">
+        <v>74</v>
+      </c>
+      <c r="D84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" t="s">
+        <v>224</v>
+      </c>
+      <c r="G84" t="s">
+        <v>2</v>
+      </c>
+      <c r="H84" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="2">
+        <v>46057</v>
+      </c>
+      <c r="J84" t="s">
+        <v>7</v>
+      </c>
+      <c r="K84" t="s">
+        <v>19</v>
+      </c>
+      <c r="L84" t="s">
+        <v>7</v>
+      </c>
+      <c r="M84" s="3">
+        <v>1</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="2">
+        <v>46056</v>
+      </c>
+      <c r="P84" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>7</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
+      <c r="A85" t="s">
+        <v>220</v>
+      </c>
+      <c r="B85" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F85" t="s">
+        <v>226</v>
+      </c>
+      <c r="G85" t="s">
+        <v>2</v>
+      </c>
+      <c r="H85" t="s">
+        <v>6</v>
+      </c>
+      <c r="I85" s="2">
+        <v>46057</v>
+      </c>
+      <c r="J85" t="s">
+        <v>7</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>7</v>
+      </c>
+      <c r="M85" s="3">
+        <v>1</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="2">
+        <v>46038</v>
+      </c>
+      <c r="P85" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>7</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
+      <c r="A86" t="s">
+        <v>220</v>
+      </c>
+      <c r="B86" t="s">
+        <v>221</v>
+      </c>
+      <c r="C86" t="s">
+        <v>227</v>
+      </c>
+      <c r="D86" t="s">
+        <v>3</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" t="s">
+        <v>228</v>
+      </c>
+      <c r="G86" t="s">
+        <v>2</v>
+      </c>
+      <c r="H86" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="2">
+        <v>46062</v>
+      </c>
+      <c r="J86" t="s">
+        <v>7</v>
+      </c>
+      <c r="K86" t="s">
+        <v>27</v>
+      </c>
+      <c r="L86" t="s">
+        <v>7</v>
+      </c>
+      <c r="M86" s="3">
+        <v>1</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="2">
+        <v>46056</v>
+      </c>
+      <c r="P86" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>7</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
+      <c r="A87" t="s">
+        <v>220</v>
+      </c>
+      <c r="B87" t="s">
+        <v>221</v>
+      </c>
+      <c r="C87" t="s">
+        <v>229</v>
+      </c>
+      <c r="D87" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" t="s">
+        <v>30</v>
+      </c>
+      <c r="F87" t="s">
+        <v>230</v>
+      </c>
+      <c r="G87" t="s">
+        <v>2</v>
+      </c>
+      <c r="H87" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" s="2">
+        <v>46044</v>
+      </c>
+      <c r="J87" t="s">
+        <v>7</v>
+      </c>
+      <c r="K87" t="s">
+        <v>32</v>
+      </c>
+      <c r="L87" t="s">
+        <v>7</v>
+      </c>
+      <c r="M87" s="3">
+        <v>1</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="2">
+        <v>46056</v>
+      </c>
+      <c r="P87" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>7</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
+      <c r="A88" t="s">
+        <v>220</v>
+      </c>
+      <c r="B88" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D88" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" t="s">
+        <v>231</v>
+      </c>
+      <c r="G88" t="s">
+        <v>2</v>
+      </c>
+      <c r="H88" t="s">
+        <v>6</v>
+      </c>
+      <c r="I88" s="2">
         <v>46050</v>
       </c>
-      <c r="J56" t="s">
-        <v>7</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="J88" t="s">
+        <v>7</v>
+      </c>
+      <c r="K88" t="s">
         <v>35</v>
       </c>
-      <c r="L56" t="s">
-        <v>7</v>
-      </c>
-      <c r="M56" s="3">
-        <v>1</v>
-      </c>
-      <c r="N56" s="3">
-        <v>0</v>
-      </c>
-      <c r="O56" s="2">
+      <c r="L88" t="s">
+        <v>7</v>
+      </c>
+      <c r="M88" s="3">
+        <v>1</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2">
         <v>46038</v>
       </c>
-      <c r="P56" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>7</v>
-      </c>
-      <c r="R56" s="3">
+      <c r="P88" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>7</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
+      <c r="A89" t="s">
+        <v>232</v>
+      </c>
+      <c r="B89" t="s">
+        <v>233</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" t="s">
+        <v>234</v>
+      </c>
+      <c r="G89" t="s">
+        <v>2</v>
+      </c>
+      <c r="H89" t="s">
+        <v>62</v>
+      </c>
+      <c r="I89" s="2">
+        <v>46090</v>
+      </c>
+      <c r="J89" t="s">
+        <v>7</v>
+      </c>
+      <c r="K89" t="s">
+        <v>63</v>
+      </c>
+      <c r="L89" t="s">
+        <v>7</v>
+      </c>
+      <c r="M89" s="3">
+        <v>1</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="2">
+        <v>46079</v>
+      </c>
+      <c r="P89" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>7</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
+      <c r="A90" t="s">
+        <v>232</v>
+      </c>
+      <c r="B90" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" t="s">
+        <v>3</v>
+      </c>
+      <c r="E90" t="s">
+        <v>65</v>
+      </c>
+      <c r="F90" t="s">
+        <v>236</v>
+      </c>
+      <c r="G90" t="s">
+        <v>2</v>
+      </c>
+      <c r="H90" t="s">
+        <v>6</v>
+      </c>
+      <c r="I90" s="2">
+        <v>46092</v>
+      </c>
+      <c r="J90" t="s">
+        <v>7</v>
+      </c>
+      <c r="K90" t="s">
+        <v>67</v>
+      </c>
+      <c r="L90" t="s">
+        <v>7</v>
+      </c>
+      <c r="M90" s="3">
+        <v>1</v>
+      </c>
+      <c r="N90" s="3">
+        <v>0</v>
+      </c>
+      <c r="O90" s="2">
+        <v>46083</v>
+      </c>
+      <c r="P90" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>7</v>
+      </c>
+      <c r="R90" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="202">
   <si>
     <t>200006254</t>
   </si>
@@ -121,607 +121,448 @@
     <t>A軸鏟花</t>
   </si>
   <si>
-    <t>200006326</t>
-  </si>
-  <si>
-    <t>1400091195</t>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>1400094671</t>
+  </si>
+  <si>
+    <t>1400097272</t>
+  </si>
+  <si>
+    <t>1400094151</t>
+  </si>
+  <si>
+    <t>1400097273</t>
+  </si>
+  <si>
+    <t>1400094152</t>
+  </si>
+  <si>
+    <t>1400097276</t>
+  </si>
+  <si>
+    <t>1400094672</t>
+  </si>
+  <si>
+    <t>1400097277</t>
+  </si>
+  <si>
+    <t>1400094153</t>
+  </si>
+  <si>
+    <t>1400097278</t>
+  </si>
+  <si>
+    <t>1400094154</t>
+  </si>
+  <si>
+    <t>1400097279</t>
   </si>
   <si>
     <t>1400094673</t>
   </si>
   <si>
+    <t>1400097290</t>
+  </si>
+  <si>
+    <t>200006483</t>
+  </si>
+  <si>
+    <t>1400094155</t>
+  </si>
+  <si>
+    <t>1400097291</t>
+  </si>
+  <si>
+    <t>A90頭噴漆</t>
+  </si>
+  <si>
+    <t>1400096917</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>1400097293</t>
+  </si>
+  <si>
+    <t>1G0054</t>
+  </si>
+  <si>
+    <t>軸承箱墊片研磨</t>
+  </si>
+  <si>
+    <t>1400094674</t>
+  </si>
+  <si>
+    <t>0150</t>
+  </si>
+  <si>
+    <t>1400097294</t>
+  </si>
+  <si>
+    <t>A90頭鏟花</t>
+  </si>
+  <si>
+    <t>1400094156</t>
+  </si>
+  <si>
+    <t>1400097295</t>
+  </si>
+  <si>
+    <t>接頭座噴漆</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>1400093587</t>
+  </si>
+  <si>
+    <t>1400097411</t>
+  </si>
+  <si>
+    <t>1400093588</t>
+  </si>
+  <si>
+    <t>1400097412</t>
+  </si>
+  <si>
+    <t>1400096378</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>1400097414</t>
+  </si>
+  <si>
+    <t>角度頭墊片研磨</t>
+  </si>
+  <si>
+    <t>1400093589</t>
+  </si>
+  <si>
+    <t>1400097415</t>
+  </si>
+  <si>
+    <t>1400093590</t>
+  </si>
+  <si>
+    <t>1400097416</t>
+  </si>
+  <si>
+    <t>1400093591</t>
+  </si>
+  <si>
+    <t>1400097417</t>
+  </si>
+  <si>
+    <t>1400093592</t>
+  </si>
+  <si>
+    <t>1400097418</t>
+  </si>
+  <si>
+    <t>1400093593</t>
+  </si>
+  <si>
+    <t>1400097419</t>
+  </si>
+  <si>
+    <t>200006489</t>
+  </si>
+  <si>
+    <t>1400093594</t>
+  </si>
+  <si>
+    <t>1400097430</t>
+  </si>
+  <si>
+    <t>1400093595</t>
+  </si>
+  <si>
+    <t>1400097431</t>
+  </si>
+  <si>
+    <t>1400096379</t>
+  </si>
+  <si>
+    <t>1400097433</t>
+  </si>
+  <si>
+    <t>1400093596</t>
+  </si>
+  <si>
+    <t>1400097434</t>
+  </si>
+  <si>
+    <t>1400093597</t>
+  </si>
+  <si>
+    <t>1400097435</t>
+  </si>
+  <si>
+    <t>1400093598</t>
+  </si>
+  <si>
+    <t>1400097436</t>
+  </si>
+  <si>
+    <t>1400093599</t>
+  </si>
+  <si>
+    <t>1400097437</t>
+  </si>
+  <si>
+    <t>1400093600</t>
+  </si>
+  <si>
+    <t>1400097438</t>
+  </si>
+  <si>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>1400093601</t>
+  </si>
+  <si>
+    <t>1400097439</t>
+  </si>
+  <si>
+    <t>1400093602</t>
+  </si>
+  <si>
+    <t>1400097440</t>
+  </si>
+  <si>
+    <t>1400093603</t>
+  </si>
+  <si>
+    <t>1400097443</t>
+  </si>
+  <si>
+    <t>1400093604</t>
+  </si>
+  <si>
+    <t>1400097444</t>
+  </si>
+  <si>
+    <t>1400093605</t>
+  </si>
+  <si>
+    <t>1400097445</t>
+  </si>
+  <si>
+    <t>1400093606</t>
+  </si>
+  <si>
+    <t>1400097446</t>
+  </si>
+  <si>
+    <t>1400093607</t>
+  </si>
+  <si>
+    <t>1400097447</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>1400094686</t>
+  </si>
+  <si>
+    <t>1400098481</t>
+  </si>
+  <si>
+    <t>1400094161</t>
+  </si>
+  <si>
+    <t>1400098482</t>
+  </si>
+  <si>
+    <t>1400094162</t>
+  </si>
+  <si>
+    <t>1400098485</t>
+  </si>
+  <si>
+    <t>1400094687</t>
+  </si>
+  <si>
+    <t>1400098486</t>
+  </si>
+  <si>
+    <t>1400094163</t>
+  </si>
+  <si>
+    <t>1400098487</t>
+  </si>
+  <si>
+    <t>1400094164</t>
+  </si>
+  <si>
+    <t>1400098488</t>
+  </si>
+  <si>
+    <t>1400094688</t>
+  </si>
+  <si>
+    <t>1400098489</t>
+  </si>
+  <si>
+    <t>200006568</t>
+  </si>
+  <si>
+    <t>1400094691</t>
+  </si>
+  <si>
+    <t>1400098620</t>
+  </si>
+  <si>
+    <t>1400094166</t>
+  </si>
+  <si>
+    <t>1400098621</t>
+  </si>
+  <si>
+    <t>1400094167</t>
+  </si>
+  <si>
+    <t>1400098624</t>
+  </si>
+  <si>
+    <t>1400094692</t>
+  </si>
+  <si>
+    <t>1400098625</t>
+  </si>
+  <si>
+    <t>1400094168</t>
+  </si>
+  <si>
+    <t>1400098626</t>
+  </si>
+  <si>
+    <t>1400094169</t>
+  </si>
+  <si>
+    <t>1400098627</t>
+  </si>
+  <si>
+    <t>1400094693</t>
+  </si>
+  <si>
+    <t>1400098628</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>1400094813</t>
+  </si>
+  <si>
+    <t>1400098691</t>
+  </si>
+  <si>
+    <t>1400094842</t>
+  </si>
+  <si>
+    <t>1400098692</t>
+  </si>
+  <si>
+    <t>1400094843</t>
+  </si>
+  <si>
+    <t>1400098695</t>
+  </si>
+  <si>
+    <t>1400094814</t>
+  </si>
+  <si>
+    <t>1400098696</t>
+  </si>
+  <si>
+    <t>1400094844</t>
+  </si>
+  <si>
+    <t>1400098697</t>
+  </si>
+  <si>
+    <t>1400094845</t>
+  </si>
+  <si>
+    <t>1400098698</t>
+  </si>
+  <si>
+    <t>1400094815</t>
+  </si>
+  <si>
+    <t>1400098699</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>1400094900</t>
+  </si>
+  <si>
+    <t>1400098785</t>
+  </si>
+  <si>
     <t>M90頭噴漆</t>
   </si>
   <si>
-    <t>1400091294</t>
-  </si>
-  <si>
-    <t>0080</t>
-  </si>
-  <si>
-    <t>1400094674</t>
+    <t>1400094945</t>
+  </si>
+  <si>
+    <t>1400098786</t>
   </si>
   <si>
     <t>M90頭鏟花</t>
   </si>
   <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>1400091823</t>
-  </si>
-  <si>
-    <t>1400095323</t>
-  </si>
-  <si>
-    <t>PBM機頭噴漆</t>
-  </si>
-  <si>
-    <t>1400091824</t>
-  </si>
-  <si>
-    <t>1400095324</t>
-  </si>
-  <si>
-    <t>PBM進給座噴漆</t>
-  </si>
-  <si>
-    <t>1400091844</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>1400095325</t>
-  </si>
-  <si>
-    <t>齒輪箱進給座鏟花</t>
-  </si>
-  <si>
-    <t>200006388</t>
-  </si>
-  <si>
-    <t>1400092027</t>
-  </si>
-  <si>
-    <t>1400095483</t>
-  </si>
-  <si>
-    <t>A90頭噴漆</t>
-  </si>
-  <si>
-    <t>1400093569</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>1400095485</t>
-  </si>
-  <si>
-    <t>1G0054</t>
-  </si>
-  <si>
-    <t>軸承箱墊片研磨</t>
-  </si>
-  <si>
-    <t>1400092068</t>
-  </si>
-  <si>
-    <t>0150</t>
-  </si>
-  <si>
-    <t>1400095486</t>
-  </si>
-  <si>
-    <t>A90頭鏟花</t>
-  </si>
-  <si>
-    <t>1400092028</t>
-  </si>
-  <si>
-    <t>1400095487</t>
-  </si>
-  <si>
-    <t>接頭座噴漆</t>
-  </si>
-  <si>
-    <t>200006389</t>
-  </si>
-  <si>
-    <t>1400092029</t>
-  </si>
-  <si>
-    <t>1400095488</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>1400095560</t>
-  </si>
-  <si>
-    <t>1400092069</t>
-  </si>
-  <si>
-    <t>1400095561</t>
-  </si>
-  <si>
-    <t>1400092030</t>
-  </si>
-  <si>
-    <t>1400095562</t>
-  </si>
-  <si>
-    <t>200006466</t>
-  </si>
-  <si>
-    <t>1400093579</t>
-  </si>
-  <si>
-    <t>1400097135</t>
-  </si>
-  <si>
-    <t>1400093580</t>
-  </si>
-  <si>
-    <t>1400097136</t>
-  </si>
-  <si>
-    <t>1400093581</t>
-  </si>
-  <si>
-    <t>1400097139</t>
-  </si>
-  <si>
-    <t>1400093582</t>
-  </si>
-  <si>
-    <t>1400097140</t>
-  </si>
-  <si>
-    <t>1400093583</t>
-  </si>
-  <si>
-    <t>1400097141</t>
-  </si>
-  <si>
-    <t>1400093584</t>
-  </si>
-  <si>
-    <t>1400097142</t>
-  </si>
-  <si>
-    <t>1400093585</t>
-  </si>
-  <si>
-    <t>1400097143</t>
-  </si>
-  <si>
-    <t>200006467</t>
-  </si>
-  <si>
-    <t>1400093586</t>
-  </si>
-  <si>
-    <t>1400097144</t>
-  </si>
-  <si>
-    <t>AE頭噴漆</t>
-  </si>
-  <si>
-    <t>200006482</t>
-  </si>
-  <si>
-    <t>1400094671</t>
-  </si>
-  <si>
-    <t>1400097272</t>
-  </si>
-  <si>
-    <t>1400094151</t>
-  </si>
-  <si>
-    <t>1400097273</t>
-  </si>
-  <si>
-    <t>1400094152</t>
-  </si>
-  <si>
-    <t>1400097276</t>
-  </si>
-  <si>
-    <t>1400094672</t>
-  </si>
-  <si>
-    <t>1400097277</t>
-  </si>
-  <si>
-    <t>1400094153</t>
-  </si>
-  <si>
-    <t>1400097278</t>
-  </si>
-  <si>
-    <t>1400094154</t>
-  </si>
-  <si>
-    <t>1400097279</t>
-  </si>
-  <si>
-    <t>1400097290</t>
-  </si>
-  <si>
-    <t>200006483</t>
-  </si>
-  <si>
-    <t>1400094155</t>
-  </si>
-  <si>
-    <t>1400097291</t>
-  </si>
-  <si>
-    <t>1400097294</t>
-  </si>
-  <si>
-    <t>1400094156</t>
-  </si>
-  <si>
-    <t>1400097295</t>
-  </si>
-  <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>1400093587</t>
-  </si>
-  <si>
-    <t>1400097411</t>
-  </si>
-  <si>
-    <t>1400093588</t>
-  </si>
-  <si>
-    <t>1400097412</t>
-  </si>
-  <si>
-    <t>1400093589</t>
-  </si>
-  <si>
-    <t>1400097415</t>
-  </si>
-  <si>
-    <t>1400093590</t>
-  </si>
-  <si>
-    <t>1400097416</t>
-  </si>
-  <si>
-    <t>1400093591</t>
-  </si>
-  <si>
-    <t>1400097417</t>
-  </si>
-  <si>
-    <t>1400093592</t>
-  </si>
-  <si>
-    <t>1400097418</t>
-  </si>
-  <si>
-    <t>1400093593</t>
-  </si>
-  <si>
-    <t>1400097419</t>
-  </si>
-  <si>
-    <t>200006489</t>
-  </si>
-  <si>
-    <t>1400093594</t>
-  </si>
-  <si>
-    <t>1400097430</t>
-  </si>
-  <si>
-    <t>1400093595</t>
-  </si>
-  <si>
-    <t>1400097431</t>
-  </si>
-  <si>
-    <t>1400093596</t>
-  </si>
-  <si>
-    <t>1400097434</t>
-  </si>
-  <si>
-    <t>1400093597</t>
-  </si>
-  <si>
-    <t>1400097435</t>
-  </si>
-  <si>
-    <t>1400093598</t>
-  </si>
-  <si>
-    <t>1400097436</t>
-  </si>
-  <si>
-    <t>1400093599</t>
-  </si>
-  <si>
-    <t>1400097437</t>
-  </si>
-  <si>
-    <t>1400093600</t>
-  </si>
-  <si>
-    <t>1400097438</t>
-  </si>
-  <si>
-    <t>200006490</t>
-  </si>
-  <si>
-    <t>1400093601</t>
-  </si>
-  <si>
-    <t>1400097439</t>
-  </si>
-  <si>
-    <t>1400093602</t>
-  </si>
-  <si>
-    <t>1400097440</t>
-  </si>
-  <si>
-    <t>1400093603</t>
-  </si>
-  <si>
-    <t>1400097443</t>
-  </si>
-  <si>
-    <t>1400093604</t>
-  </si>
-  <si>
-    <t>1400097444</t>
-  </si>
-  <si>
-    <t>1400093605</t>
-  </si>
-  <si>
-    <t>1400097445</t>
-  </si>
-  <si>
-    <t>1400093606</t>
-  </si>
-  <si>
-    <t>1400097446</t>
-  </si>
-  <si>
-    <t>1400093607</t>
-  </si>
-  <si>
-    <t>1400097447</t>
-  </si>
-  <si>
-    <t>200006493</t>
-  </si>
-  <si>
-    <t>1400094676</t>
-  </si>
-  <si>
-    <t>0070</t>
-  </si>
-  <si>
-    <t>1400097491</t>
-  </si>
-  <si>
-    <t>機頭精度檢驗</t>
-  </si>
-  <si>
-    <t>200006494</t>
-  </si>
-  <si>
-    <t>1400094677</t>
-  </si>
-  <si>
-    <t>1400097492</t>
-  </si>
-  <si>
-    <t>200006533</t>
-  </si>
-  <si>
-    <t>1400094679</t>
-  </si>
-  <si>
-    <t>1400097984</t>
-  </si>
-  <si>
-    <t>200006534</t>
-  </si>
-  <si>
-    <t>1400094678</t>
-  </si>
-  <si>
-    <t>1400097983</t>
-  </si>
-  <si>
-    <t>200006537</t>
-  </si>
-  <si>
-    <t>1400094681</t>
-  </si>
-  <si>
-    <t>1400097986</t>
-  </si>
-  <si>
-    <t>200006538</t>
-  </si>
-  <si>
-    <t>1400094680</t>
-  </si>
-  <si>
-    <t>1400097985</t>
-  </si>
-  <si>
-    <t>200006541</t>
-  </si>
-  <si>
-    <t>1400094683</t>
-  </si>
-  <si>
-    <t>1400097988</t>
-  </si>
-  <si>
-    <t>200006542</t>
-  </si>
-  <si>
-    <t>1400094682</t>
-  </si>
-  <si>
-    <t>1400097987</t>
-  </si>
-  <si>
-    <t>200006567</t>
-  </si>
-  <si>
-    <t>1400094686</t>
-  </si>
-  <si>
-    <t>1400098481</t>
-  </si>
-  <si>
-    <t>1400094161</t>
-  </si>
-  <si>
-    <t>1400098482</t>
-  </si>
-  <si>
-    <t>1400094162</t>
-  </si>
-  <si>
-    <t>1400098485</t>
-  </si>
-  <si>
-    <t>1400094687</t>
-  </si>
-  <si>
-    <t>1400098486</t>
-  </si>
-  <si>
-    <t>1400094163</t>
-  </si>
-  <si>
-    <t>1400098487</t>
-  </si>
-  <si>
-    <t>1400094164</t>
-  </si>
-  <si>
-    <t>1400098488</t>
-  </si>
-  <si>
-    <t>1400094688</t>
-  </si>
-  <si>
-    <t>1400098489</t>
-  </si>
-  <si>
-    <t>200006568</t>
-  </si>
-  <si>
-    <t>1400094691</t>
-  </si>
-  <si>
-    <t>1400098620</t>
-  </si>
-  <si>
-    <t>1400094166</t>
-  </si>
-  <si>
-    <t>1400098621</t>
-  </si>
-  <si>
-    <t>1400094167</t>
-  </si>
-  <si>
-    <t>1400098624</t>
-  </si>
-  <si>
-    <t>1400094692</t>
-  </si>
-  <si>
-    <t>1400098625</t>
-  </si>
-  <si>
-    <t>1400094168</t>
-  </si>
-  <si>
-    <t>1400098626</t>
-  </si>
-  <si>
-    <t>1400094169</t>
-  </si>
-  <si>
-    <t>1400098627</t>
-  </si>
-  <si>
-    <t>1400094693</t>
-  </si>
-  <si>
-    <t>1400098628</t>
-  </si>
-  <si>
-    <t>630000329</t>
-  </si>
-  <si>
-    <t>1400092948</t>
-  </si>
-  <si>
-    <t>1400096493</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>1400096496</t>
-  </si>
-  <si>
-    <t>1400092949</t>
-  </si>
-  <si>
-    <t>1400096497</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1400096498</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>1400096499</t>
-  </si>
-  <si>
-    <t>1400096510</t>
-  </si>
-  <si>
-    <t>630000337</t>
-  </si>
-  <si>
-    <t>1400093711</t>
-  </si>
-  <si>
-    <t>1400097255</t>
-  </si>
-  <si>
-    <t>1400094670</t>
-  </si>
-  <si>
-    <t>1400097256</t>
+    <t>200006575</t>
+  </si>
+  <si>
+    <t>1400094901</t>
+  </si>
+  <si>
+    <t>1400098787</t>
+  </si>
+  <si>
+    <t>1400094947</t>
+  </si>
+  <si>
+    <t>1400098800</t>
+  </si>
+  <si>
+    <t>1400094904</t>
+  </si>
+  <si>
+    <t>1400098801</t>
+  </si>
+  <si>
+    <t>200006580</t>
+  </si>
+  <si>
+    <t>1400094902</t>
+  </si>
+  <si>
+    <t>1400098795</t>
+  </si>
+  <si>
+    <t>1400094946</t>
+  </si>
+  <si>
+    <t>1400098798</t>
+  </si>
+  <si>
+    <t>1400094903</t>
+  </si>
+  <si>
+    <t>1400098799</t>
   </si>
   <si>
     <t>訂單</t>
@@ -880,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -905,58 +746,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1374,16 +1215,16 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="J9" t="s">
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="L9" t="s">
         <v>7</v>
@@ -1395,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="2">
-        <v>45979</v>
+        <v>46083</v>
       </c>
       <c r="P9" t="s">
         <v>7</v>
@@ -1412,46 +1253,46 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
       <c r="G10" t="s">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I10" s="2">
-        <v>46099</v>
+        <v>46121</v>
       </c>
       <c r="J10" t="s">
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M10" s="3">
         <v>1</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2">
-        <v>45979</v>
+        <v>46083</v>
       </c>
       <c r="P10" t="s">
         <v>7</v>
@@ -1460,15 +1301,15 @@
         <v>7</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
@@ -1477,10 +1318,10 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
         <v>2</v>
@@ -1489,13 +1330,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="2">
-        <v>46065</v>
+        <v>46133</v>
       </c>
       <c r="J11" t="s">
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="L11" t="s">
         <v>9</v>
@@ -1507,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="2">
-        <v>45995</v>
+        <v>46083</v>
       </c>
       <c r="P11" t="s">
         <v>7</v>
@@ -1521,49 +1362,49 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
         <v>44</v>
       </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
       <c r="G12" t="s">
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2">
-        <v>46065</v>
+        <v>46133</v>
       </c>
       <c r="J12" t="s">
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M12" s="3">
         <v>1</v>
       </c>
       <c r="N12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2">
-        <v>45995</v>
+        <v>46083</v>
       </c>
       <c r="P12" t="s">
         <v>7</v>
@@ -1572,15 +1413,15 @@
         <v>7</v>
       </c>
       <c r="R12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
@@ -1589,37 +1430,37 @@
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2">
-        <v>46097</v>
+        <v>46136</v>
       </c>
       <c r="J13" t="s">
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M13" s="3">
         <v>1</v>
       </c>
       <c r="N13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2">
-        <v>45995</v>
+        <v>46083</v>
       </c>
       <c r="P13" t="s">
         <v>7</v>
@@ -1628,27 +1469,27 @@
         <v>7</v>
       </c>
       <c r="R13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
         <v>2</v>
@@ -1657,13 +1498,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="2">
-        <v>46014</v>
+        <v>46120</v>
       </c>
       <c r="J14" t="s">
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="L14" t="s">
         <v>9</v>
@@ -1675,13 +1516,13 @@
         <v>1</v>
       </c>
       <c r="O14" s="2">
-        <v>46035</v>
+        <v>46083</v>
       </c>
       <c r="P14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R14" s="3">
         <v>1</v>
@@ -1689,49 +1530,49 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G15" t="s">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="I15" s="2">
-        <v>46063</v>
+        <v>46125</v>
       </c>
       <c r="J15" t="s">
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M15" s="3">
         <v>1</v>
       </c>
       <c r="N15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2">
-        <v>46064</v>
+        <v>46083</v>
       </c>
       <c r="P15" t="s">
         <v>7</v>
@@ -1740,15 +1581,15 @@
         <v>7</v>
       </c>
       <c r="R15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
@@ -1757,25 +1598,25 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
         <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2">
-        <v>46029</v>
+        <v>46114</v>
       </c>
       <c r="J16" t="s">
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="L16" t="s">
         <v>9</v>
@@ -1787,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="2">
-        <v>46002</v>
+        <v>46083</v>
       </c>
       <c r="P16" t="s">
         <v>7</v>
@@ -1801,11 +1642,11 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
       <c r="C17" t="s">
         <v>2</v>
       </c>
@@ -1813,54 +1654,54 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="I17" s="2">
-        <v>46029</v>
+        <v>46140</v>
       </c>
       <c r="J17" t="s">
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="L17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M17" s="3">
         <v>1</v>
       </c>
       <c r="N17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2">
-        <v>46035</v>
+        <v>46134</v>
       </c>
       <c r="P17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
         <v>2</v>
@@ -1869,25 +1710,25 @@
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I18" s="2">
-        <v>46007</v>
+        <v>46134</v>
       </c>
       <c r="J18" t="s">
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L18" t="s">
         <v>9</v>
@@ -1899,13 +1740,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="2">
-        <v>46035</v>
+        <v>46083</v>
       </c>
       <c r="P18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R18" s="3">
         <v>1</v>
@@ -1913,37 +1754,37 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2">
-        <v>46059</v>
+        <v>46134</v>
       </c>
       <c r="J19" t="s">
         <v>7</v>
       </c>
       <c r="K19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L19" t="s">
         <v>9</v>
@@ -1955,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="2">
-        <v>46064</v>
+        <v>46083</v>
       </c>
       <c r="P19" t="s">
         <v>7</v>
@@ -1969,10 +1810,10 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>2</v>
@@ -1981,10 +1822,10 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
         <v>2</v>
@@ -1993,13 +1834,13 @@
         <v>6</v>
       </c>
       <c r="I20" s="2">
-        <v>46024</v>
+        <v>46094</v>
       </c>
       <c r="J20" t="s">
         <v>7</v>
       </c>
       <c r="K20" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="L20" t="s">
         <v>9</v>
@@ -2011,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="2">
-        <v>46055</v>
+        <v>46125</v>
       </c>
       <c r="P20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R20" s="3">
         <v>1</v>
@@ -2025,22 +1866,22 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
         <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" t="s">
-        <v>79</v>
       </c>
       <c r="G21" t="s">
         <v>2</v>
@@ -2049,13 +1890,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="2">
-        <v>46024</v>
+        <v>46097</v>
       </c>
       <c r="J21" t="s">
         <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="L21" t="s">
         <v>9</v>
@@ -2067,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="2">
-        <v>46035</v>
+        <v>46125</v>
       </c>
       <c r="P21" t="s">
         <v>10</v>
@@ -2081,10 +1922,10 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
@@ -2093,37 +1934,37 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="I22" s="2">
-        <v>46065</v>
+        <v>46122</v>
       </c>
       <c r="J22" t="s">
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="L22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M22" s="3">
         <v>1</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2">
-        <v>46065</v>
+        <v>46119</v>
       </c>
       <c r="P22" t="s">
         <v>7</v>
@@ -2132,15 +1973,15 @@
         <v>7</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
@@ -2149,10 +1990,10 @@
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
@@ -2161,42 +2002,42 @@
         <v>14</v>
       </c>
       <c r="I23" s="2">
-        <v>46066</v>
+        <v>46105</v>
       </c>
       <c r="J23" t="s">
         <v>7</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M23" s="3">
         <v>1</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
         <v>2</v>
@@ -2205,55 +2046,55 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I24" s="2">
-        <v>46083</v>
+        <v>46105</v>
       </c>
       <c r="J24" t="s">
         <v>7</v>
       </c>
       <c r="K24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M24" s="3">
         <v>1</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
         <v>80</v>
       </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
       <c r="C25" t="s">
         <v>2</v>
       </c>
@@ -2261,66 +2102,66 @@
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2">
-        <v>46083</v>
+        <v>46108</v>
       </c>
       <c r="J25" t="s">
         <v>7</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M25" s="3">
         <v>1</v>
       </c>
       <c r="N25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s">
         <v>2</v>
@@ -2329,42 +2170,42 @@
         <v>14</v>
       </c>
       <c r="I26" s="2">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="J26" t="s">
         <v>7</v>
       </c>
       <c r="K26" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M26" s="3">
         <v>1</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P26" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
@@ -2373,66 +2214,66 @@
         <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I27" s="2">
-        <v>46065</v>
+        <v>46100</v>
       </c>
       <c r="J27" t="s">
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M27" s="3">
         <v>1</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
@@ -2441,22 +2282,22 @@
         <v>6</v>
       </c>
       <c r="I28" s="2">
-        <v>46077</v>
+        <v>46114</v>
       </c>
       <c r="J28" t="s">
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="L28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M28" s="3">
         <v>1</v>
       </c>
       <c r="N28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2">
         <v>46065</v>
@@ -2468,15 +2309,15 @@
         <v>7</v>
       </c>
       <c r="R28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
         <v>2</v>
@@ -2485,10 +2326,10 @@
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
         <v>2</v>
@@ -2497,42 +2338,42 @@
         <v>14</v>
       </c>
       <c r="I29" s="2">
-        <v>46077</v>
+        <v>46119</v>
       </c>
       <c r="J29" t="s">
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M29" s="3">
         <v>1</v>
       </c>
       <c r="N29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R29" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
         <v>2</v>
@@ -2541,37 +2382,37 @@
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s">
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="I30" s="2">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="J30" t="s">
         <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="L30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M30" s="3">
         <v>1</v>
       </c>
       <c r="N30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2">
-        <v>46083</v>
+        <v>46119</v>
       </c>
       <c r="P30" t="s">
         <v>7</v>
@@ -2580,15 +2421,15 @@
         <v>7</v>
       </c>
       <c r="R30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
         <v>2</v>
@@ -2597,10 +2438,10 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
         <v>2</v>
@@ -2609,42 +2450,42 @@
         <v>14</v>
       </c>
       <c r="I31" s="2">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="J31" t="s">
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M31" s="3">
         <v>1</v>
       </c>
       <c r="N31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="P31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
         <v>2</v>
@@ -2653,37 +2494,37 @@
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I32" s="2">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="J32" t="s">
         <v>7</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M32" s="3">
         <v>1</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="P32" t="s">
         <v>7</v>
@@ -2692,15 +2533,15 @@
         <v>7</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
         <v>2</v>
@@ -2709,66 +2550,66 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I33" s="2">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="J33" t="s">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M33" s="3">
         <v>1</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="P33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
         <v>99</v>
       </c>
-      <c r="B34" t="s">
-        <v>108</v>
-      </c>
       <c r="C34" t="s">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
@@ -2777,42 +2618,42 @@
         <v>14</v>
       </c>
       <c r="I34" s="2">
-        <v>46136</v>
+        <v>46119</v>
       </c>
       <c r="J34" t="s">
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M34" s="3">
         <v>1</v>
       </c>
       <c r="N34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="P34" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
@@ -2821,37 +2662,37 @@
         <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I35" s="2">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="J35" t="s">
         <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M35" s="3">
         <v>1</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="P35" t="s">
         <v>7</v>
@@ -2860,27 +2701,27 @@
         <v>7</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
@@ -2889,25 +2730,25 @@
         <v>6</v>
       </c>
       <c r="I36" s="2">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="J36" t="s">
         <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="L36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M36" s="3">
         <v>1</v>
       </c>
       <c r="N36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="P36" t="s">
         <v>7</v>
@@ -2916,15 +2757,15 @@
         <v>7</v>
       </c>
       <c r="R36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
         <v>2</v>
@@ -2933,10 +2774,10 @@
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
@@ -2945,42 +2786,42 @@
         <v>14</v>
       </c>
       <c r="I37" s="2">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="J37" t="s">
         <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M37" s="3">
         <v>1</v>
       </c>
       <c r="N37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="P37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -2989,54 +2830,54 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I38" s="2">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="J38" t="s">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="L38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M38" s="3">
         <v>1</v>
       </c>
       <c r="N38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="P38" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
@@ -3045,37 +2886,37 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I39" s="2">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="J39" t="s">
         <v>7</v>
       </c>
       <c r="K39" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="L39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="P39" t="s">
         <v>7</v>
@@ -3084,15 +2925,15 @@
         <v>7</v>
       </c>
       <c r="R39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -3101,66 +2942,66 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I40" s="2">
-        <v>46094</v>
+        <v>46136</v>
       </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="L40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M40" s="3">
         <v>1</v>
       </c>
       <c r="N40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G41" t="s">
         <v>2</v>
@@ -3169,78 +3010,78 @@
         <v>14</v>
       </c>
       <c r="I41" s="2">
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="J41" t="s">
         <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L41" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M41" s="3">
         <v>1</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P41" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q41" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G42" t="s">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I42" s="2">
-        <v>46105</v>
+        <v>46128</v>
       </c>
       <c r="J42" t="s">
         <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M42" s="3">
         <v>1</v>
       </c>
       <c r="N42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2">
         <v>46065</v>
@@ -3252,16 +3093,16 @@
         <v>7</v>
       </c>
       <c r="R42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" t="s">
         <v>119</v>
       </c>
-      <c r="B43" t="s">
-        <v>126</v>
-      </c>
       <c r="C43" t="s">
         <v>2</v>
       </c>
@@ -3269,10 +3110,10 @@
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G43" t="s">
         <v>2</v>
@@ -3281,13 +3122,13 @@
         <v>6</v>
       </c>
       <c r="I43" s="2">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="J43" t="s">
         <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L43" t="s">
         <v>7</v>
@@ -3299,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P43" t="s">
         <v>7</v>
@@ -3313,10 +3154,10 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
@@ -3325,10 +3166,10 @@
         <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G44" t="s">
         <v>2</v>
@@ -3337,13 +3178,13 @@
         <v>14</v>
       </c>
       <c r="I44" s="2">
-        <v>46108</v>
+        <v>46084</v>
       </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L44" t="s">
         <v>7</v>
@@ -3355,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P44" t="s">
         <v>7</v>
@@ -3369,22 +3210,22 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G45" t="s">
         <v>2</v>
@@ -3399,7 +3240,7 @@
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L45" t="s">
         <v>7</v>
@@ -3411,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P45" t="s">
         <v>7</v>
@@ -3425,22 +3266,22 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G46" t="s">
         <v>2</v>
@@ -3449,13 +3290,13 @@
         <v>6</v>
       </c>
       <c r="I46" s="2">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L46" t="s">
         <v>7</v>
@@ -3467,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P46" t="s">
         <v>7</v>
@@ -3481,10 +3322,10 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
@@ -3493,25 +3334,25 @@
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I47" s="2">
-        <v>46114</v>
+        <v>46100</v>
       </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="L47" t="s">
         <v>7</v>
@@ -3523,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P47" t="s">
         <v>7</v>
@@ -3537,22 +3378,22 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
@@ -3561,13 +3402,13 @@
         <v>14</v>
       </c>
       <c r="I48" s="2">
-        <v>46119</v>
+        <v>46083</v>
       </c>
       <c r="J48" t="s">
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L48" t="s">
         <v>7</v>
@@ -3579,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P48" t="s">
         <v>7</v>
@@ -3593,37 +3434,37 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I49" s="2">
-        <v>46127</v>
+        <v>46086</v>
       </c>
       <c r="J49" t="s">
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L49" t="s">
         <v>7</v>
@@ -3635,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P49" t="s">
         <v>7</v>
@@ -3649,11 +3490,11 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" t="s">
         <v>134</v>
       </c>
-      <c r="B50" t="s">
-        <v>141</v>
-      </c>
       <c r="C50" t="s">
         <v>2</v>
       </c>
@@ -3661,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
@@ -3673,13 +3514,13 @@
         <v>6</v>
       </c>
       <c r="I50" s="2">
-        <v>46127</v>
+        <v>46085</v>
       </c>
       <c r="J50" t="s">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L50" t="s">
         <v>7</v>
@@ -3691,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P50" t="s">
         <v>7</v>
@@ -3705,10 +3546,10 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
@@ -3717,10 +3558,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
@@ -3729,13 +3570,13 @@
         <v>14</v>
       </c>
       <c r="I51" s="2">
-        <v>46132</v>
+        <v>46086</v>
       </c>
       <c r="J51" t="s">
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L51" t="s">
         <v>7</v>
@@ -3747,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P51" t="s">
         <v>7</v>
@@ -3761,22 +3602,22 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
@@ -3785,13 +3626,13 @@
         <v>14</v>
       </c>
       <c r="I52" s="2">
-        <v>46119</v>
+        <v>46098</v>
       </c>
       <c r="J52" t="s">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L52" t="s">
         <v>7</v>
@@ -3803,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P52" t="s">
         <v>7</v>
@@ -3817,22 +3658,22 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F53" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
@@ -3841,13 +3682,13 @@
         <v>6</v>
       </c>
       <c r="I53" s="2">
-        <v>46122</v>
+        <v>46098</v>
       </c>
       <c r="J53" t="s">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L53" t="s">
         <v>7</v>
@@ -3859,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P53" t="s">
         <v>7</v>
@@ -3873,10 +3714,10 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
         <v>2</v>
@@ -3885,25 +3726,25 @@
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G54" t="s">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I54" s="2">
-        <v>46122</v>
+        <v>46101</v>
       </c>
       <c r="J54" t="s">
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="L54" t="s">
         <v>7</v>
@@ -3915,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P54" t="s">
         <v>7</v>
@@ -3929,22 +3770,22 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C55" t="s">
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F55" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G55" t="s">
         <v>2</v>
@@ -3953,13 +3794,13 @@
         <v>14</v>
       </c>
       <c r="I55" s="2">
-        <v>46125</v>
+        <v>46085</v>
       </c>
       <c r="J55" t="s">
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L55" t="s">
         <v>7</v>
@@ -3971,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P55" t="s">
         <v>7</v>
@@ -3985,37 +3826,37 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C56" t="s">
         <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G56" t="s">
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I56" s="2">
-        <v>46133</v>
+        <v>46090</v>
       </c>
       <c r="J56" t="s">
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L56" t="s">
         <v>7</v>
@@ -4027,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P56" t="s">
         <v>7</v>
@@ -4041,11 +3882,11 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" t="s">
         <v>149</v>
       </c>
-      <c r="B57" t="s">
-        <v>156</v>
-      </c>
       <c r="C57" t="s">
         <v>2</v>
       </c>
@@ -4053,10 +3894,10 @@
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G57" t="s">
         <v>2</v>
@@ -4065,13 +3906,13 @@
         <v>6</v>
       </c>
       <c r="I57" s="2">
-        <v>46133</v>
+        <v>46084</v>
       </c>
       <c r="J57" t="s">
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L57" t="s">
         <v>7</v>
@@ -4083,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="2">
-        <v>46065</v>
+        <v>46084</v>
       </c>
       <c r="P57" t="s">
         <v>7</v>
@@ -4097,10 +3938,10 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B58" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
@@ -4109,10 +3950,10 @@
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
         <v>2</v>
@@ -4121,13 +3962,13 @@
         <v>14</v>
       </c>
       <c r="I58" s="2">
-        <v>46136</v>
+        <v>46085</v>
       </c>
       <c r="J58" t="s">
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L58" t="s">
         <v>7</v>
@@ -4139,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2">
-        <v>46065</v>
+        <v>46085</v>
       </c>
       <c r="P58" t="s">
         <v>7</v>
@@ -4153,22 +3994,22 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G59" t="s">
         <v>2</v>
@@ -4177,13 +4018,13 @@
         <v>14</v>
       </c>
       <c r="I59" s="2">
-        <v>46125</v>
+        <v>46097</v>
       </c>
       <c r="J59" t="s">
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L59" t="s">
         <v>7</v>
@@ -4195,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="2">
-        <v>46065</v>
+        <v>46085</v>
       </c>
       <c r="P59" t="s">
         <v>7</v>
@@ -4209,22 +4050,22 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F60" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G60" t="s">
         <v>2</v>
@@ -4233,13 +4074,13 @@
         <v>6</v>
       </c>
       <c r="I60" s="2">
-        <v>46128</v>
+        <v>46097</v>
       </c>
       <c r="J60" t="s">
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L60" t="s">
         <v>7</v>
@@ -4251,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="2">
-        <v>46065</v>
+        <v>46084</v>
       </c>
       <c r="P60" t="s">
         <v>7</v>
@@ -4265,10 +4106,10 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
@@ -4277,16 +4118,16 @@
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G61" t="s">
         <v>2</v>
       </c>
       <c r="H61" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I61" s="2">
         <v>46100</v>
@@ -4295,7 +4136,7 @@
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>168</v>
+        <v>27</v>
       </c>
       <c r="L61" t="s">
         <v>7</v>
@@ -4307,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="P61" t="s">
         <v>7</v>
@@ -4321,37 +4162,37 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C62" t="s">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="F62" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G62" t="s">
         <v>2</v>
       </c>
       <c r="H62" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I62" s="2">
-        <v>46101</v>
+        <v>46084</v>
       </c>
       <c r="J62" t="s">
         <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="L62" t="s">
         <v>7</v>
@@ -4363,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="P62" t="s">
         <v>7</v>
@@ -4377,22 +4218,22 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E63" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="G63" t="s">
         <v>2</v>
@@ -4401,13 +4242,13 @@
         <v>6</v>
       </c>
       <c r="I63" s="2">
-        <v>46163</v>
+        <v>46087</v>
       </c>
       <c r="J63" t="s">
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>168</v>
+        <v>35</v>
       </c>
       <c r="L63" t="s">
         <v>7</v>
@@ -4419,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="P63" t="s">
         <v>7</v>
@@ -4433,10 +4274,10 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
@@ -4445,26 +4286,26 @@
         <v>3</v>
       </c>
       <c r="E64" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" t="s">
+        <v>2</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="2">
+        <v>46167</v>
+      </c>
+      <c r="J64" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" t="s">
         <v>166</v>
       </c>
-      <c r="F64" t="s">
-        <v>177</v>
-      </c>
-      <c r="G64" t="s">
-        <v>2</v>
-      </c>
-      <c r="H64" t="s">
-        <v>6</v>
-      </c>
-      <c r="I64" s="2">
-        <v>46163</v>
-      </c>
-      <c r="J64" t="s">
-        <v>7</v>
-      </c>
-      <c r="K64" t="s">
-        <v>168</v>
-      </c>
       <c r="L64" t="s">
         <v>7</v>
       </c>
@@ -4475,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P64" t="s">
         <v>7</v>
@@ -4489,10 +4330,10 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B65" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C65" t="s">
         <v>2</v>
@@ -4501,10 +4342,10 @@
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="F65" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G65" t="s">
         <v>2</v>
@@ -4513,25 +4354,25 @@
         <v>6</v>
       </c>
       <c r="I65" s="2">
-        <v>46213</v>
+        <v>46170</v>
       </c>
       <c r="J65" t="s">
         <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L65" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M65" s="3">
         <v>1</v>
       </c>
       <c r="N65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P65" t="s">
         <v>7</v>
@@ -4540,15 +4381,15 @@
         <v>7</v>
       </c>
       <c r="R65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
@@ -4557,25 +4398,25 @@
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>166</v>
+        <v>4</v>
       </c>
       <c r="F66" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G66" t="s">
         <v>2</v>
       </c>
       <c r="H66" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I66" s="2">
-        <v>46213</v>
+        <v>46167</v>
       </c>
       <c r="J66" t="s">
         <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="L66" t="s">
         <v>7</v>
@@ -4587,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P66" t="s">
         <v>7</v>
@@ -4601,10 +4442,10 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -4613,10 +4454,10 @@
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="G67" t="s">
         <v>2</v>
@@ -4625,13 +4466,13 @@
         <v>6</v>
       </c>
       <c r="I67" s="2">
-        <v>46252</v>
+        <v>46183</v>
       </c>
       <c r="J67" t="s">
         <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="L67" t="s">
         <v>7</v>
@@ -4643,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P67" t="s">
         <v>7</v>
@@ -4657,10 +4498,10 @@
     </row>
     <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B68" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
@@ -4669,25 +4510,25 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="G68" t="s">
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I68" s="2">
-        <v>46252</v>
+        <v>46183</v>
       </c>
       <c r="J68" t="s">
         <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="L68" t="s">
         <v>7</v>
@@ -4699,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P68" t="s">
         <v>7</v>
@@ -4713,10 +4554,10 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B69" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C69" t="s">
         <v>2</v>
@@ -4728,22 +4569,22 @@
         <v>4</v>
       </c>
       <c r="F69" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="G69" t="s">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I69" s="2">
-        <v>46083</v>
+        <v>46153</v>
       </c>
       <c r="J69" t="s">
         <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="L69" t="s">
         <v>7</v>
@@ -4755,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P69" t="s">
         <v>7</v>
@@ -4769,10 +4610,10 @@
     </row>
     <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B70" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
@@ -4781,25 +4622,25 @@
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G70" t="s">
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I70" s="2">
-        <v>46084</v>
+        <v>46169</v>
       </c>
       <c r="J70" t="s">
         <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="L70" t="s">
         <v>7</v>
@@ -4811,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P70" t="s">
         <v>7</v>
@@ -4825,10 +4666,10 @@
     </row>
     <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B71" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C71" t="s">
         <v>2</v>
@@ -4837,10 +4678,10 @@
         <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F71" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G71" t="s">
         <v>2</v>
@@ -4849,13 +4690,13 @@
         <v>14</v>
       </c>
       <c r="I71" s="2">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="J71" t="s">
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="L71" t="s">
         <v>7</v>
@@ -4867,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P71" t="s">
         <v>7</v>
@@ -4876,1070 +4717,6 @@
         <v>7</v>
       </c>
       <c r="R71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18">
-      <c r="A72" t="s">
-        <v>190</v>
-      </c>
-      <c r="B72" t="s">
-        <v>197</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" t="s">
-        <v>21</v>
-      </c>
-      <c r="F72" t="s">
-        <v>198</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2</v>
-      </c>
-      <c r="H72" t="s">
-        <v>6</v>
-      </c>
-      <c r="I72" s="2">
-        <v>46097</v>
-      </c>
-      <c r="J72" t="s">
-        <v>7</v>
-      </c>
-      <c r="K72" t="s">
-        <v>23</v>
-      </c>
-      <c r="L72" t="s">
-        <v>7</v>
-      </c>
-      <c r="M72" s="3">
-        <v>1</v>
-      </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P72" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>7</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
-      <c r="A73" t="s">
-        <v>190</v>
-      </c>
-      <c r="B73" t="s">
-        <v>199</v>
-      </c>
-      <c r="C73" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" t="s">
-        <v>3</v>
-      </c>
-      <c r="E73" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" t="s">
-        <v>200</v>
-      </c>
-      <c r="G73" t="s">
-        <v>2</v>
-      </c>
-      <c r="H73" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" s="2">
-        <v>46100</v>
-      </c>
-      <c r="J73" t="s">
-        <v>7</v>
-      </c>
-      <c r="K73" t="s">
-        <v>27</v>
-      </c>
-      <c r="L73" t="s">
-        <v>7</v>
-      </c>
-      <c r="M73" s="3">
-        <v>1</v>
-      </c>
-      <c r="N73" s="3">
-        <v>0</v>
-      </c>
-      <c r="O73" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P73" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>7</v>
-      </c>
-      <c r="R73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
-      <c r="A74" t="s">
-        <v>190</v>
-      </c>
-      <c r="B74" t="s">
-        <v>201</v>
-      </c>
-      <c r="C74" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" t="s">
-        <v>29</v>
-      </c>
-      <c r="E74" t="s">
-        <v>30</v>
-      </c>
-      <c r="F74" t="s">
-        <v>202</v>
-      </c>
-      <c r="G74" t="s">
-        <v>2</v>
-      </c>
-      <c r="H74" t="s">
-        <v>14</v>
-      </c>
-      <c r="I74" s="2">
-        <v>46083</v>
-      </c>
-      <c r="J74" t="s">
-        <v>7</v>
-      </c>
-      <c r="K74" t="s">
-        <v>32</v>
-      </c>
-      <c r="L74" t="s">
-        <v>7</v>
-      </c>
-      <c r="M74" s="3">
-        <v>1</v>
-      </c>
-      <c r="N74" s="3">
-        <v>0</v>
-      </c>
-      <c r="O74" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P74" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>7</v>
-      </c>
-      <c r="R74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18">
-      <c r="A75" t="s">
-        <v>190</v>
-      </c>
-      <c r="B75" t="s">
-        <v>203</v>
-      </c>
-      <c r="C75" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" t="s">
-        <v>29</v>
-      </c>
-      <c r="E75" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" t="s">
-        <v>204</v>
-      </c>
-      <c r="G75" t="s">
-        <v>2</v>
-      </c>
-      <c r="H75" t="s">
-        <v>6</v>
-      </c>
-      <c r="I75" s="2">
-        <v>46086</v>
-      </c>
-      <c r="J75" t="s">
-        <v>7</v>
-      </c>
-      <c r="K75" t="s">
-        <v>35</v>
-      </c>
-      <c r="L75" t="s">
-        <v>7</v>
-      </c>
-      <c r="M75" s="3">
-        <v>1</v>
-      </c>
-      <c r="N75" s="3">
-        <v>0</v>
-      </c>
-      <c r="O75" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P75" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>7</v>
-      </c>
-      <c r="R75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18">
-      <c r="A76" t="s">
-        <v>205</v>
-      </c>
-      <c r="B76" t="s">
-        <v>206</v>
-      </c>
-      <c r="C76" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>4</v>
-      </c>
-      <c r="F76" t="s">
-        <v>207</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2</v>
-      </c>
-      <c r="H76" t="s">
-        <v>6</v>
-      </c>
-      <c r="I76" s="2">
-        <v>46085</v>
-      </c>
-      <c r="J76" t="s">
-        <v>7</v>
-      </c>
-      <c r="K76" t="s">
-        <v>8</v>
-      </c>
-      <c r="L76" t="s">
-        <v>7</v>
-      </c>
-      <c r="M76" s="3">
-        <v>1</v>
-      </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P76" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>7</v>
-      </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" t="s">
-        <v>205</v>
-      </c>
-      <c r="B77" t="s">
-        <v>208</v>
-      </c>
-      <c r="C77" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" t="s">
-        <v>3</v>
-      </c>
-      <c r="E77" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" t="s">
-        <v>209</v>
-      </c>
-      <c r="G77" t="s">
-        <v>2</v>
-      </c>
-      <c r="H77" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" s="2">
-        <v>46086</v>
-      </c>
-      <c r="J77" t="s">
-        <v>7</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" t="s">
-        <v>7</v>
-      </c>
-      <c r="M77" s="3">
-        <v>1</v>
-      </c>
-      <c r="N77" s="3">
-        <v>0</v>
-      </c>
-      <c r="O77" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P77" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>7</v>
-      </c>
-      <c r="R77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18">
-      <c r="A78" t="s">
-        <v>205</v>
-      </c>
-      <c r="B78" t="s">
-        <v>210</v>
-      </c>
-      <c r="C78" t="s">
-        <v>2</v>
-      </c>
-      <c r="D78" t="s">
-        <v>3</v>
-      </c>
-      <c r="E78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F78" t="s">
-        <v>211</v>
-      </c>
-      <c r="G78" t="s">
-        <v>2</v>
-      </c>
-      <c r="H78" t="s">
-        <v>14</v>
-      </c>
-      <c r="I78" s="2">
-        <v>46098</v>
-      </c>
-      <c r="J78" t="s">
-        <v>7</v>
-      </c>
-      <c r="K78" t="s">
-        <v>19</v>
-      </c>
-      <c r="L78" t="s">
-        <v>7</v>
-      </c>
-      <c r="M78" s="3">
-        <v>1</v>
-      </c>
-      <c r="N78" s="3">
-        <v>0</v>
-      </c>
-      <c r="O78" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P78" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>7</v>
-      </c>
-      <c r="R78" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18">
-      <c r="A79" t="s">
-        <v>205</v>
-      </c>
-      <c r="B79" t="s">
-        <v>212</v>
-      </c>
-      <c r="C79" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" t="s">
-        <v>3</v>
-      </c>
-      <c r="E79" t="s">
-        <v>21</v>
-      </c>
-      <c r="F79" t="s">
-        <v>213</v>
-      </c>
-      <c r="G79" t="s">
-        <v>2</v>
-      </c>
-      <c r="H79" t="s">
-        <v>6</v>
-      </c>
-      <c r="I79" s="2">
-        <v>46098</v>
-      </c>
-      <c r="J79" t="s">
-        <v>7</v>
-      </c>
-      <c r="K79" t="s">
-        <v>23</v>
-      </c>
-      <c r="L79" t="s">
-        <v>7</v>
-      </c>
-      <c r="M79" s="3">
-        <v>1</v>
-      </c>
-      <c r="N79" s="3">
-        <v>0</v>
-      </c>
-      <c r="O79" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P79" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>7</v>
-      </c>
-      <c r="R79" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18">
-      <c r="A80" t="s">
-        <v>205</v>
-      </c>
-      <c r="B80" t="s">
-        <v>214</v>
-      </c>
-      <c r="C80" t="s">
-        <v>2</v>
-      </c>
-      <c r="D80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E80" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" t="s">
-        <v>215</v>
-      </c>
-      <c r="G80" t="s">
-        <v>2</v>
-      </c>
-      <c r="H80" t="s">
-        <v>14</v>
-      </c>
-      <c r="I80" s="2">
-        <v>46101</v>
-      </c>
-      <c r="J80" t="s">
-        <v>7</v>
-      </c>
-      <c r="K80" t="s">
-        <v>27</v>
-      </c>
-      <c r="L80" t="s">
-        <v>7</v>
-      </c>
-      <c r="M80" s="3">
-        <v>1</v>
-      </c>
-      <c r="N80" s="3">
-        <v>0</v>
-      </c>
-      <c r="O80" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P80" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>7</v>
-      </c>
-      <c r="R80" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18">
-      <c r="A81" t="s">
-        <v>205</v>
-      </c>
-      <c r="B81" t="s">
-        <v>216</v>
-      </c>
-      <c r="C81" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" t="s">
-        <v>29</v>
-      </c>
-      <c r="E81" t="s">
-        <v>30</v>
-      </c>
-      <c r="F81" t="s">
-        <v>217</v>
-      </c>
-      <c r="G81" t="s">
-        <v>2</v>
-      </c>
-      <c r="H81" t="s">
-        <v>14</v>
-      </c>
-      <c r="I81" s="2">
-        <v>46085</v>
-      </c>
-      <c r="J81" t="s">
-        <v>7</v>
-      </c>
-      <c r="K81" t="s">
-        <v>32</v>
-      </c>
-      <c r="L81" t="s">
-        <v>7</v>
-      </c>
-      <c r="M81" s="3">
-        <v>1</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P81" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>7</v>
-      </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18">
-      <c r="A82" t="s">
-        <v>205</v>
-      </c>
-      <c r="B82" t="s">
-        <v>218</v>
-      </c>
-      <c r="C82" t="s">
-        <v>2</v>
-      </c>
-      <c r="D82" t="s">
-        <v>29</v>
-      </c>
-      <c r="E82" t="s">
-        <v>17</v>
-      </c>
-      <c r="F82" t="s">
-        <v>219</v>
-      </c>
-      <c r="G82" t="s">
-        <v>2</v>
-      </c>
-      <c r="H82" t="s">
-        <v>6</v>
-      </c>
-      <c r="I82" s="2">
-        <v>46090</v>
-      </c>
-      <c r="J82" t="s">
-        <v>7</v>
-      </c>
-      <c r="K82" t="s">
-        <v>35</v>
-      </c>
-      <c r="L82" t="s">
-        <v>7</v>
-      </c>
-      <c r="M82" s="3">
-        <v>1</v>
-      </c>
-      <c r="N82" s="3">
-        <v>0</v>
-      </c>
-      <c r="O82" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P82" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>7</v>
-      </c>
-      <c r="R82" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18">
-      <c r="A83" t="s">
-        <v>220</v>
-      </c>
-      <c r="B83" t="s">
-        <v>221</v>
-      </c>
-      <c r="C83" t="s">
-        <v>2</v>
-      </c>
-      <c r="D83" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" t="s">
-        <v>222</v>
-      </c>
-      <c r="G83" t="s">
-        <v>2</v>
-      </c>
-      <c r="H83" t="s">
-        <v>14</v>
-      </c>
-      <c r="I83" s="2">
-        <v>46045</v>
-      </c>
-      <c r="J83" t="s">
-        <v>7</v>
-      </c>
-      <c r="K83" t="s">
-        <v>15</v>
-      </c>
-      <c r="L83" t="s">
-        <v>7</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="2">
-        <v>46056</v>
-      </c>
-      <c r="P83" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>7</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18">
-      <c r="A84" t="s">
-        <v>220</v>
-      </c>
-      <c r="B84" t="s">
-        <v>221</v>
-      </c>
-      <c r="C84" t="s">
-        <v>74</v>
-      </c>
-      <c r="D84" t="s">
-        <v>3</v>
-      </c>
-      <c r="E84" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" t="s">
-        <v>224</v>
-      </c>
-      <c r="G84" t="s">
-        <v>2</v>
-      </c>
-      <c r="H84" t="s">
-        <v>14</v>
-      </c>
-      <c r="I84" s="2">
-        <v>46057</v>
-      </c>
-      <c r="J84" t="s">
-        <v>7</v>
-      </c>
-      <c r="K84" t="s">
-        <v>19</v>
-      </c>
-      <c r="L84" t="s">
-        <v>7</v>
-      </c>
-      <c r="M84" s="3">
-        <v>1</v>
-      </c>
-      <c r="N84" s="3">
-        <v>0</v>
-      </c>
-      <c r="O84" s="2">
-        <v>46056</v>
-      </c>
-      <c r="P84" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>7</v>
-      </c>
-      <c r="R84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18">
-      <c r="A85" t="s">
-        <v>220</v>
-      </c>
-      <c r="B85" t="s">
-        <v>225</v>
-      </c>
-      <c r="C85" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" t="s">
-        <v>3</v>
-      </c>
-      <c r="E85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F85" t="s">
-        <v>226</v>
-      </c>
-      <c r="G85" t="s">
-        <v>2</v>
-      </c>
-      <c r="H85" t="s">
-        <v>6</v>
-      </c>
-      <c r="I85" s="2">
-        <v>46057</v>
-      </c>
-      <c r="J85" t="s">
-        <v>7</v>
-      </c>
-      <c r="K85" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85" t="s">
-        <v>7</v>
-      </c>
-      <c r="M85" s="3">
-        <v>1</v>
-      </c>
-      <c r="N85" s="3">
-        <v>0</v>
-      </c>
-      <c r="O85" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P85" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>7</v>
-      </c>
-      <c r="R85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18">
-      <c r="A86" t="s">
-        <v>220</v>
-      </c>
-      <c r="B86" t="s">
-        <v>221</v>
-      </c>
-      <c r="C86" t="s">
-        <v>227</v>
-      </c>
-      <c r="D86" t="s">
-        <v>3</v>
-      </c>
-      <c r="E86" t="s">
-        <v>25</v>
-      </c>
-      <c r="F86" t="s">
-        <v>228</v>
-      </c>
-      <c r="G86" t="s">
-        <v>2</v>
-      </c>
-      <c r="H86" t="s">
-        <v>14</v>
-      </c>
-      <c r="I86" s="2">
-        <v>46062</v>
-      </c>
-      <c r="J86" t="s">
-        <v>7</v>
-      </c>
-      <c r="K86" t="s">
-        <v>27</v>
-      </c>
-      <c r="L86" t="s">
-        <v>7</v>
-      </c>
-      <c r="M86" s="3">
-        <v>1</v>
-      </c>
-      <c r="N86" s="3">
-        <v>0</v>
-      </c>
-      <c r="O86" s="2">
-        <v>46056</v>
-      </c>
-      <c r="P86" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>7</v>
-      </c>
-      <c r="R86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18">
-      <c r="A87" t="s">
-        <v>220</v>
-      </c>
-      <c r="B87" t="s">
-        <v>221</v>
-      </c>
-      <c r="C87" t="s">
-        <v>229</v>
-      </c>
-      <c r="D87" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" t="s">
-        <v>30</v>
-      </c>
-      <c r="F87" t="s">
-        <v>230</v>
-      </c>
-      <c r="G87" t="s">
-        <v>2</v>
-      </c>
-      <c r="H87" t="s">
-        <v>14</v>
-      </c>
-      <c r="I87" s="2">
-        <v>46044</v>
-      </c>
-      <c r="J87" t="s">
-        <v>7</v>
-      </c>
-      <c r="K87" t="s">
-        <v>32</v>
-      </c>
-      <c r="L87" t="s">
-        <v>7</v>
-      </c>
-      <c r="M87" s="3">
-        <v>1</v>
-      </c>
-      <c r="N87" s="3">
-        <v>0</v>
-      </c>
-      <c r="O87" s="2">
-        <v>46056</v>
-      </c>
-      <c r="P87" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>7</v>
-      </c>
-      <c r="R87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18">
-      <c r="A88" t="s">
-        <v>220</v>
-      </c>
-      <c r="B88" t="s">
-        <v>225</v>
-      </c>
-      <c r="C88" t="s">
-        <v>74</v>
-      </c>
-      <c r="D88" t="s">
-        <v>29</v>
-      </c>
-      <c r="E88" t="s">
-        <v>17</v>
-      </c>
-      <c r="F88" t="s">
-        <v>231</v>
-      </c>
-      <c r="G88" t="s">
-        <v>2</v>
-      </c>
-      <c r="H88" t="s">
-        <v>6</v>
-      </c>
-      <c r="I88" s="2">
-        <v>46050</v>
-      </c>
-      <c r="J88" t="s">
-        <v>7</v>
-      </c>
-      <c r="K88" t="s">
-        <v>35</v>
-      </c>
-      <c r="L88" t="s">
-        <v>7</v>
-      </c>
-      <c r="M88" s="3">
-        <v>1</v>
-      </c>
-      <c r="N88" s="3">
-        <v>0</v>
-      </c>
-      <c r="O88" s="2">
-        <v>46038</v>
-      </c>
-      <c r="P88" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>7</v>
-      </c>
-      <c r="R88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18">
-      <c r="A89" t="s">
-        <v>232</v>
-      </c>
-      <c r="B89" t="s">
-        <v>233</v>
-      </c>
-      <c r="C89" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" t="s">
-        <v>60</v>
-      </c>
-      <c r="F89" t="s">
-        <v>234</v>
-      </c>
-      <c r="G89" t="s">
-        <v>2</v>
-      </c>
-      <c r="H89" t="s">
-        <v>62</v>
-      </c>
-      <c r="I89" s="2">
-        <v>46090</v>
-      </c>
-      <c r="J89" t="s">
-        <v>7</v>
-      </c>
-      <c r="K89" t="s">
-        <v>63</v>
-      </c>
-      <c r="L89" t="s">
-        <v>7</v>
-      </c>
-      <c r="M89" s="3">
-        <v>1</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="2">
-        <v>46079</v>
-      </c>
-      <c r="P89" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>7</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18">
-      <c r="A90" t="s">
-        <v>232</v>
-      </c>
-      <c r="B90" t="s">
-        <v>235</v>
-      </c>
-      <c r="C90" t="s">
-        <v>2</v>
-      </c>
-      <c r="D90" t="s">
-        <v>3</v>
-      </c>
-      <c r="E90" t="s">
-        <v>65</v>
-      </c>
-      <c r="F90" t="s">
-        <v>236</v>
-      </c>
-      <c r="G90" t="s">
-        <v>2</v>
-      </c>
-      <c r="H90" t="s">
-        <v>6</v>
-      </c>
-      <c r="I90" s="2">
-        <v>46092</v>
-      </c>
-      <c r="J90" t="s">
-        <v>7</v>
-      </c>
-      <c r="K90" t="s">
-        <v>67</v>
-      </c>
-      <c r="L90" t="s">
-        <v>7</v>
-      </c>
-      <c r="M90" s="3">
-        <v>1</v>
-      </c>
-      <c r="N90" s="3">
-        <v>0</v>
-      </c>
-      <c r="O90" s="2">
-        <v>46083</v>
-      </c>
-      <c r="P90" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>7</v>
-      </c>
-      <c r="R90" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="215">
   <si>
     <t>200006254</t>
   </si>
@@ -310,6 +310,30 @@
     <t>1400097436</t>
   </si>
   <si>
+    <t>1400097110</t>
+  </si>
+  <si>
+    <t>0191</t>
+  </si>
+  <si>
+    <t>1400101049</t>
+  </si>
+  <si>
+    <t>鏟花八小時</t>
+  </si>
+  <si>
+    <t>1400097074</t>
+  </si>
+  <si>
+    <t>0192</t>
+  </si>
+  <si>
+    <t>1400101050</t>
+  </si>
+  <si>
+    <t>噴漆二小時</t>
+  </si>
+  <si>
     <t>1400093599</t>
   </si>
   <si>
@@ -563,6 +587,21 @@
   </si>
   <si>
     <t>1400098799</t>
+  </si>
+  <si>
+    <t>200006701</t>
+  </si>
+  <si>
+    <t>1400097113</t>
+  </si>
+  <si>
+    <t>0070</t>
+  </si>
+  <si>
+    <t>1400101107</t>
+  </si>
+  <si>
+    <t>機頭精度檢驗</t>
   </si>
   <si>
     <t>訂單</t>
@@ -721,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -746,58 +785,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2603,49 +2642,49 @@
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I34" s="2">
-        <v>46119</v>
+        <v>46139</v>
       </c>
       <c r="J34" t="s">
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="L34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M34" s="3">
         <v>1</v>
       </c>
       <c r="N34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>46125</v>
+        <v>46140</v>
       </c>
       <c r="P34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2653,46 +2692,46 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="F35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G35" t="s">
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="J35" t="s">
         <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="L35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M35" s="3">
         <v>1</v>
       </c>
       <c r="N35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2">
-        <v>46065</v>
+        <v>46140</v>
       </c>
       <c r="P35" t="s">
         <v>7</v>
@@ -2701,42 +2740,42 @@
         <v>7</v>
       </c>
       <c r="R35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I36" s="2">
-        <v>46122</v>
+        <v>46119</v>
       </c>
       <c r="J36" t="s">
         <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L36" t="s">
         <v>9</v>
@@ -2748,13 +2787,13 @@
         <v>1</v>
       </c>
       <c r="O36" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R36" s="3">
         <v>1</v>
@@ -2762,37 +2801,37 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="J37" t="s">
         <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L37" t="s">
         <v>9</v>
@@ -2804,13 +2843,13 @@
         <v>1</v>
       </c>
       <c r="O37" s="2">
-        <v>46125</v>
+        <v>46065</v>
       </c>
       <c r="P37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R37" s="3">
         <v>1</v>
@@ -2818,10 +2857,10 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -2830,25 +2869,25 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I38" s="2">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="J38" t="s">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L38" t="s">
         <v>9</v>
@@ -2860,13 +2899,13 @@
         <v>1</v>
       </c>
       <c r="O38" s="2">
-        <v>46125</v>
+        <v>46065</v>
       </c>
       <c r="P38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R38" s="3">
         <v>1</v>
@@ -2874,10 +2913,10 @@
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
@@ -2886,25 +2925,25 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I39" s="2">
-        <v>46133</v>
+        <v>46125</v>
       </c>
       <c r="J39" t="s">
         <v>7</v>
       </c>
       <c r="K39" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L39" t="s">
         <v>9</v>
@@ -2916,13 +2955,13 @@
         <v>1</v>
       </c>
       <c r="O39" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P39" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R39" s="3">
         <v>1</v>
@@ -2930,10 +2969,10 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
@@ -2942,10 +2981,10 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
@@ -2954,13 +2993,13 @@
         <v>14</v>
       </c>
       <c r="I40" s="2">
-        <v>46136</v>
+        <v>46133</v>
       </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L40" t="s">
         <v>9</v>
@@ -2986,37 +3025,37 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F41" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G41" t="s">
         <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I41" s="2">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="J41" t="s">
         <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L41" t="s">
         <v>9</v>
@@ -3028,13 +3067,13 @@
         <v>1</v>
       </c>
       <c r="O41" s="2">
-        <v>46125</v>
+        <v>46065</v>
       </c>
       <c r="P41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R41" s="3">
         <v>1</v>
@@ -3042,37 +3081,37 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G42" t="s">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="J42" t="s">
         <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L42" t="s">
         <v>9</v>
@@ -3084,13 +3123,13 @@
         <v>1</v>
       </c>
       <c r="O42" s="2">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="P42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R42" s="3">
         <v>1</v>
@@ -3098,105 +3137,105 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G43" t="s">
         <v>2</v>
       </c>
       <c r="H43" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I43" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="J43" t="s">
         <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M43" s="3">
         <v>1</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="P43" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G44" t="s">
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I44" s="2">
-        <v>46084</v>
+        <v>46128</v>
       </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L44" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M44" s="3">
         <v>1</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2">
-        <v>46083</v>
+        <v>46065</v>
       </c>
       <c r="P44" t="s">
         <v>7</v>
@@ -3205,15 +3244,15 @@
         <v>7</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -3222,25 +3261,25 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G45" t="s">
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I45" s="2">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="J45" t="s">
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L45" t="s">
         <v>7</v>
@@ -3266,10 +3305,10 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
@@ -3278,25 +3317,25 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G46" t="s">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I46" s="2">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L46" t="s">
         <v>7</v>
@@ -3322,10 +3361,10 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
@@ -3334,10 +3373,10 @@
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
@@ -3346,13 +3385,13 @@
         <v>14</v>
       </c>
       <c r="I47" s="2">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L47" t="s">
         <v>7</v>
@@ -3378,37 +3417,37 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I48" s="2">
-        <v>46083</v>
+        <v>46097</v>
       </c>
       <c r="J48" t="s">
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L48" t="s">
         <v>7</v>
@@ -3434,37 +3473,37 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I49" s="2">
-        <v>46086</v>
+        <v>46100</v>
       </c>
       <c r="J49" t="s">
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L49" t="s">
         <v>7</v>
@@ -3490,37 +3529,37 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E50" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I50" s="2">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="J50" t="s">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L50" t="s">
         <v>7</v>
@@ -3546,28 +3585,28 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I51" s="2">
         <v>46086</v>
@@ -3576,7 +3615,7 @@
         <v>7</v>
       </c>
       <c r="K51" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L51" t="s">
         <v>7</v>
@@ -3602,10 +3641,10 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
@@ -3614,25 +3653,25 @@
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I52" s="2">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="J52" t="s">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L52" t="s">
         <v>7</v>
@@ -3658,10 +3697,10 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
@@ -3670,25 +3709,25 @@
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
       </c>
       <c r="H53" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I53" s="2">
-        <v>46098</v>
+        <v>46086</v>
       </c>
       <c r="J53" t="s">
         <v>7</v>
       </c>
       <c r="K53" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L53" t="s">
         <v>7</v>
@@ -3714,10 +3753,10 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
         <v>2</v>
@@ -3726,10 +3765,10 @@
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G54" t="s">
         <v>2</v>
@@ -3738,13 +3777,13 @@
         <v>14</v>
       </c>
       <c r="I54" s="2">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="J54" t="s">
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L54" t="s">
         <v>7</v>
@@ -3770,37 +3809,37 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F55" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G55" t="s">
         <v>2</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I55" s="2">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="J55" t="s">
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L55" t="s">
         <v>7</v>
@@ -3826,37 +3865,37 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C56" t="s">
         <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G56" t="s">
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I56" s="2">
-        <v>46090</v>
+        <v>46101</v>
       </c>
       <c r="J56" t="s">
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L56" t="s">
         <v>7</v>
@@ -3882,37 +3921,37 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
         <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F57" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G57" t="s">
         <v>2</v>
       </c>
       <c r="H57" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I57" s="2">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="J57" t="s">
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L57" t="s">
         <v>7</v>
@@ -3924,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="2">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="P57" t="s">
         <v>7</v>
@@ -3938,37 +3977,37 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G58" t="s">
         <v>2</v>
       </c>
       <c r="H58" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I58" s="2">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="J58" t="s">
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L58" t="s">
         <v>7</v>
@@ -3980,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="P58" t="s">
         <v>7</v>
@@ -3994,10 +4033,10 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
@@ -4006,25 +4045,25 @@
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G59" t="s">
         <v>2</v>
       </c>
       <c r="H59" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I59" s="2">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="J59" t="s">
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L59" t="s">
         <v>7</v>
@@ -4036,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="2">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="P59" t="s">
         <v>7</v>
@@ -4050,10 +4089,10 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
         <v>2</v>
@@ -4062,25 +4101,25 @@
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G60" t="s">
         <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I60" s="2">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="J60" t="s">
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L60" t="s">
         <v>7</v>
@@ -4092,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="2">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="P60" t="s">
         <v>7</v>
@@ -4106,10 +4145,10 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
@@ -4118,10 +4157,10 @@
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G61" t="s">
         <v>2</v>
@@ -4130,13 +4169,13 @@
         <v>14</v>
       </c>
       <c r="I61" s="2">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="J61" t="s">
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L61" t="s">
         <v>7</v>
@@ -4162,49 +4201,49 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F62" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G62" t="s">
         <v>2</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I62" s="2">
+        <v>46097</v>
+      </c>
+      <c r="J62" t="s">
+        <v>7</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>7</v>
+      </c>
+      <c r="M62" s="3">
+        <v>1</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2">
         <v>46084</v>
-      </c>
-      <c r="J62" t="s">
-        <v>7</v>
-      </c>
-      <c r="K62" t="s">
-        <v>32</v>
-      </c>
-      <c r="L62" t="s">
-        <v>7</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="2">
-        <v>46085</v>
       </c>
       <c r="P62" t="s">
         <v>7</v>
@@ -4218,37 +4257,37 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F63" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G63" t="s">
         <v>2</v>
       </c>
       <c r="H63" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I63" s="2">
-        <v>46087</v>
+        <v>46100</v>
       </c>
       <c r="J63" t="s">
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L63" t="s">
         <v>7</v>
@@ -4260,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="2">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="P63" t="s">
         <v>7</v>
@@ -4274,22 +4313,22 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F64" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G64" t="s">
         <v>2</v>
@@ -4298,13 +4337,13 @@
         <v>14</v>
       </c>
       <c r="I64" s="2">
-        <v>46167</v>
+        <v>46084</v>
       </c>
       <c r="J64" t="s">
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="L64" t="s">
         <v>7</v>
@@ -4316,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="2">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="P64" t="s">
         <v>7</v>
@@ -4330,22 +4369,22 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C65" t="s">
         <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G65" t="s">
         <v>2</v>
@@ -4354,25 +4393,25 @@
         <v>6</v>
       </c>
       <c r="I65" s="2">
-        <v>46170</v>
+        <v>46087</v>
       </c>
       <c r="J65" t="s">
         <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>169</v>
+        <v>35</v>
       </c>
       <c r="L65" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M65" s="3">
         <v>1</v>
       </c>
       <c r="N65" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="2">
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="P65" t="s">
         <v>7</v>
@@ -4381,15 +4420,15 @@
         <v>7</v>
       </c>
       <c r="R65" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
@@ -4401,7 +4440,7 @@
         <v>4</v>
       </c>
       <c r="F66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G66" t="s">
         <v>2</v>
@@ -4416,7 +4455,7 @@
         <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s">
         <v>7</v>
@@ -4442,10 +4481,10 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -4454,10 +4493,10 @@
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F67" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G67" t="s">
         <v>2</v>
@@ -4466,22 +4505,22 @@
         <v>6</v>
       </c>
       <c r="I67" s="2">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="J67" t="s">
         <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>63</v>
+        <v>177</v>
       </c>
       <c r="L67" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M67" s="3">
         <v>1</v>
       </c>
       <c r="N67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="2">
         <v>46086</v>
@@ -4493,15 +4532,15 @@
         <v>7</v>
       </c>
       <c r="R67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
@@ -4510,10 +4549,10 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F68" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G68" t="s">
         <v>2</v>
@@ -4522,13 +4561,13 @@
         <v>14</v>
       </c>
       <c r="I68" s="2">
-        <v>46183</v>
+        <v>46167</v>
       </c>
       <c r="J68" t="s">
         <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="L68" t="s">
         <v>7</v>
@@ -4554,10 +4593,10 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B69" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C69" t="s">
         <v>2</v>
@@ -4566,25 +4605,25 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F69" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G69" t="s">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I69" s="2">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="J69" t="s">
         <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="L69" t="s">
         <v>7</v>
@@ -4610,10 +4649,10 @@
     </row>
     <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B70" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
@@ -4622,25 +4661,25 @@
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F70" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G70" t="s">
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I70" s="2">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="J70" t="s">
         <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L70" t="s">
         <v>7</v>
@@ -4666,10 +4705,10 @@
     </row>
     <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B71" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s">
         <v>2</v>
@@ -4678,10 +4717,10 @@
         <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F71" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G71" t="s">
         <v>2</v>
@@ -4690,13 +4729,13 @@
         <v>14</v>
       </c>
       <c r="I71" s="2">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="J71" t="s">
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="L71" t="s">
         <v>7</v>
@@ -4717,6 +4756,174 @@
         <v>7</v>
       </c>
       <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>61</v>
+      </c>
+      <c r="F72" t="s">
+        <v>189</v>
+      </c>
+      <c r="G72" t="s">
+        <v>2</v>
+      </c>
+      <c r="H72" t="s">
+        <v>6</v>
+      </c>
+      <c r="I72" s="2">
+        <v>46169</v>
+      </c>
+      <c r="J72" t="s">
+        <v>7</v>
+      </c>
+      <c r="K72" t="s">
+        <v>63</v>
+      </c>
+      <c r="L72" t="s">
+        <v>7</v>
+      </c>
+      <c r="M72" s="3">
+        <v>1</v>
+      </c>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2">
+        <v>46086</v>
+      </c>
+      <c r="P72" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>7</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" t="s">
+        <v>190</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>191</v>
+      </c>
+      <c r="G73" t="s">
+        <v>2</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="2">
+        <v>46169</v>
+      </c>
+      <c r="J73" t="s">
+        <v>7</v>
+      </c>
+      <c r="K73" t="s">
+        <v>66</v>
+      </c>
+      <c r="L73" t="s">
+        <v>7</v>
+      </c>
+      <c r="M73" s="3">
+        <v>1</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>46086</v>
+      </c>
+      <c r="P73" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>7</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" t="s">
+        <v>193</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" t="s">
+        <v>194</v>
+      </c>
+      <c r="F74" t="s">
+        <v>195</v>
+      </c>
+      <c r="G74" t="s">
+        <v>2</v>
+      </c>
+      <c r="H74" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="2">
+        <v>46141</v>
+      </c>
+      <c r="J74" t="s">
+        <v>7</v>
+      </c>
+      <c r="K74" t="s">
+        <v>196</v>
+      </c>
+      <c r="L74" t="s">
+        <v>7</v>
+      </c>
+      <c r="M74" s="3">
+        <v>1</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2">
+        <v>46140</v>
+      </c>
+      <c r="P74" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>7</v>
+      </c>
+      <c r="R74" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -2722,13 +2722,13 @@
         <v>106</v>
       </c>
       <c r="L35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M35" s="3">
         <v>1</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2">
         <v>46140</v>
@@ -2740,7 +2740,7 @@
         <v>7</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:18">

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="226">
   <si>
     <t>200006254</t>
   </si>
@@ -602,6 +602,39 @@
   </si>
   <si>
     <t>機頭精度檢驗</t>
+  </si>
+  <si>
+    <t>200006723</t>
+  </si>
+  <si>
+    <t>1400097283</t>
+  </si>
+  <si>
+    <t>1400101237</t>
+  </si>
+  <si>
+    <t>PBM機頭噴漆</t>
+  </si>
+  <si>
+    <t>1400097284</t>
+  </si>
+  <si>
+    <t>1400101238</t>
+  </si>
+  <si>
+    <t>PBM進給座噴漆</t>
+  </si>
+  <si>
+    <t>1400097327</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>1400101239</t>
+  </si>
+  <si>
+    <t>齒輪箱進給座鏟花</t>
   </si>
   <si>
     <t>訂單</t>
@@ -760,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R74"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -785,58 +818,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -4924,6 +4957,174 @@
         <v>7</v>
       </c>
       <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" t="s">
+        <v>199</v>
+      </c>
+      <c r="G75" t="s">
+        <v>2</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="2">
+        <v>46225</v>
+      </c>
+      <c r="J75" t="s">
+        <v>7</v>
+      </c>
+      <c r="K75" t="s">
+        <v>200</v>
+      </c>
+      <c r="L75" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" s="3">
+        <v>1</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P75" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>7</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F76" t="s">
+        <v>202</v>
+      </c>
+      <c r="G76" t="s">
+        <v>2</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="2">
+        <v>46225</v>
+      </c>
+      <c r="J76" t="s">
+        <v>7</v>
+      </c>
+      <c r="K76" t="s">
+        <v>203</v>
+      </c>
+      <c r="L76" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" s="3">
+        <v>1</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P76" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>7</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" t="s">
+        <v>197</v>
+      </c>
+      <c r="B77" t="s">
+        <v>204</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>205</v>
+      </c>
+      <c r="F77" t="s">
+        <v>206</v>
+      </c>
+      <c r="G77" t="s">
+        <v>2</v>
+      </c>
+      <c r="H77" t="s">
+        <v>6</v>
+      </c>
+      <c r="I77" s="2">
+        <v>46247</v>
+      </c>
+      <c r="J77" t="s">
+        <v>7</v>
+      </c>
+      <c r="K77" t="s">
+        <v>207</v>
+      </c>
+      <c r="L77" t="s">
+        <v>7</v>
+      </c>
+      <c r="M77" s="3">
+        <v>1</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P77" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>7</v>
+      </c>
+      <c r="R77" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Newdata/請款.XLSX
+++ b/Newdata/請款.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="209">
   <si>
     <t>200006254</t>
   </si>
@@ -214,427 +214,376 @@
     <t>接頭座噴漆</t>
   </si>
   <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>1400093587</t>
-  </si>
-  <si>
-    <t>1400097411</t>
-  </si>
-  <si>
-    <t>1400093588</t>
-  </si>
-  <si>
-    <t>1400097412</t>
-  </si>
-  <si>
-    <t>1400096378</t>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>1400093601</t>
+  </si>
+  <si>
+    <t>1400097439</t>
+  </si>
+  <si>
+    <t>1400093602</t>
+  </si>
+  <si>
+    <t>1400097440</t>
   </si>
   <si>
     <t>0080</t>
   </si>
   <si>
+    <t>1400097442</t>
+  </si>
+  <si>
+    <t>角度頭墊片研磨</t>
+  </si>
+  <si>
+    <t>1400093603</t>
+  </si>
+  <si>
+    <t>1400097443</t>
+  </si>
+  <si>
+    <t>1400093604</t>
+  </si>
+  <si>
+    <t>1400097444</t>
+  </si>
+  <si>
+    <t>1400093605</t>
+  </si>
+  <si>
+    <t>1400097445</t>
+  </si>
+  <si>
+    <t>1400093606</t>
+  </si>
+  <si>
+    <t>1400097446</t>
+  </si>
+  <si>
+    <t>1400093607</t>
+  </si>
+  <si>
+    <t>1400097447</t>
+  </si>
+  <si>
+    <t>200006567</t>
+  </si>
+  <si>
+    <t>1400094686</t>
+  </si>
+  <si>
+    <t>1400098481</t>
+  </si>
+  <si>
+    <t>1400094161</t>
+  </si>
+  <si>
+    <t>1400098482</t>
+  </si>
+  <si>
+    <t>1400094162</t>
+  </si>
+  <si>
+    <t>1400098485</t>
+  </si>
+  <si>
+    <t>1400094687</t>
+  </si>
+  <si>
+    <t>1400098486</t>
+  </si>
+  <si>
+    <t>1400094163</t>
+  </si>
+  <si>
+    <t>1400098487</t>
+  </si>
+  <si>
+    <t>1400094164</t>
+  </si>
+  <si>
+    <t>1400098488</t>
+  </si>
+  <si>
+    <t>1400094688</t>
+  </si>
+  <si>
+    <t>1400098489</t>
+  </si>
+  <si>
+    <t>200006568</t>
+  </si>
+  <si>
+    <t>1400094691</t>
+  </si>
+  <si>
+    <t>1400098620</t>
+  </si>
+  <si>
+    <t>1400094166</t>
+  </si>
+  <si>
+    <t>1400098621</t>
+  </si>
+  <si>
+    <t>1400094167</t>
+  </si>
+  <si>
+    <t>1400098624</t>
+  </si>
+  <si>
+    <t>1400094692</t>
+  </si>
+  <si>
+    <t>1400098625</t>
+  </si>
+  <si>
+    <t>1400094168</t>
+  </si>
+  <si>
+    <t>1400098626</t>
+  </si>
+  <si>
+    <t>1400094169</t>
+  </si>
+  <si>
+    <t>1400098627</t>
+  </si>
+  <si>
+    <t>1400094693</t>
+  </si>
+  <si>
+    <t>1400098628</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>1400094813</t>
+  </si>
+  <si>
+    <t>1400098691</t>
+  </si>
+  <si>
+    <t>1400094842</t>
+  </si>
+  <si>
+    <t>1400098692</t>
+  </si>
+  <si>
+    <t>1400094843</t>
+  </si>
+  <si>
+    <t>1400098695</t>
+  </si>
+  <si>
+    <t>1400094814</t>
+  </si>
+  <si>
+    <t>1400098696</t>
+  </si>
+  <si>
+    <t>1400094844</t>
+  </si>
+  <si>
+    <t>1400098697</t>
+  </si>
+  <si>
+    <t>1400094845</t>
+  </si>
+  <si>
+    <t>1400098698</t>
+  </si>
+  <si>
+    <t>1400094815</t>
+  </si>
+  <si>
+    <t>1400098699</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>1400094900</t>
+  </si>
+  <si>
+    <t>1400098785</t>
+  </si>
+  <si>
+    <t>M90頭噴漆</t>
+  </si>
+  <si>
+    <t>1400094945</t>
+  </si>
+  <si>
+    <t>1400098786</t>
+  </si>
+  <si>
+    <t>M90頭鏟花</t>
+  </si>
+  <si>
+    <t>200006575</t>
+  </si>
+  <si>
+    <t>1400094901</t>
+  </si>
+  <si>
+    <t>1400098787</t>
+  </si>
+  <si>
+    <t>1400094947</t>
+  </si>
+  <si>
+    <t>1400098800</t>
+  </si>
+  <si>
+    <t>1400094904</t>
+  </si>
+  <si>
+    <t>1400098801</t>
+  </si>
+  <si>
+    <t>200006580</t>
+  </si>
+  <si>
+    <t>1400094902</t>
+  </si>
+  <si>
+    <t>1400098795</t>
+  </si>
+  <si>
+    <t>1400097441</t>
+  </si>
+  <si>
+    <t>1400098797</t>
+  </si>
+  <si>
+    <t>1400094946</t>
+  </si>
+  <si>
+    <t>1400098798</t>
+  </si>
+  <si>
+    <t>1400094903</t>
+  </si>
+  <si>
+    <t>1400098799</t>
+  </si>
+  <si>
+    <t>200006701</t>
+  </si>
+  <si>
+    <t>1400097113</t>
+  </si>
+  <si>
+    <t>0070</t>
+  </si>
+  <si>
+    <t>1400101107</t>
+  </si>
+  <si>
+    <t>機頭精度檢驗</t>
+  </si>
+  <si>
+    <t>200006723</t>
+  </si>
+  <si>
+    <t>1400097283</t>
+  </si>
+  <si>
+    <t>1400101237</t>
+  </si>
+  <si>
+    <t>PBM機頭噴漆</t>
+  </si>
+  <si>
+    <t>1400097284</t>
+  </si>
+  <si>
+    <t>1400101238</t>
+  </si>
+  <si>
+    <t>PBM進給座噴漆</t>
+  </si>
+  <si>
+    <t>1400097327</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>1400101239</t>
+  </si>
+  <si>
+    <t>齒輪箱進給座鏟花</t>
+  </si>
+  <si>
+    <t>200006732</t>
+  </si>
+  <si>
+    <t>1400097413</t>
+  </si>
+  <si>
+    <t>1400101388</t>
+  </si>
+  <si>
+    <t>1400097418</t>
+  </si>
+  <si>
+    <t>1400101411</t>
+  </si>
+  <si>
     <t>1400097414</t>
   </si>
   <si>
-    <t>角度頭墊片研磨</t>
-  </si>
-  <si>
-    <t>1400093589</t>
-  </si>
-  <si>
-    <t>1400097415</t>
-  </si>
-  <si>
-    <t>1400093590</t>
-  </si>
-  <si>
-    <t>1400097416</t>
-  </si>
-  <si>
-    <t>1400093591</t>
-  </si>
-  <si>
-    <t>1400097417</t>
-  </si>
-  <si>
-    <t>1400093592</t>
-  </si>
-  <si>
-    <t>1400097418</t>
-  </si>
-  <si>
-    <t>1400093593</t>
-  </si>
-  <si>
-    <t>1400097419</t>
-  </si>
-  <si>
-    <t>200006489</t>
-  </si>
-  <si>
-    <t>1400093594</t>
-  </si>
-  <si>
-    <t>1400097430</t>
-  </si>
-  <si>
-    <t>1400093595</t>
-  </si>
-  <si>
-    <t>1400097431</t>
-  </si>
-  <si>
-    <t>1400096379</t>
-  </si>
-  <si>
-    <t>1400097433</t>
-  </si>
-  <si>
-    <t>1400093596</t>
-  </si>
-  <si>
-    <t>1400097434</t>
-  </si>
-  <si>
-    <t>1400093597</t>
-  </si>
-  <si>
-    <t>1400097435</t>
-  </si>
-  <si>
-    <t>1400093598</t>
-  </si>
-  <si>
-    <t>1400097436</t>
-  </si>
-  <si>
-    <t>1400097110</t>
-  </si>
-  <si>
-    <t>0191</t>
-  </si>
-  <si>
-    <t>1400101049</t>
-  </si>
-  <si>
-    <t>鏟花八小時</t>
-  </si>
-  <si>
-    <t>1400097074</t>
-  </si>
-  <si>
-    <t>0192</t>
-  </si>
-  <si>
-    <t>1400101050</t>
-  </si>
-  <si>
-    <t>噴漆二小時</t>
-  </si>
-  <si>
-    <t>1400093599</t>
-  </si>
-  <si>
-    <t>1400097437</t>
-  </si>
-  <si>
-    <t>1400093600</t>
-  </si>
-  <si>
-    <t>1400097438</t>
-  </si>
-  <si>
-    <t>200006490</t>
-  </si>
-  <si>
-    <t>1400093601</t>
-  </si>
-  <si>
-    <t>1400097439</t>
-  </si>
-  <si>
-    <t>1400093602</t>
-  </si>
-  <si>
-    <t>1400097440</t>
-  </si>
-  <si>
-    <t>1400093603</t>
-  </si>
-  <si>
-    <t>1400097443</t>
-  </si>
-  <si>
-    <t>1400093604</t>
-  </si>
-  <si>
-    <t>1400097444</t>
-  </si>
-  <si>
-    <t>1400093605</t>
-  </si>
-  <si>
-    <t>1400097445</t>
-  </si>
-  <si>
-    <t>1400093606</t>
-  </si>
-  <si>
-    <t>1400097446</t>
-  </si>
-  <si>
-    <t>1400093607</t>
-  </si>
-  <si>
-    <t>1400097447</t>
-  </si>
-  <si>
-    <t>200006567</t>
-  </si>
-  <si>
-    <t>1400094686</t>
-  </si>
-  <si>
-    <t>1400098481</t>
-  </si>
-  <si>
-    <t>1400094161</t>
-  </si>
-  <si>
-    <t>1400098482</t>
-  </si>
-  <si>
-    <t>1400094162</t>
-  </si>
-  <si>
-    <t>1400098485</t>
-  </si>
-  <si>
-    <t>1400094687</t>
-  </si>
-  <si>
-    <t>1400098486</t>
-  </si>
-  <si>
-    <t>1400094163</t>
-  </si>
-  <si>
-    <t>1400098487</t>
-  </si>
-  <si>
-    <t>1400094164</t>
-  </si>
-  <si>
-    <t>1400098488</t>
-  </si>
-  <si>
-    <t>1400094688</t>
-  </si>
-  <si>
-    <t>1400098489</t>
-  </si>
-  <si>
-    <t>200006568</t>
-  </si>
-  <si>
-    <t>1400094691</t>
-  </si>
-  <si>
-    <t>1400098620</t>
-  </si>
-  <si>
-    <t>1400094166</t>
-  </si>
-  <si>
-    <t>1400098621</t>
-  </si>
-  <si>
-    <t>1400094167</t>
-  </si>
-  <si>
-    <t>1400098624</t>
-  </si>
-  <si>
-    <t>1400094692</t>
-  </si>
-  <si>
-    <t>1400098625</t>
-  </si>
-  <si>
-    <t>1400094168</t>
-  </si>
-  <si>
-    <t>1400098626</t>
-  </si>
-  <si>
-    <t>1400094169</t>
-  </si>
-  <si>
-    <t>1400098627</t>
-  </si>
-  <si>
-    <t>1400094693</t>
-  </si>
-  <si>
-    <t>1400098628</t>
-  </si>
-  <si>
-    <t>200006569</t>
-  </si>
-  <si>
-    <t>1400094813</t>
-  </si>
-  <si>
-    <t>1400098691</t>
-  </si>
-  <si>
-    <t>1400094842</t>
-  </si>
-  <si>
-    <t>1400098692</t>
-  </si>
-  <si>
-    <t>1400094843</t>
-  </si>
-  <si>
-    <t>1400098695</t>
-  </si>
-  <si>
-    <t>1400094814</t>
-  </si>
-  <si>
-    <t>1400098696</t>
-  </si>
-  <si>
-    <t>1400094844</t>
-  </si>
-  <si>
-    <t>1400098697</t>
-  </si>
-  <si>
-    <t>1400094845</t>
-  </si>
-  <si>
-    <t>1400098698</t>
-  </si>
-  <si>
-    <t>1400094815</t>
-  </si>
-  <si>
-    <t>1400098699</t>
-  </si>
-  <si>
-    <t>200006573</t>
-  </si>
-  <si>
-    <t>1400094900</t>
-  </si>
-  <si>
-    <t>1400098785</t>
-  </si>
-  <si>
-    <t>M90頭噴漆</t>
-  </si>
-  <si>
-    <t>1400094945</t>
-  </si>
-  <si>
-    <t>1400098786</t>
-  </si>
-  <si>
-    <t>M90頭鏟花</t>
-  </si>
-  <si>
-    <t>200006575</t>
-  </si>
-  <si>
-    <t>1400094901</t>
-  </si>
-  <si>
-    <t>1400098787</t>
-  </si>
-  <si>
-    <t>1400094947</t>
-  </si>
-  <si>
-    <t>1400098800</t>
-  </si>
-  <si>
-    <t>1400094904</t>
-  </si>
-  <si>
-    <t>1400098801</t>
-  </si>
-  <si>
-    <t>200006580</t>
-  </si>
-  <si>
-    <t>1400094902</t>
-  </si>
-  <si>
-    <t>1400098795</t>
-  </si>
-  <si>
-    <t>1400094946</t>
-  </si>
-  <si>
-    <t>1400098798</t>
-  </si>
-  <si>
-    <t>1400094903</t>
-  </si>
-  <si>
-    <t>1400098799</t>
-  </si>
-  <si>
-    <t>200006701</t>
-  </si>
-  <si>
-    <t>1400097113</t>
-  </si>
-  <si>
-    <t>0070</t>
-  </si>
-  <si>
-    <t>1400101107</t>
-  </si>
-  <si>
-    <t>機頭精度檢驗</t>
-  </si>
-  <si>
-    <t>200006723</t>
-  </si>
-  <si>
-    <t>1400097283</t>
-  </si>
-  <si>
-    <t>1400101237</t>
-  </si>
-  <si>
-    <t>PBM機頭噴漆</t>
-  </si>
-  <si>
-    <t>1400097284</t>
-  </si>
-  <si>
-    <t>1400101238</t>
-  </si>
-  <si>
-    <t>PBM進給座噴漆</t>
-  </si>
-  <si>
-    <t>1400097327</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>1400101239</t>
-  </si>
-  <si>
-    <t>齒輪箱進給座鏟花</t>
+    <t>1400101412</t>
+  </si>
+  <si>
+    <t>200006737</t>
+  </si>
+  <si>
+    <t>1400097484</t>
+  </si>
+  <si>
+    <t>1400101477</t>
+  </si>
+  <si>
+    <t>1400097466</t>
+  </si>
+  <si>
+    <t>1400101478</t>
+  </si>
+  <si>
+    <t>1400097467</t>
+  </si>
+  <si>
+    <t>1400101481</t>
+  </si>
+  <si>
+    <t>1400097485</t>
+  </si>
+  <si>
+    <t>1400101482</t>
+  </si>
+  <si>
+    <t>1400097468</t>
+  </si>
+  <si>
+    <t>1400101483</t>
+  </si>
+  <si>
+    <t>1400097469</t>
+  </si>
+  <si>
+    <t>1400101484</t>
+  </si>
+  <si>
+    <t>1400097486</t>
+  </si>
+  <si>
+    <t>1400101485</t>
   </si>
   <si>
     <t>訂單</t>
@@ -793,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -818,58 +767,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1364,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R10" s="3">
         <v>1</v>
@@ -1420,13 +1369,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R11" s="3">
         <v>1</v>
@@ -1532,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="O13" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R13" s="3">
         <v>1</v>
@@ -1588,13 +1537,13 @@
         <v>1</v>
       </c>
       <c r="O14" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R14" s="3">
         <v>1</v>
@@ -1700,13 +1649,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R16" s="3">
         <v>1</v>
@@ -1812,13 +1761,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R18" s="3">
         <v>1</v>
@@ -1868,13 +1817,13 @@
         <v>1</v>
       </c>
       <c r="O19" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R19" s="3">
         <v>1</v>
@@ -1906,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="I20" s="2">
-        <v>46094</v>
+        <v>46122</v>
       </c>
       <c r="J20" t="s">
         <v>7</v>
@@ -1924,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="2">
-        <v>46125</v>
+        <v>46154</v>
       </c>
       <c r="P20" t="s">
         <v>10</v>
@@ -1962,7 +1911,7 @@
         <v>14</v>
       </c>
       <c r="I21" s="2">
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="J21" t="s">
         <v>7</v>
@@ -1997,19 +1946,19 @@
         <v>67</v>
       </c>
       <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
         <v>72</v>
       </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>73</v>
-      </c>
-      <c r="F22" t="s">
-        <v>74</v>
       </c>
       <c r="G22" t="s">
         <v>2</v>
@@ -2018,25 +1967,25 @@
         <v>58</v>
       </c>
       <c r="I22" s="2">
-        <v>46122</v>
+        <v>46164</v>
       </c>
       <c r="J22" t="s">
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M22" s="3">
         <v>1</v>
       </c>
       <c r="N22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2">
-        <v>46119</v>
+        <v>46154</v>
       </c>
       <c r="P22" t="s">
         <v>7</v>
@@ -2045,7 +1994,7 @@
         <v>7</v>
       </c>
       <c r="R22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2053,7 +2002,7 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
@@ -2065,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
@@ -2074,7 +2023,7 @@
         <v>14</v>
       </c>
       <c r="I23" s="2">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="J23" t="s">
         <v>7</v>
@@ -2109,7 +2058,7 @@
         <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
         <v>2</v>
@@ -2121,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
@@ -2130,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="I24" s="2">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="J24" t="s">
         <v>7</v>
@@ -2148,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="2">
-        <v>46125</v>
+        <v>46154</v>
       </c>
       <c r="P24" t="s">
         <v>10</v>
@@ -2165,7 +2114,7 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
         <v>2</v>
@@ -2177,7 +2126,7 @@
         <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
@@ -2186,7 +2135,7 @@
         <v>14</v>
       </c>
       <c r="I25" s="2">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="J25" t="s">
         <v>7</v>
@@ -2221,7 +2170,7 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
         <v>2</v>
@@ -2233,7 +2182,7 @@
         <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
         <v>2</v>
@@ -2242,7 +2191,7 @@
         <v>14</v>
       </c>
       <c r="I26" s="2">
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="J26" t="s">
         <v>7</v>
@@ -2277,7 +2226,7 @@
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
@@ -2289,7 +2238,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
         <v>2</v>
@@ -2298,7 +2247,7 @@
         <v>6</v>
       </c>
       <c r="I27" s="2">
-        <v>46100</v>
+        <v>46128</v>
       </c>
       <c r="J27" t="s">
         <v>7</v>
@@ -2316,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="2">
-        <v>46125</v>
+        <v>46154</v>
       </c>
       <c r="P27" t="s">
         <v>10</v>
@@ -2330,10 +2279,10 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
         <v>86</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
@@ -2345,7 +2294,7 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
@@ -2354,7 +2303,7 @@
         <v>6</v>
       </c>
       <c r="I28" s="2">
-        <v>46114</v>
+        <v>46083</v>
       </c>
       <c r="J28" t="s">
         <v>7</v>
@@ -2363,16 +2312,16 @@
         <v>8</v>
       </c>
       <c r="L28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M28" s="3">
         <v>1</v>
       </c>
       <c r="N28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P28" t="s">
         <v>7</v>
@@ -2381,15 +2330,15 @@
         <v>7</v>
       </c>
       <c r="R28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
         <v>2</v>
@@ -2401,7 +2350,7 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
         <v>2</v>
@@ -2410,7 +2359,7 @@
         <v>14</v>
       </c>
       <c r="I29" s="2">
-        <v>46119</v>
+        <v>46084</v>
       </c>
       <c r="J29" t="s">
         <v>7</v>
@@ -2419,72 +2368,72 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M29" s="3">
         <v>1</v>
       </c>
       <c r="N29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="P29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
         <v>91</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" t="s">
-        <v>92</v>
-      </c>
       <c r="G30" t="s">
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2">
-        <v>46122</v>
+        <v>46097</v>
       </c>
       <c r="J30" t="s">
         <v>7</v>
       </c>
       <c r="K30" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M30" s="3">
         <v>1</v>
       </c>
       <c r="N30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2">
-        <v>46119</v>
+        <v>46083</v>
       </c>
       <c r="P30" t="s">
         <v>7</v>
@@ -2493,110 +2442,110 @@
         <v>7</v>
       </c>
       <c r="R30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
         <v>93</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" t="s">
-        <v>94</v>
-      </c>
       <c r="G31" t="s">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I31" s="2">
-        <v>46127</v>
+        <v>46097</v>
       </c>
       <c r="J31" t="s">
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M31" s="3">
         <v>1</v>
       </c>
       <c r="N31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="P31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
         <v>95</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>96</v>
-      </c>
       <c r="G32" t="s">
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I32" s="2">
-        <v>46127</v>
+        <v>46100</v>
       </c>
       <c r="J32" t="s">
         <v>7</v>
       </c>
       <c r="K32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M32" s="3">
         <v>1</v>
       </c>
       <c r="N32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P32" t="s">
         <v>7</v>
@@ -2605,27 +2554,27 @@
         <v>7</v>
       </c>
       <c r="R32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
         <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" t="s">
-        <v>98</v>
       </c>
       <c r="G33" t="s">
         <v>2</v>
@@ -2634,54 +2583,54 @@
         <v>14</v>
       </c>
       <c r="I33" s="2">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="J33" t="s">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M33" s="3">
         <v>1</v>
       </c>
       <c r="N33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="P33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" t="s">
         <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" t="s">
-        <v>101</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
@@ -2690,13 +2639,13 @@
         <v>6</v>
       </c>
       <c r="I34" s="2">
-        <v>46139</v>
+        <v>46086</v>
       </c>
       <c r="J34" t="s">
         <v>7</v>
       </c>
       <c r="K34" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="L34" t="s">
         <v>7</v>
@@ -2708,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>46140</v>
+        <v>46083</v>
       </c>
       <c r="P34" t="s">
         <v>7</v>
@@ -2722,10 +2671,10 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
@@ -2734,37 +2683,37 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I35" s="2">
-        <v>46140</v>
+        <v>46085</v>
       </c>
       <c r="J35" t="s">
         <v>7</v>
       </c>
       <c r="K35" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="L35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M35" s="3">
         <v>1</v>
       </c>
       <c r="N35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2">
-        <v>46140</v>
+        <v>46083</v>
       </c>
       <c r="P35" t="s">
         <v>7</v>
@@ -2773,27 +2722,27 @@
         <v>7</v>
       </c>
       <c r="R35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
@@ -2802,81 +2751,81 @@
         <v>14</v>
       </c>
       <c r="I36" s="2">
-        <v>46119</v>
+        <v>46086</v>
       </c>
       <c r="J36" t="s">
         <v>7</v>
       </c>
       <c r="K36" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M36" s="3">
         <v>1</v>
       </c>
       <c r="N36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="P36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I37" s="2">
-        <v>46122</v>
+        <v>46098</v>
       </c>
       <c r="J37" t="s">
         <v>7</v>
       </c>
       <c r="K37" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M37" s="3">
         <v>1</v>
       </c>
       <c r="N37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P37" t="s">
         <v>7</v>
@@ -2885,15 +2834,15 @@
         <v>7</v>
       </c>
       <c r="R37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
         <v>2</v>
@@ -2902,10 +2851,10 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
@@ -2914,25 +2863,25 @@
         <v>6</v>
       </c>
       <c r="I38" s="2">
-        <v>46122</v>
+        <v>46098</v>
       </c>
       <c r="J38" t="s">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="L38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M38" s="3">
         <v>1</v>
       </c>
       <c r="N38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P38" t="s">
         <v>7</v>
@@ -2941,15 +2890,15 @@
         <v>7</v>
       </c>
       <c r="R38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
         <v>2</v>
@@ -2958,10 +2907,10 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
@@ -2970,54 +2919,54 @@
         <v>14</v>
       </c>
       <c r="I39" s="2">
-        <v>46125</v>
+        <v>46101</v>
       </c>
       <c r="J39" t="s">
         <v>7</v>
       </c>
       <c r="K39" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="P39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
         <v>111</v>
       </c>
-      <c r="B40" t="s">
-        <v>116</v>
-      </c>
       <c r="C40" t="s">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
@@ -3026,54 +2975,54 @@
         <v>14</v>
       </c>
       <c r="I40" s="2">
-        <v>46133</v>
+        <v>46085</v>
       </c>
       <c r="J40" t="s">
         <v>7</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M40" s="3">
         <v>1</v>
       </c>
       <c r="N40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="P40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G41" t="s">
         <v>2</v>
@@ -3082,25 +3031,25 @@
         <v>6</v>
       </c>
       <c r="I41" s="2">
-        <v>46133</v>
+        <v>46090</v>
       </c>
       <c r="J41" t="s">
         <v>7</v>
       </c>
       <c r="K41" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M41" s="3">
         <v>1</v>
       </c>
       <c r="N41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="P41" t="s">
         <v>7</v>
@@ -3109,15 +3058,15 @@
         <v>7</v>
       </c>
       <c r="R41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
@@ -3126,66 +3075,66 @@
         <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G42" t="s">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I42" s="2">
-        <v>46136</v>
+        <v>46084</v>
       </c>
       <c r="J42" t="s">
         <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M42" s="3">
         <v>1</v>
       </c>
       <c r="N42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="P42" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G43" t="s">
         <v>2</v>
@@ -3194,81 +3143,81 @@
         <v>14</v>
       </c>
       <c r="I43" s="2">
-        <v>46125</v>
+        <v>46085</v>
       </c>
       <c r="J43" t="s">
         <v>7</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M43" s="3">
         <v>1</v>
       </c>
       <c r="N43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2">
-        <v>46125</v>
+        <v>46085</v>
       </c>
       <c r="P43" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I44" s="2">
-        <v>46128</v>
+        <v>46097</v>
       </c>
       <c r="J44" t="s">
         <v>7</v>
       </c>
       <c r="K44" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M44" s="3">
         <v>1</v>
       </c>
       <c r="N44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2">
-        <v>46065</v>
+        <v>46085</v>
       </c>
       <c r="P44" t="s">
         <v>7</v>
@@ -3277,15 +3226,15 @@
         <v>7</v>
       </c>
       <c r="R44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -3294,10 +3243,10 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G45" t="s">
         <v>2</v>
@@ -3306,13 +3255,13 @@
         <v>6</v>
       </c>
       <c r="I45" s="2">
-        <v>46083</v>
+        <v>46097</v>
       </c>
       <c r="J45" t="s">
         <v>7</v>
       </c>
       <c r="K45" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="L45" t="s">
         <v>7</v>
@@ -3324,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="P45" t="s">
         <v>7</v>
@@ -3338,10 +3287,10 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
         <v>2</v>
@@ -3350,10 +3299,10 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G46" t="s">
         <v>2</v>
@@ -3362,13 +3311,13 @@
         <v>14</v>
       </c>
       <c r="I46" s="2">
-        <v>46084</v>
+        <v>46100</v>
       </c>
       <c r="J46" t="s">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L46" t="s">
         <v>7</v>
@@ -3380,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="P46" t="s">
         <v>7</v>
@@ -3394,22 +3343,22 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
         <v>126</v>
       </c>
-      <c r="B47" t="s">
-        <v>131</v>
-      </c>
       <c r="C47" t="s">
         <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F47" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
@@ -3418,13 +3367,13 @@
         <v>14</v>
       </c>
       <c r="I47" s="2">
-        <v>46097</v>
+        <v>46084</v>
       </c>
       <c r="J47" t="s">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L47" t="s">
         <v>7</v>
@@ -3436,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="P47" t="s">
         <v>7</v>
@@ -3450,22 +3399,22 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
@@ -3474,13 +3423,13 @@
         <v>6</v>
       </c>
       <c r="I48" s="2">
-        <v>46097</v>
+        <v>46087</v>
       </c>
       <c r="J48" t="s">
         <v>7</v>
       </c>
       <c r="K48" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L48" t="s">
         <v>7</v>
@@ -3492,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="P48" t="s">
         <v>7</v>
@@ -3506,10 +3455,10 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
@@ -3518,10 +3467,10 @@
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
@@ -3530,25 +3479,25 @@
         <v>14</v>
       </c>
       <c r="I49" s="2">
-        <v>46100</v>
+        <v>46167</v>
       </c>
       <c r="J49" t="s">
         <v>7</v>
       </c>
       <c r="K49" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M49" s="3">
         <v>1</v>
       </c>
       <c r="N49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P49" t="s">
         <v>7</v>
@@ -3562,105 +3511,105 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F50" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I50" s="2">
-        <v>46083</v>
+        <v>46170</v>
       </c>
       <c r="J50" t="s">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M50" s="3">
         <v>1</v>
       </c>
       <c r="N50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P50" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" t="s">
         <v>139</v>
       </c>
-      <c r="C51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" t="s">
-        <v>140</v>
-      </c>
       <c r="G51" t="s">
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I51" s="2">
+        <v>46167</v>
+      </c>
+      <c r="J51" t="s">
+        <v>7</v>
+      </c>
+      <c r="K51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L51" t="s">
+        <v>7</v>
+      </c>
+      <c r="M51" s="3">
+        <v>1</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2">
         <v>46086</v>
-      </c>
-      <c r="J51" t="s">
-        <v>7</v>
-      </c>
-      <c r="K51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L51" t="s">
-        <v>7</v>
-      </c>
-      <c r="M51" s="3">
-        <v>1</v>
-      </c>
-      <c r="N51" s="3">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2">
-        <v>46083</v>
       </c>
       <c r="P51" t="s">
         <v>7</v>
@@ -3674,22 +3623,22 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" t="s">
         <v>141</v>
-      </c>
-      <c r="B52" t="s">
-        <v>142</v>
-      </c>
-      <c r="C52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" t="s">
-        <v>143</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
@@ -3698,13 +3647,13 @@
         <v>6</v>
       </c>
       <c r="I52" s="2">
-        <v>46085</v>
+        <v>46183</v>
       </c>
       <c r="J52" t="s">
         <v>7</v>
       </c>
       <c r="K52" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="L52" t="s">
         <v>7</v>
@@ -3716,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P52" t="s">
         <v>7</v>
@@ -3730,10 +3679,10 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
@@ -3742,10 +3691,10 @@
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
@@ -3754,25 +3703,25 @@
         <v>14</v>
       </c>
       <c r="I53" s="2">
+        <v>46183</v>
+      </c>
+      <c r="J53" t="s">
+        <v>7</v>
+      </c>
+      <c r="K53" t="s">
+        <v>66</v>
+      </c>
+      <c r="L53" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" s="3">
+        <v>1</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2">
         <v>46086</v>
-      </c>
-      <c r="J53" t="s">
-        <v>7</v>
-      </c>
-      <c r="K53" t="s">
-        <v>15</v>
-      </c>
-      <c r="L53" t="s">
-        <v>7</v>
-      </c>
-      <c r="M53" s="3">
-        <v>1</v>
-      </c>
-      <c r="N53" s="3">
-        <v>0</v>
-      </c>
-      <c r="O53" s="2">
-        <v>46083</v>
       </c>
       <c r="P53" t="s">
         <v>7</v>
@@ -3786,22 +3735,22 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
+        <v>145</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" t="s">
         <v>146</v>
-      </c>
-      <c r="C54" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" t="s">
-        <v>3</v>
-      </c>
-      <c r="E54" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" t="s">
-        <v>147</v>
       </c>
       <c r="G54" t="s">
         <v>2</v>
@@ -3810,25 +3759,25 @@
         <v>14</v>
       </c>
       <c r="I54" s="2">
-        <v>46098</v>
+        <v>46153</v>
       </c>
       <c r="J54" t="s">
         <v>7</v>
       </c>
       <c r="K54" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="L54" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M54" s="3">
         <v>1</v>
       </c>
       <c r="N54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P54" t="s">
         <v>7</v>
@@ -3842,37 +3791,37 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>56</v>
+      </c>
+      <c r="F55" t="s">
         <v>148</v>
       </c>
-      <c r="C55" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" t="s">
-        <v>149</v>
-      </c>
       <c r="G55" t="s">
         <v>2</v>
       </c>
       <c r="H55" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="I55" s="2">
-        <v>46098</v>
+        <v>46164</v>
       </c>
       <c r="J55" t="s">
         <v>7</v>
       </c>
       <c r="K55" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="L55" t="s">
         <v>7</v>
@@ -3884,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="2">
-        <v>46083</v>
+        <v>46154</v>
       </c>
       <c r="P55" t="s">
         <v>7</v>
@@ -3898,37 +3847,37 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" t="s">
         <v>150</v>
       </c>
-      <c r="C56" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>3</v>
-      </c>
-      <c r="E56" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" t="s">
-        <v>151</v>
-      </c>
       <c r="G56" t="s">
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I56" s="2">
-        <v>46101</v>
+        <v>46169</v>
       </c>
       <c r="J56" t="s">
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="L56" t="s">
         <v>7</v>
@@ -3940,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P56" t="s">
         <v>7</v>
@@ -3954,22 +3903,22 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B57" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" t="s">
         <v>152</v>
-      </c>
-      <c r="C57" t="s">
-        <v>2</v>
-      </c>
-      <c r="D57" t="s">
-        <v>29</v>
-      </c>
-      <c r="E57" t="s">
-        <v>30</v>
-      </c>
-      <c r="F57" t="s">
-        <v>153</v>
       </c>
       <c r="G57" t="s">
         <v>2</v>
@@ -3978,25 +3927,25 @@
         <v>14</v>
       </c>
       <c r="I57" s="2">
-        <v>46085</v>
+        <v>46169</v>
       </c>
       <c r="J57" t="s">
         <v>7</v>
       </c>
       <c r="K57" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="L57" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M57" s="3">
         <v>1</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="P57" t="s">
         <v>7</v>
@@ -4010,7 +3959,7 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B58" t="s">
         <v>154</v>
@@ -4019,13 +3968,13 @@
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="F58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G58" t="s">
         <v>2</v>
@@ -4034,13 +3983,13 @@
         <v>6</v>
       </c>
       <c r="I58" s="2">
-        <v>46090</v>
+        <v>46141</v>
       </c>
       <c r="J58" t="s">
         <v>7</v>
       </c>
       <c r="K58" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="L58" t="s">
         <v>7</v>
@@ -4052,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2">
-        <v>46083</v>
+        <v>46140</v>
       </c>
       <c r="P58" t="s">
         <v>7</v>
@@ -4066,10 +4015,10 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
@@ -4081,22 +4030,22 @@
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G59" t="s">
         <v>2</v>
       </c>
       <c r="H59" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I59" s="2">
-        <v>46084</v>
+        <v>46225</v>
       </c>
       <c r="J59" t="s">
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s">
         <v>7</v>
@@ -4108,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="2">
-        <v>46084</v>
+        <v>46148</v>
       </c>
       <c r="P59" t="s">
         <v>7</v>
@@ -4122,10 +4071,10 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C60" t="s">
         <v>2</v>
@@ -4134,10 +4083,10 @@
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F60" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G60" t="s">
         <v>2</v>
@@ -4146,13 +4095,13 @@
         <v>14</v>
       </c>
       <c r="I60" s="2">
-        <v>46085</v>
+        <v>46225</v>
       </c>
       <c r="J60" t="s">
         <v>7</v>
       </c>
       <c r="K60" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="L60" t="s">
         <v>7</v>
@@ -4164,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="2">
-        <v>46085</v>
+        <v>46148</v>
       </c>
       <c r="P60" t="s">
         <v>7</v>
@@ -4178,10 +4127,10 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C61" t="s">
         <v>2</v>
@@ -4190,25 +4139,25 @@
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G61" t="s">
         <v>2</v>
       </c>
       <c r="H61" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I61" s="2">
-        <v>46097</v>
+        <v>46247</v>
       </c>
       <c r="J61" t="s">
         <v>7</v>
       </c>
       <c r="K61" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="L61" t="s">
         <v>7</v>
@@ -4220,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="2">
-        <v>46085</v>
+        <v>46148</v>
       </c>
       <c r="P61" t="s">
         <v>7</v>
@@ -4234,10 +4183,10 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C62" t="s">
         <v>2</v>
@@ -4246,25 +4195,25 @@
         <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G62" t="s">
         <v>2</v>
       </c>
       <c r="H62" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I62" s="2">
-        <v>46097</v>
+        <v>46237</v>
       </c>
       <c r="J62" t="s">
         <v>7</v>
       </c>
       <c r="K62" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="L62" t="s">
         <v>7</v>
@@ -4276,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="2">
-        <v>46084</v>
+        <v>46153</v>
       </c>
       <c r="P62" t="s">
         <v>7</v>
@@ -4290,10 +4239,10 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C63" t="s">
         <v>2</v>
@@ -4302,25 +4251,25 @@
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G63" t="s">
         <v>2</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I63" s="2">
-        <v>46100</v>
+        <v>46253</v>
       </c>
       <c r="J63" t="s">
         <v>7</v>
       </c>
       <c r="K63" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="L63" t="s">
         <v>7</v>
@@ -4332,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="2">
-        <v>46085</v>
+        <v>46153</v>
       </c>
       <c r="P63" t="s">
         <v>7</v>
@@ -4346,22 +4295,22 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F64" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G64" t="s">
         <v>2</v>
@@ -4370,13 +4319,13 @@
         <v>14</v>
       </c>
       <c r="I64" s="2">
-        <v>46084</v>
+        <v>46253</v>
       </c>
       <c r="J64" t="s">
         <v>7</v>
       </c>
       <c r="K64" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="L64" t="s">
         <v>7</v>
@@ -4388,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="2">
-        <v>46085</v>
+        <v>46153</v>
       </c>
       <c r="P64" t="s">
         <v>7</v>
@@ -4402,22 +4351,22 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
         <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F65" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G65" t="s">
         <v>2</v>
@@ -4426,13 +4375,13 @@
         <v>6</v>
       </c>
       <c r="I65" s="2">
-        <v>46087</v>
+        <v>46240</v>
       </c>
       <c r="J65" t="s">
         <v>7</v>
       </c>
       <c r="K65" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="L65" t="s">
         <v>7</v>
@@ -4444,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="2">
-        <v>46084</v>
+        <v>46154</v>
       </c>
       <c r="P65" t="s">
         <v>7</v>
@@ -4458,10 +4407,10 @@
     </row>
     <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
@@ -4470,10 +4419,10 @@
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G66" t="s">
         <v>2</v>
@@ -4482,13 +4431,13 @@
         <v>14</v>
       </c>
       <c r="I66" s="2">
-        <v>46167</v>
+        <v>46241</v>
       </c>
       <c r="J66" t="s">
         <v>7</v>
       </c>
       <c r="K66" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="L66" t="s">
         <v>7</v>
@@ -4500,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="2">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="P66" t="s">
         <v>7</v>
@@ -4514,10 +4463,10 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B67" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -4526,37 +4475,37 @@
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G67" t="s">
         <v>2</v>
       </c>
       <c r="H67" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I67" s="2">
-        <v>46170</v>
+        <v>46253</v>
       </c>
       <c r="J67" t="s">
         <v>7</v>
       </c>
       <c r="K67" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="L67" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M67" s="3">
         <v>1</v>
       </c>
       <c r="N67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="P67" t="s">
         <v>7</v>
@@ -4565,15 +4514,15 @@
         <v>7</v>
       </c>
       <c r="R67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B68" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
@@ -4582,25 +4531,25 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F68" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G68" t="s">
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I68" s="2">
-        <v>46167</v>
+        <v>46253</v>
       </c>
       <c r="J68" t="s">
         <v>7</v>
       </c>
       <c r="K68" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="L68" t="s">
         <v>7</v>
@@ -4612,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="2">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="P68" t="s">
         <v>7</v>
@@ -4626,10 +4575,10 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s">
         <v>2</v>
@@ -4638,25 +4587,25 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G69" t="s">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I69" s="2">
-        <v>46183</v>
+        <v>46258</v>
       </c>
       <c r="J69" t="s">
         <v>7</v>
       </c>
       <c r="K69" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="L69" t="s">
         <v>7</v>
@@ -4668,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="2">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="P69" t="s">
         <v>7</v>
@@ -4682,22 +4631,22 @@
     </row>
     <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B70" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E70" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F70" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G70" t="s">
         <v>2</v>
@@ -4706,13 +4655,13 @@
         <v>14</v>
       </c>
       <c r="I70" s="2">
-        <v>46183</v>
+        <v>46240</v>
       </c>
       <c r="J70" t="s">
         <v>7</v>
       </c>
       <c r="K70" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L70" t="s">
         <v>7</v>
@@ -4724,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="2">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="P70" t="s">
         <v>7</v>
@@ -4738,37 +4687,37 @@
     </row>
     <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B71" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C71" t="s">
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E71" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G71" t="s">
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I71" s="2">
-        <v>46153</v>
+        <v>46245</v>
       </c>
       <c r="J71" t="s">
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L71" t="s">
         <v>7</v>
@@ -4780,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="2">
-        <v>46086</v>
+        <v>46154</v>
       </c>
       <c r="P71" t="s">
         <v>7</v>
@@ -4789,342 +4738,6 @@
         <v>7</v>
       </c>
       <c r="R71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18">
-      <c r="A72" t="s">
-        <v>185</v>
-      </c>
-      <c r="B72" t="s">
-        <v>188</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" t="s">
-        <v>61</v>
-      </c>
-      <c r="F72" t="s">
-        <v>189</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2</v>
-      </c>
-      <c r="H72" t="s">
-        <v>6</v>
-      </c>
-      <c r="I72" s="2">
-        <v>46169</v>
-      </c>
-      <c r="J72" t="s">
-        <v>7</v>
-      </c>
-      <c r="K72" t="s">
-        <v>63</v>
-      </c>
-      <c r="L72" t="s">
-        <v>7</v>
-      </c>
-      <c r="M72" s="3">
-        <v>1</v>
-      </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="2">
-        <v>46086</v>
-      </c>
-      <c r="P72" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>7</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
-      <c r="A73" t="s">
-        <v>185</v>
-      </c>
-      <c r="B73" t="s">
-        <v>190</v>
-      </c>
-      <c r="C73" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" t="s">
-        <v>3</v>
-      </c>
-      <c r="E73" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" t="s">
-        <v>191</v>
-      </c>
-      <c r="G73" t="s">
-        <v>2</v>
-      </c>
-      <c r="H73" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" s="2">
-        <v>46169</v>
-      </c>
-      <c r="J73" t="s">
-        <v>7</v>
-      </c>
-      <c r="K73" t="s">
-        <v>66</v>
-      </c>
-      <c r="L73" t="s">
-        <v>7</v>
-      </c>
-      <c r="M73" s="3">
-        <v>1</v>
-      </c>
-      <c r="N73" s="3">
-        <v>0</v>
-      </c>
-      <c r="O73" s="2">
-        <v>46086</v>
-      </c>
-      <c r="P73" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>7</v>
-      </c>
-      <c r="R73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
-      <c r="A74" t="s">
-        <v>192</v>
-      </c>
-      <c r="B74" t="s">
-        <v>193</v>
-      </c>
-      <c r="C74" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" t="s">
-        <v>3</v>
-      </c>
-      <c r="E74" t="s">
-        <v>194</v>
-      </c>
-      <c r="F74" t="s">
-        <v>195</v>
-      </c>
-      <c r="G74" t="s">
-        <v>2</v>
-      </c>
-      <c r="H74" t="s">
-        <v>6</v>
-      </c>
-      <c r="I74" s="2">
-        <v>46141</v>
-      </c>
-      <c r="J74" t="s">
-        <v>7</v>
-      </c>
-      <c r="K74" t="s">
-        <v>196</v>
-      </c>
-      <c r="L74" t="s">
-        <v>7</v>
-      </c>
-      <c r="M74" s="3">
-        <v>1</v>
-      </c>
-      <c r="N74" s="3">
-        <v>0</v>
-      </c>
-      <c r="O74" s="2">
-        <v>46140</v>
-      </c>
-      <c r="P74" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>7</v>
-      </c>
-      <c r="R74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18">
-      <c r="A75" t="s">
-        <v>197</v>
-      </c>
-      <c r="B75" t="s">
-        <v>198</v>
-      </c>
-      <c r="C75" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E75" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" t="s">
-        <v>199</v>
-      </c>
-      <c r="G75" t="s">
-        <v>2</v>
-      </c>
-      <c r="H75" t="s">
-        <v>14</v>
-      </c>
-      <c r="I75" s="2">
-        <v>46225</v>
-      </c>
-      <c r="J75" t="s">
-        <v>7</v>
-      </c>
-      <c r="K75" t="s">
-        <v>200</v>
-      </c>
-      <c r="L75" t="s">
-        <v>7</v>
-      </c>
-      <c r="M75" s="3">
-        <v>1</v>
-      </c>
-      <c r="N75" s="3">
-        <v>0</v>
-      </c>
-      <c r="O75" s="2">
-        <v>46148</v>
-      </c>
-      <c r="P75" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>7</v>
-      </c>
-      <c r="R75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18">
-      <c r="A76" t="s">
-        <v>197</v>
-      </c>
-      <c r="B76" t="s">
-        <v>201</v>
-      </c>
-      <c r="C76" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>30</v>
-      </c>
-      <c r="F76" t="s">
-        <v>202</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2</v>
-      </c>
-      <c r="H76" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" s="2">
-        <v>46225</v>
-      </c>
-      <c r="J76" t="s">
-        <v>7</v>
-      </c>
-      <c r="K76" t="s">
-        <v>203</v>
-      </c>
-      <c r="L76" t="s">
-        <v>7</v>
-      </c>
-      <c r="M76" s="3">
-        <v>1</v>
-      </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="2">
-        <v>46148</v>
-      </c>
-      <c r="P76" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>7</v>
-      </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" t="s">
-        <v>197</v>
-      </c>
-      <c r="B77" t="s">
-        <v>204</v>
-      </c>
-      <c r="C77" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" t="s">
-        <v>3</v>
-      </c>
-      <c r="E77" t="s">
-        <v>205</v>
-      </c>
-      <c r="F77" t="s">
-        <v>206</v>
-      </c>
-      <c r="G77" t="s">
-        <v>2</v>
-      </c>
-      <c r="H77" t="s">
-        <v>6</v>
-      </c>
-      <c r="I77" s="2">
-        <v>46247</v>
-      </c>
-      <c r="J77" t="s">
-        <v>7</v>
-      </c>
-      <c r="K77" t="s">
-        <v>207</v>
-      </c>
-      <c r="L77" t="s">
-        <v>7</v>
-      </c>
-      <c r="M77" s="3">
-        <v>1</v>
-      </c>
-      <c r="N77" s="3">
-        <v>0</v>
-      </c>
-      <c r="O77" s="2">
-        <v>46148</v>
-      </c>
-      <c r="P77" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>7</v>
-      </c>
-      <c r="R77" s="3">
         <v>0</v>
       </c>
     </row>
